--- a/_templates/DEFAULT WP.xlsx
+++ b/_templates/DEFAULT WP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\colby\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Colby.Kellersberger\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5707AB1A-09E7-4218-9B3C-C2B4DD588D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFEA60D-698E-4B49-8CE9-2561CB68CC57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23625" yWindow="2595" windowWidth="25170" windowHeight="16305" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4900" yWindow="4900" windowWidth="28800" windowHeight="15360" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions _ Common Tickmarks" sheetId="2" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="76">
   <si>
     <t>Tickmark</t>
   </si>
@@ -172,9 +172,6 @@
   </si>
   <si>
     <t>Daily</t>
-  </si>
-  <si>
-    <t>Multiple times per day</t>
   </si>
   <si>
     <t>Attachments</t>
@@ -1101,15 +1098,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF15488B"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF15488B"/>
       </left>
@@ -1381,6 +1369,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF15488B"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF0080C0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0080C0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1427,7 +1428,7 @@
     <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1482,18 +1483,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -1517,18 +1506,14 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1540,7 +1525,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1591,7 +1580,7 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -1600,14 +1589,14 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="43" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1628,11 +1617,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="43" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="43" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1643,15 +1632,15 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="48" fillId="34" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="48" fillId="34" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1705,9 +1694,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1723,11 +1709,11 @@
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="55" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="55" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="56" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1756,36 +1742,46 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1794,6 +1790,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="47" fillId="34" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="47" fillId="34" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1802,10 +1802,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="34" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1815,13 +1811,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1830,90 +1829,113 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1991,13 +2013,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>211667</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>170626</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>182727</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -2556,19 +2578,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83B0AAC3-C8F9-463F-BDFF-E021531C1393}">
   <dimension ref="B2:H16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
-    <col min="6" max="8" width="26.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.54296875" customWidth="1"/>
+    <col min="6" max="8" width="26.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B2" s="63" t="s">
+    <row r="2" spans="2:8" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B2" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="64" t="s">
+      <c r="C2" s="60" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -2576,151 +2598,146 @@
       </c>
       <c r="H2" s="16"/>
     </row>
-    <row r="3" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="74" t="s">
+    <row r="3" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="101" t="s">
+      <c r="C3" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="101"/>
-      <c r="F3" s="102" t="s">
+      <c r="D3" s="98"/>
+      <c r="F3" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-    </row>
-    <row r="4" spans="2:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="75" t="s">
+      <c r="G3" s="97"/>
+      <c r="H3" s="97"/>
+    </row>
+    <row r="4" spans="2:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="101" t="s">
+      <c r="C4" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="101"/>
-      <c r="F4" s="59" t="s">
+      <c r="D4" s="98"/>
+      <c r="F4" s="55" t="s">
         <v>8</v>
       </c>
       <c r="H4" s="16"/>
     </row>
-    <row r="5" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="72" t="s">
+    <row r="5" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="101" t="s">
+      <c r="C5" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="101"/>
-      <c r="F5" s="59" t="s">
+      <c r="D5" s="98"/>
+      <c r="F5" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="72" t="s">
+    <row r="6" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="101" t="s">
+      <c r="C6" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="101"/>
-      <c r="F6" s="62" t="s">
+      <c r="D6" s="98"/>
+      <c r="F6" s="58" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="72" t="s">
+    <row r="7" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="101" t="s">
+      <c r="C7" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="101"/>
-      <c r="F7" s="58" t="s">
+      <c r="D7" s="98"/>
+      <c r="F7" s="54" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="72" t="s">
+    <row r="8" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="101" t="s">
+      <c r="C8" s="98" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="101"/>
-    </row>
-    <row r="9" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="72" t="s">
+      <c r="D8" s="98"/>
+    </row>
+    <row r="9" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="101" t="s">
+      <c r="C9" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="101"/>
-    </row>
-    <row r="10" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="72" t="s">
+      <c r="D9" s="98"/>
+    </row>
+    <row r="10" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="101" t="s">
+      <c r="C10" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="101"/>
-    </row>
-    <row r="11" spans="2:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="72" t="s">
+      <c r="D10" s="98"/>
+    </row>
+    <row r="11" spans="2:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="101" t="s">
+      <c r="C11" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="101"/>
-    </row>
-    <row r="12" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="72" t="s">
+      <c r="D11" s="98"/>
+    </row>
+    <row r="12" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="101" t="s">
+      <c r="C12" s="98" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="101"/>
-    </row>
-    <row r="13" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="73"/>
-      <c r="C13" s="70"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="72" t="s">
+      <c r="D12" s="98"/>
+    </row>
+    <row r="13" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="69"/>
+      <c r="C13" s="66"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B14" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="101" t="s">
+      <c r="C14" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="101"/>
-    </row>
-    <row r="15" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="72"/>
-      <c r="C15" s="101"/>
-      <c r="D15" s="101"/>
-    </row>
-    <row r="16" spans="2:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="72" t="s">
+      <c r="D14" s="98"/>
+    </row>
+    <row r="15" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="68"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="98"/>
+    </row>
+    <row r="16" spans="2:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="101" t="s">
+      <c r="C16" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="101"/>
+      <c r="D16" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C15:D15"/>
@@ -2730,6 +2747,11 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2738,37 +2760,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:U73"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:U71"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.5703125" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="27.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="29.85546875" style="16" customWidth="1"/>
+    <col min="1" max="1" width="1.54296875" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="18.453125" customWidth="1"/>
+    <col min="4" max="4" width="27.1796875" customWidth="1"/>
+    <col min="5" max="5" width="23.453125" customWidth="1"/>
+    <col min="6" max="6" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.453125" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.453125" customWidth="1"/>
+    <col min="13" max="13" width="13.453125" customWidth="1"/>
+    <col min="14" max="14" width="29.81640625" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B2" s="125"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
+    <row r="2" spans="2:21" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
     </row>
-    <row r="3" spans="2:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -2780,17 +2802,17 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="126" t="s">
+    <row r="4" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="100" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="127"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="129"/>
-      <c r="I4" s="130"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="104"/>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="S4" s="2"/>
@@ -2801,19 +2823,19 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="131" t="s">
+    <row r="5" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="105" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="132"/>
-      <c r="D5" s="133" t="s">
+      <c r="C5" s="106"/>
+      <c r="D5" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="135"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="103"/>
+      <c r="I5" s="104"/>
       <c r="J5" s="15"/>
       <c r="K5" s="15"/>
       <c r="S5" s="2"/>
@@ -2822,19 +2844,19 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="103" t="s">
+    <row r="6" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="107" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="104"/>
-      <c r="D6" s="105" t="s">
+      <c r="C6" s="108"/>
+      <c r="D6" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="106"/>
-      <c r="F6" s="106"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="106"/>
-      <c r="I6" s="107"/>
+      <c r="E6" s="141"/>
+      <c r="F6" s="141"/>
+      <c r="G6" s="141"/>
+      <c r="H6" s="141"/>
+      <c r="I6" s="142"/>
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
       <c r="S6" s="2"/>
@@ -2843,1091 +2865,1062 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="17"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="107"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2" t="s">
+    <row r="8" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+      <c r="B8" s="36" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B8" s="18"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="108"/>
-      <c r="E8" s="109"/>
-      <c r="F8" s="109"/>
-      <c r="G8" s="109"/>
-      <c r="H8" s="109"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-    </row>
-    <row r="10" spans="2:21" ht="21" x14ac:dyDescent="0.25">
-      <c r="B10" s="40" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="2:21" s="21" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B9" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-    </row>
-    <row r="11" spans="2:21" s="25" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="22" t="s">
+      <c r="C9" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="D9" s="109" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="111" t="s">
+      <c r="E9" s="109"/>
+      <c r="F9" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="111"/>
-      <c r="F11" s="22" t="s">
+      <c r="G9" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="N9" s="47"/>
+    </row>
+    <row r="10" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B10" s="65">
+        <v>1</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="110"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="33"/>
+    </row>
+    <row r="11" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+    </row>
+    <row r="12" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+      <c r="B12" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="N11" s="51"/>
-    </row>
-    <row r="12" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="69">
+      <c r="I12" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+    </row>
+    <row r="13" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B13" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B14" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="117"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="118"/>
+      <c r="G14" s="119"/>
+      <c r="I14" s="22">
         <v>1</v>
       </c>
-      <c r="C12" s="38"/>
-      <c r="D12" s="112"/>
-      <c r="E12" s="112"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="37"/>
-    </row>
-    <row r="13" spans="2:21" ht="21" x14ac:dyDescent="0.25">
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-    </row>
-    <row r="14" spans="2:21" ht="21" x14ac:dyDescent="0.25">
-      <c r="B14" s="40" t="s">
-        <v>48</v>
-      </c>
-      <c r="I14" s="40" t="s">
-        <v>49</v>
-      </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-    </row>
-    <row r="15" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="22" t="s">
+      <c r="J14" s="114"/>
+      <c r="K14" s="115"/>
+      <c r="L14" s="116"/>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B15" s="22"/>
+      <c r="C15" s="120"/>
+      <c r="D15" s="121"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="121"/>
+      <c r="G15" s="122"/>
+      <c r="I15" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="J15" s="114"/>
+      <c r="K15" s="115"/>
+      <c r="L15" s="116"/>
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="B16" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="117"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="118"/>
+      <c r="G16" s="119"/>
+      <c r="I16" s="67" t="s">
+        <v>3</v>
+      </c>
+      <c r="J16" s="114"/>
+      <c r="K16" s="115"/>
+      <c r="L16" s="116"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B17" s="23"/>
+      <c r="C17" s="120"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="121"/>
+      <c r="G17" s="122"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="114"/>
+      <c r="K17" s="115"/>
+      <c r="L17" s="116"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B18" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="117"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="118"/>
+      <c r="G18" s="119"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C19" s="120"/>
+      <c r="D19" s="121"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="122"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+    </row>
+    <row r="21" spans="2:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+    </row>
+    <row r="22" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B22" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="53">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+    </row>
+    <row r="23" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B23" s="1"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="111" t="s">
+        <v>53</v>
+      </c>
+      <c r="I23" s="112"/>
+      <c r="J23" s="112"/>
+      <c r="K23" s="112"/>
+      <c r="L23" s="113"/>
+    </row>
+    <row r="24" spans="2:15" s="44" customFormat="1" ht="31" x14ac:dyDescent="0.35">
+      <c r="B24" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="64" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="64" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24" s="64" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" s="61" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24" s="62" t="s">
+        <v>61</v>
+      </c>
+      <c r="J24" s="62" t="s">
+        <v>62</v>
+      </c>
+      <c r="K24" s="62" t="s">
+        <v>63</v>
+      </c>
+      <c r="L24" s="63" t="s">
+        <v>64</v>
+      </c>
+      <c r="M24" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="N24" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="O24" s="20"/>
+    </row>
+    <row r="25" spans="2:15" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B25" s="37">
+        <v>1</v>
+      </c>
+      <c r="C25" s="25"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="I25" s="57" t="s">
+        <v>6</v>
+      </c>
+      <c r="J25" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="K25" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="L25" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="M25" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="N25" s="48"/>
+    </row>
+    <row r="26" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="37">
+        <v>2</v>
+      </c>
+      <c r="C26" s="25"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="48"/>
+    </row>
+    <row r="27" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="37">
+        <v>3</v>
+      </c>
+      <c r="C27" s="25"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="48"/>
+    </row>
+    <row r="28" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="37">
+        <v>4</v>
+      </c>
+      <c r="C28" s="25"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="48"/>
+    </row>
+    <row r="29" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="37">
+        <v>5</v>
+      </c>
+      <c r="C29" s="25"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="48"/>
+    </row>
+    <row r="30" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="37">
+        <v>6</v>
+      </c>
+      <c r="C30" s="25"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="30"/>
+      <c r="L30" s="30"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="48"/>
+    </row>
+    <row r="31" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="37">
+        <v>7</v>
+      </c>
+      <c r="C31" s="25"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="31"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="48"/>
+    </row>
+    <row r="32" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="37">
+        <v>8</v>
+      </c>
+      <c r="C32" s="25"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="48"/>
+    </row>
+    <row r="33" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="37">
+        <v>9</v>
+      </c>
+      <c r="C33" s="25"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="27"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="30"/>
+      <c r="L33" s="30"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="48"/>
+    </row>
+    <row r="34" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="37">
+        <v>10</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="48"/>
+    </row>
+    <row r="35" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="37">
+        <v>11</v>
+      </c>
+      <c r="C35" s="25"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="30"/>
+      <c r="L35" s="30"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="48"/>
+    </row>
+    <row r="36" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="37">
+        <v>12</v>
+      </c>
+      <c r="C36" s="25"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="27"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="48"/>
+    </row>
+    <row r="37" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="37">
+        <v>13</v>
+      </c>
+      <c r="C37" s="25"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="27"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="27"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="48"/>
+    </row>
+    <row r="38" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="37">
+        <v>14</v>
+      </c>
+      <c r="C38" s="25"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="27"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="27"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="30"/>
+      <c r="L38" s="30"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="48"/>
+    </row>
+    <row r="39" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="37">
+        <v>15</v>
+      </c>
+      <c r="C39" s="25"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="30"/>
+      <c r="L39" s="30"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="48"/>
+    </row>
+    <row r="40" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="37">
+        <v>16</v>
+      </c>
+      <c r="C40" s="25"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="26"/>
+      <c r="N40" s="48"/>
+    </row>
+    <row r="41" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="37">
+        <v>17</v>
+      </c>
+      <c r="C41" s="25"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="28"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="30"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="48"/>
+    </row>
+    <row r="42" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="37">
+        <v>18</v>
+      </c>
+      <c r="C42" s="25"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="48"/>
+    </row>
+    <row r="43" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="37">
+        <v>19</v>
+      </c>
+      <c r="C43" s="25"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="48"/>
+    </row>
+    <row r="44" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="37">
+        <v>20</v>
+      </c>
+      <c r="C44" s="25"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="28"/>
+      <c r="J44" s="29"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="26"/>
+      <c r="N44" s="48"/>
+    </row>
+    <row r="45" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="37">
+        <v>21</v>
+      </c>
+      <c r="C45" s="25"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="28"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="30"/>
+      <c r="M45" s="26"/>
+      <c r="N45" s="48"/>
+    </row>
+    <row r="46" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="37">
+        <v>22</v>
+      </c>
+      <c r="C46" s="25"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="48"/>
+    </row>
+    <row r="47" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="37">
+        <v>23</v>
+      </c>
+      <c r="C47" s="25"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="26"/>
+      <c r="N47" s="48"/>
+    </row>
+    <row r="48" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="37">
+        <v>24</v>
+      </c>
+      <c r="C48" s="25"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="26"/>
+      <c r="N48" s="48"/>
+    </row>
+    <row r="49" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="37">
+        <v>25</v>
+      </c>
+      <c r="C49" s="25"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="26"/>
+      <c r="N49" s="48"/>
+    </row>
+    <row r="50" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="37">
+        <v>26</v>
+      </c>
+      <c r="C50" s="25"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="31"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="28"/>
+      <c r="J50" s="29"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="26"/>
+      <c r="N50" s="48"/>
+    </row>
+    <row r="51" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="37">
+        <v>27</v>
+      </c>
+      <c r="C51" s="25"/>
+      <c r="D51" s="27"/>
+      <c r="E51" s="27"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="27"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="26"/>
+      <c r="N51" s="48"/>
+    </row>
+    <row r="52" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="37">
+        <v>28</v>
+      </c>
+      <c r="C52" s="25"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="26"/>
+      <c r="N52" s="48"/>
+    </row>
+    <row r="53" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="37">
+        <v>29</v>
+      </c>
+      <c r="C53" s="25"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="28"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="30"/>
+      <c r="M53" s="26"/>
+      <c r="N53" s="48"/>
+    </row>
+    <row r="54" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="37">
+        <v>30</v>
+      </c>
+      <c r="C54" s="25"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="31"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="28"/>
+      <c r="J54" s="29"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="26"/>
+      <c r="N54" s="48"/>
+    </row>
+    <row r="55" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B55" s="37">
+        <v>31</v>
+      </c>
+      <c r="C55" s="25"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="27"/>
+      <c r="H55" s="49"/>
+      <c r="I55" s="50"/>
+      <c r="J55" s="49"/>
+      <c r="K55" s="49"/>
+      <c r="L55" s="49"/>
+      <c r="M55" s="26"/>
+      <c r="N55" s="48"/>
+    </row>
+    <row r="56" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B56" s="37">
+        <v>32</v>
+      </c>
+      <c r="C56" s="25"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="49"/>
+      <c r="I56" s="50"/>
+      <c r="J56" s="49"/>
+      <c r="K56" s="49"/>
+      <c r="L56" s="49"/>
+      <c r="M56" s="26"/>
+      <c r="N56" s="48"/>
+    </row>
+    <row r="57" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B57" s="37">
+        <v>33</v>
+      </c>
+      <c r="C57" s="25"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="49"/>
+      <c r="I57" s="50"/>
+      <c r="J57" s="49"/>
+      <c r="K57" s="50"/>
+      <c r="L57" s="49"/>
+      <c r="M57" s="26"/>
+      <c r="N57" s="48"/>
+    </row>
+    <row r="58" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B58" s="37">
+        <v>34</v>
+      </c>
+      <c r="C58" s="25"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="49"/>
+      <c r="I58" s="50"/>
+      <c r="J58" s="49"/>
+      <c r="K58" s="50"/>
+      <c r="L58" s="49"/>
+      <c r="M58" s="26"/>
+      <c r="N58" s="48"/>
+    </row>
+    <row r="59" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B59" s="37">
+        <v>35</v>
+      </c>
+      <c r="C59" s="25"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="49"/>
+      <c r="I59" s="50"/>
+      <c r="J59" s="49"/>
+      <c r="K59" s="49"/>
+      <c r="L59" s="49"/>
+      <c r="M59" s="26"/>
+      <c r="N59" s="48"/>
+    </row>
+    <row r="60" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B60" s="37">
+        <v>36</v>
+      </c>
+      <c r="C60" s="25"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27"/>
+      <c r="G60" s="27"/>
+      <c r="H60" s="49"/>
+      <c r="I60" s="50"/>
+      <c r="J60" s="49"/>
+      <c r="K60" s="49"/>
+      <c r="L60" s="49"/>
+      <c r="M60" s="26"/>
+      <c r="N60" s="48"/>
+    </row>
+    <row r="61" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B61" s="37">
+        <v>37</v>
+      </c>
+      <c r="C61" s="25"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="49"/>
+      <c r="I61" s="49"/>
+      <c r="J61" s="49"/>
+      <c r="K61" s="49"/>
+      <c r="L61" s="49"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="45"/>
+    </row>
+    <row r="62" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B62" s="37">
+        <v>38</v>
+      </c>
+      <c r="C62" s="25"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="27"/>
+      <c r="G62" s="27"/>
+      <c r="H62" s="49"/>
+      <c r="I62" s="50"/>
+      <c r="J62" s="49"/>
+      <c r="K62" s="50"/>
+      <c r="L62" s="49"/>
+      <c r="M62" s="26"/>
+      <c r="N62" s="48"/>
+    </row>
+    <row r="63" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B63" s="37">
+        <v>39</v>
+      </c>
+      <c r="C63" s="25"/>
+      <c r="D63" s="27"/>
+      <c r="E63" s="27"/>
+      <c r="F63" s="27"/>
+      <c r="G63" s="27"/>
+      <c r="H63" s="49"/>
+      <c r="I63" s="50"/>
+      <c r="J63" s="49"/>
+      <c r="K63" s="50"/>
+      <c r="L63" s="49"/>
+      <c r="M63" s="26"/>
+      <c r="N63" s="48"/>
+    </row>
+    <row r="64" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B64" s="37">
+        <v>40</v>
+      </c>
+      <c r="C64" s="25"/>
+      <c r="D64" s="27"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="27"/>
+      <c r="H64" s="49"/>
+      <c r="I64" s="50"/>
+      <c r="J64" s="49"/>
+      <c r="K64" s="50"/>
+      <c r="L64" s="49"/>
+      <c r="M64" s="26"/>
+      <c r="N64" s="48"/>
+    </row>
+    <row r="65" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B65" s="37">
+        <v>41</v>
+      </c>
+      <c r="C65" s="25"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="27"/>
+      <c r="F65" s="27"/>
+      <c r="G65" s="27"/>
+      <c r="H65" s="49"/>
+      <c r="I65" s="50"/>
+      <c r="J65" s="49"/>
+      <c r="K65" s="50"/>
+      <c r="L65" s="49"/>
+      <c r="M65" s="26"/>
+      <c r="N65" s="48"/>
+    </row>
+    <row r="66" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B66" s="37">
+        <v>42</v>
+      </c>
+      <c r="C66" s="25"/>
+      <c r="D66" s="27"/>
+      <c r="E66" s="27"/>
+      <c r="F66" s="27"/>
+      <c r="G66" s="27"/>
+      <c r="H66" s="49"/>
+      <c r="I66" s="50"/>
+      <c r="J66" s="49"/>
+      <c r="K66" s="50"/>
+      <c r="L66" s="49"/>
+      <c r="M66" s="26"/>
+      <c r="N66" s="48"/>
+    </row>
+    <row r="67" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B67" s="37">
         <v>43</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C67" s="25"/>
+      <c r="D67" s="27"/>
+      <c r="E67" s="27"/>
+      <c r="F67" s="27"/>
+      <c r="G67" s="27"/>
+      <c r="H67" s="49"/>
+      <c r="I67" s="50"/>
+      <c r="J67" s="49"/>
+      <c r="K67" s="50"/>
+      <c r="L67" s="49"/>
+      <c r="M67" s="26"/>
+      <c r="N67" s="48"/>
+    </row>
+    <row r="68" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B68" s="37">
         <v>44</v>
       </c>
-      <c r="I15" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B16" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="119"/>
-      <c r="D16" s="120"/>
-      <c r="E16" s="120"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="121"/>
-      <c r="I16" s="26">
-        <v>1</v>
-      </c>
-      <c r="J16" s="116"/>
-      <c r="K16" s="117"/>
-      <c r="L16" s="118"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B17" s="26"/>
-      <c r="C17" s="122"/>
-      <c r="D17" s="123"/>
-      <c r="E17" s="123"/>
-      <c r="F17" s="123"/>
-      <c r="G17" s="124"/>
-      <c r="I17" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="J17" s="116"/>
-      <c r="K17" s="117"/>
-      <c r="L17" s="118"/>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B18" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="119"/>
-      <c r="D18" s="120"/>
-      <c r="E18" s="120"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="121"/>
-      <c r="I18" s="71" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="116"/>
-      <c r="K18" s="117"/>
-      <c r="L18" s="118"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B19" s="27"/>
-      <c r="C19" s="122"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="123"/>
-      <c r="F19" s="123"/>
-      <c r="G19" s="124"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="116"/>
-      <c r="K19" s="117"/>
-      <c r="L19" s="118"/>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B20" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="119"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="120"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="121"/>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C21" s="122"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="123"/>
-      <c r="F21" s="123"/>
-      <c r="G21" s="124"/>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-    </row>
-    <row r="23" spans="2:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-    </row>
-    <row r="24" spans="2:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B24" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="12"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="57">
-        <v>1</v>
-      </c>
-      <c r="H24" s="1"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-    </row>
-    <row r="25" spans="2:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B25" s="1"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="113" t="s">
-        <v>54</v>
-      </c>
-      <c r="I25" s="114"/>
-      <c r="J25" s="114"/>
-      <c r="K25" s="114"/>
-      <c r="L25" s="115"/>
-    </row>
-    <row r="26" spans="2:15" s="48" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B26" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="68" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="68" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" s="68" t="s">
-        <v>58</v>
-      </c>
-      <c r="F26" s="68" t="s">
-        <v>59</v>
-      </c>
-      <c r="G26" s="68" t="s">
-        <v>60</v>
-      </c>
-      <c r="H26" s="65" t="s">
-        <v>61</v>
-      </c>
-      <c r="I26" s="66" t="s">
-        <v>62</v>
-      </c>
-      <c r="J26" s="66" t="s">
-        <v>63</v>
-      </c>
-      <c r="K26" s="66" t="s">
-        <v>64</v>
-      </c>
-      <c r="L26" s="67" t="s">
-        <v>65</v>
-      </c>
-      <c r="M26" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="N26" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="O26" s="24"/>
-    </row>
-    <row r="27" spans="2:15" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="41">
-        <v>1</v>
-      </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="61" t="s">
-        <v>6</v>
-      </c>
-      <c r="J27" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="N27" s="52"/>
-    </row>
-    <row r="28" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="41">
-        <v>2</v>
-      </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="36"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="30"/>
-      <c r="N28" s="52"/>
-    </row>
-    <row r="29" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="41">
-        <v>3</v>
-      </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="34"/>
-      <c r="L29" s="34"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="52"/>
-    </row>
-    <row r="30" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="41">
-        <v>4</v>
-      </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="30"/>
-      <c r="N30" s="52"/>
-    </row>
-    <row r="31" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="41">
-        <v>5</v>
-      </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="31"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="52"/>
-    </row>
-    <row r="32" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="41">
-        <v>6</v>
-      </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="33"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="52"/>
-    </row>
-    <row r="33" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="41">
-        <v>7</v>
-      </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="31"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="52"/>
-    </row>
-    <row r="34" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="41">
-        <v>8</v>
-      </c>
-      <c r="C34" s="29"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="31"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="30"/>
-      <c r="N34" s="52"/>
-    </row>
-    <row r="35" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="41">
-        <v>9</v>
-      </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="32"/>
-      <c r="J35" s="33"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="30"/>
-      <c r="N35" s="52"/>
-    </row>
-    <row r="36" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="41">
-        <v>10</v>
-      </c>
-      <c r="C36" s="29"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="35"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="30"/>
-      <c r="N36" s="52"/>
-    </row>
-    <row r="37" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="41">
-        <v>11</v>
-      </c>
-      <c r="C37" s="29"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="36"/>
-      <c r="I37" s="32"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="34"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="52"/>
-    </row>
-    <row r="38" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="41">
-        <v>12</v>
-      </c>
-      <c r="C38" s="29"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="32"/>
-      <c r="J38" s="33"/>
-      <c r="K38" s="34"/>
-      <c r="L38" s="34"/>
-      <c r="M38" s="30"/>
-      <c r="N38" s="52"/>
-    </row>
-    <row r="39" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="41">
-        <v>13</v>
-      </c>
-      <c r="C39" s="29"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="32"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="34"/>
-      <c r="L39" s="34"/>
-      <c r="M39" s="30"/>
-      <c r="N39" s="52"/>
-    </row>
-    <row r="40" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="41">
-        <v>14</v>
-      </c>
-      <c r="C40" s="29"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="31"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="32"/>
-      <c r="J40" s="33"/>
-      <c r="K40" s="34"/>
-      <c r="L40" s="34"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="52"/>
-    </row>
-    <row r="41" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="41">
-        <v>15</v>
-      </c>
-      <c r="C41" s="29"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="36"/>
-      <c r="I41" s="32"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="34"/>
-      <c r="L41" s="34"/>
-      <c r="M41" s="30"/>
-      <c r="N41" s="52"/>
-    </row>
-    <row r="42" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="41">
-        <v>16</v>
-      </c>
-      <c r="C42" s="29"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="32"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="34"/>
-      <c r="M42" s="30"/>
-      <c r="N42" s="52"/>
-    </row>
-    <row r="43" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="41">
-        <v>17</v>
-      </c>
-      <c r="C43" s="29"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="36"/>
-      <c r="I43" s="32"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="34"/>
-      <c r="L43" s="34"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="52"/>
-    </row>
-    <row r="44" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="41">
-        <v>18</v>
-      </c>
-      <c r="C44" s="29"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="32"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="34"/>
-      <c r="L44" s="34"/>
-      <c r="M44" s="30"/>
-      <c r="N44" s="52"/>
-    </row>
-    <row r="45" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="41">
-        <v>19</v>
-      </c>
-      <c r="C45" s="29"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="35"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="36"/>
-      <c r="I45" s="32"/>
-      <c r="J45" s="33"/>
-      <c r="K45" s="34"/>
-      <c r="L45" s="34"/>
-      <c r="M45" s="30"/>
-      <c r="N45" s="52"/>
-    </row>
-    <row r="46" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="41">
-        <v>20</v>
-      </c>
-      <c r="C46" s="29"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="32"/>
-      <c r="J46" s="33"/>
-      <c r="K46" s="34"/>
-      <c r="L46" s="34"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="52"/>
-    </row>
-    <row r="47" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="41">
-        <v>21</v>
-      </c>
-      <c r="C47" s="29"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="35"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="36"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="33"/>
-      <c r="K47" s="34"/>
-      <c r="L47" s="34"/>
-      <c r="M47" s="30"/>
-      <c r="N47" s="52"/>
-    </row>
-    <row r="48" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="41">
-        <v>22</v>
-      </c>
-      <c r="C48" s="29"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="35"/>
-      <c r="G48" s="31"/>
-      <c r="H48" s="36"/>
-      <c r="I48" s="32"/>
-      <c r="J48" s="33"/>
-      <c r="K48" s="34"/>
-      <c r="L48" s="34"/>
-      <c r="M48" s="30"/>
-      <c r="N48" s="52"/>
-    </row>
-    <row r="49" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="41">
-        <v>23</v>
-      </c>
-      <c r="C49" s="29"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="35"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="36"/>
-      <c r="I49" s="32"/>
-      <c r="J49" s="33"/>
-      <c r="K49" s="34"/>
-      <c r="L49" s="34"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="52"/>
-    </row>
-    <row r="50" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="41">
-        <v>24</v>
-      </c>
-      <c r="C50" s="29"/>
-      <c r="D50" s="31"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="35"/>
-      <c r="G50" s="31"/>
-      <c r="H50" s="36"/>
-      <c r="I50" s="32"/>
-      <c r="J50" s="33"/>
-      <c r="K50" s="34"/>
-      <c r="L50" s="34"/>
-      <c r="M50" s="30"/>
-      <c r="N50" s="52"/>
-    </row>
-    <row r="51" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="41">
-        <v>25</v>
-      </c>
-      <c r="C51" s="29"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="35"/>
-      <c r="G51" s="31"/>
-      <c r="H51" s="36"/>
-      <c r="I51" s="32"/>
-      <c r="J51" s="33"/>
-      <c r="K51" s="34"/>
-      <c r="L51" s="34"/>
-      <c r="M51" s="30"/>
-      <c r="N51" s="52"/>
-    </row>
-    <row r="52" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="41">
-        <v>26</v>
-      </c>
-      <c r="C52" s="29"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="35"/>
-      <c r="G52" s="31"/>
-      <c r="H52" s="36"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="33"/>
-      <c r="K52" s="34"/>
-      <c r="L52" s="34"/>
-      <c r="M52" s="30"/>
-      <c r="N52" s="52"/>
-    </row>
-    <row r="53" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="41">
-        <v>27</v>
-      </c>
-      <c r="C53" s="29"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="35"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="36"/>
-      <c r="I53" s="32"/>
-      <c r="J53" s="33"/>
-      <c r="K53" s="34"/>
-      <c r="L53" s="34"/>
-      <c r="M53" s="30"/>
-      <c r="N53" s="52"/>
-    </row>
-    <row r="54" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="41">
-        <v>28</v>
-      </c>
-      <c r="C54" s="29"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31"/>
-      <c r="F54" s="35"/>
-      <c r="G54" s="31"/>
-      <c r="H54" s="36"/>
-      <c r="I54" s="32"/>
-      <c r="J54" s="33"/>
-      <c r="K54" s="34"/>
-      <c r="L54" s="34"/>
-      <c r="M54" s="30"/>
-      <c r="N54" s="52"/>
-    </row>
-    <row r="55" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="41">
-        <v>29</v>
-      </c>
-      <c r="C55" s="29"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="31"/>
-      <c r="H55" s="36"/>
-      <c r="I55" s="32"/>
-      <c r="J55" s="33"/>
-      <c r="K55" s="34"/>
-      <c r="L55" s="34"/>
-      <c r="M55" s="30"/>
-      <c r="N55" s="52"/>
-    </row>
-    <row r="56" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="41">
-        <v>30</v>
-      </c>
-      <c r="C56" s="29"/>
-      <c r="D56" s="31"/>
-      <c r="E56" s="31"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="31"/>
-      <c r="H56" s="36"/>
-      <c r="I56" s="32"/>
-      <c r="J56" s="33"/>
-      <c r="K56" s="34"/>
-      <c r="L56" s="34"/>
-      <c r="M56" s="30"/>
-      <c r="N56" s="52"/>
-    </row>
-    <row r="57" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B57" s="41">
-        <v>31</v>
-      </c>
-      <c r="C57" s="29"/>
-      <c r="D57" s="31"/>
-      <c r="E57" s="31"/>
-      <c r="F57" s="31"/>
-      <c r="G57" s="31"/>
-      <c r="H57" s="53"/>
-      <c r="I57" s="54"/>
-      <c r="J57" s="53"/>
-      <c r="K57" s="53"/>
-      <c r="L57" s="53"/>
-      <c r="M57" s="30"/>
-      <c r="N57" s="52"/>
-    </row>
-    <row r="58" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B58" s="41">
-        <v>32</v>
-      </c>
-      <c r="C58" s="29"/>
-      <c r="D58" s="31"/>
-      <c r="E58" s="31"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="31"/>
-      <c r="H58" s="53"/>
-      <c r="I58" s="54"/>
-      <c r="J58" s="53"/>
-      <c r="K58" s="53"/>
-      <c r="L58" s="53"/>
-      <c r="M58" s="30"/>
-      <c r="N58" s="52"/>
-    </row>
-    <row r="59" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B59" s="41">
-        <v>33</v>
-      </c>
-      <c r="C59" s="29"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31"/>
-      <c r="F59" s="31"/>
-      <c r="G59" s="31"/>
-      <c r="H59" s="53"/>
-      <c r="I59" s="54"/>
-      <c r="J59" s="53"/>
-      <c r="K59" s="54"/>
-      <c r="L59" s="53"/>
-      <c r="M59" s="30"/>
-      <c r="N59" s="52"/>
-    </row>
-    <row r="60" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B60" s="41">
-        <v>34</v>
-      </c>
-      <c r="C60" s="29"/>
-      <c r="D60" s="31"/>
-      <c r="E60" s="31"/>
-      <c r="F60" s="31"/>
-      <c r="G60" s="31"/>
-      <c r="H60" s="53"/>
-      <c r="I60" s="54"/>
-      <c r="J60" s="53"/>
-      <c r="K60" s="54"/>
-      <c r="L60" s="53"/>
-      <c r="M60" s="30"/>
-      <c r="N60" s="52"/>
-    </row>
-    <row r="61" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B61" s="41">
-        <v>35</v>
-      </c>
-      <c r="C61" s="29"/>
-      <c r="D61" s="31"/>
-      <c r="E61" s="31"/>
-      <c r="F61" s="31"/>
-      <c r="G61" s="31"/>
-      <c r="H61" s="53"/>
-      <c r="I61" s="54"/>
-      <c r="J61" s="53"/>
-      <c r="K61" s="53"/>
-      <c r="L61" s="53"/>
-      <c r="M61" s="30"/>
-      <c r="N61" s="52"/>
-    </row>
-    <row r="62" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B62" s="41">
-        <v>36</v>
-      </c>
-      <c r="C62" s="29"/>
-      <c r="D62" s="31"/>
-      <c r="E62" s="31"/>
-      <c r="F62" s="31"/>
-      <c r="G62" s="31"/>
-      <c r="H62" s="53"/>
-      <c r="I62" s="54"/>
-      <c r="J62" s="53"/>
-      <c r="K62" s="53"/>
-      <c r="L62" s="53"/>
-      <c r="M62" s="30"/>
-      <c r="N62" s="52"/>
-    </row>
-    <row r="63" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B63" s="41">
-        <v>37</v>
-      </c>
-      <c r="C63" s="29"/>
-      <c r="D63" s="31"/>
-      <c r="E63" s="31"/>
-      <c r="F63" s="31"/>
-      <c r="G63" s="31"/>
-      <c r="H63" s="53"/>
-      <c r="I63" s="53"/>
-      <c r="J63" s="53"/>
-      <c r="K63" s="53"/>
-      <c r="L63" s="53"/>
-      <c r="M63" s="30"/>
-      <c r="N63" s="49"/>
-    </row>
-    <row r="64" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B64" s="41">
-        <v>38</v>
-      </c>
-      <c r="C64" s="29"/>
-      <c r="D64" s="31"/>
-      <c r="E64" s="31"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="31"/>
-      <c r="H64" s="53"/>
-      <c r="I64" s="54"/>
-      <c r="J64" s="53"/>
-      <c r="K64" s="54"/>
-      <c r="L64" s="53"/>
-      <c r="M64" s="30"/>
-      <c r="N64" s="52"/>
-    </row>
-    <row r="65" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B65" s="41">
-        <v>39</v>
-      </c>
-      <c r="C65" s="29"/>
-      <c r="D65" s="31"/>
-      <c r="E65" s="31"/>
-      <c r="F65" s="31"/>
-      <c r="G65" s="31"/>
-      <c r="H65" s="53"/>
-      <c r="I65" s="54"/>
-      <c r="J65" s="53"/>
-      <c r="K65" s="54"/>
-      <c r="L65" s="53"/>
-      <c r="M65" s="30"/>
-      <c r="N65" s="52"/>
-    </row>
-    <row r="66" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B66" s="41">
-        <v>40</v>
-      </c>
-      <c r="C66" s="29"/>
-      <c r="D66" s="31"/>
-      <c r="E66" s="31"/>
-      <c r="F66" s="31"/>
-      <c r="G66" s="31"/>
-      <c r="H66" s="53"/>
-      <c r="I66" s="54"/>
-      <c r="J66" s="53"/>
-      <c r="K66" s="54"/>
-      <c r="L66" s="53"/>
-      <c r="M66" s="30"/>
-      <c r="N66" s="52"/>
-    </row>
-    <row r="67" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B67" s="41">
-        <v>41</v>
-      </c>
-      <c r="C67" s="29"/>
-      <c r="D67" s="31"/>
-      <c r="E67" s="31"/>
-      <c r="F67" s="31"/>
-      <c r="G67" s="31"/>
-      <c r="H67" s="53"/>
-      <c r="I67" s="54"/>
-      <c r="J67" s="53"/>
-      <c r="K67" s="54"/>
-      <c r="L67" s="53"/>
-      <c r="M67" s="30"/>
-      <c r="N67" s="52"/>
-    </row>
-    <row r="68" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="41">
-        <v>42</v>
-      </c>
-      <c r="C68" s="29"/>
-      <c r="D68" s="31"/>
-      <c r="E68" s="31"/>
-      <c r="F68" s="31"/>
-      <c r="G68" s="31"/>
-      <c r="H68" s="53"/>
-      <c r="I68" s="54"/>
-      <c r="J68" s="53"/>
-      <c r="K68" s="54"/>
-      <c r="L68" s="53"/>
-      <c r="M68" s="30"/>
-      <c r="N68" s="52"/>
-    </row>
-    <row r="69" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="41">
-        <v>43</v>
-      </c>
-      <c r="C69" s="29"/>
-      <c r="D69" s="31"/>
-      <c r="E69" s="31"/>
-      <c r="F69" s="31"/>
-      <c r="G69" s="31"/>
-      <c r="H69" s="53"/>
-      <c r="I69" s="54"/>
-      <c r="J69" s="53"/>
-      <c r="K69" s="54"/>
-      <c r="L69" s="53"/>
-      <c r="M69" s="30"/>
-      <c r="N69" s="52"/>
-    </row>
-    <row r="70" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B70" s="41">
-        <v>44</v>
-      </c>
-      <c r="C70" s="29"/>
-      <c r="D70" s="31"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="55"/>
-      <c r="I70" s="54"/>
-      <c r="J70" s="53"/>
-      <c r="K70" s="54"/>
-      <c r="L70" s="54"/>
-      <c r="M70" s="30"/>
-      <c r="N70" s="52"/>
-    </row>
-    <row r="71" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B71" s="41">
+      <c r="C68" s="25"/>
+      <c r="D68" s="27"/>
+      <c r="E68" s="27"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="27"/>
+      <c r="H68" s="51"/>
+      <c r="I68" s="50"/>
+      <c r="J68" s="49"/>
+      <c r="K68" s="50"/>
+      <c r="L68" s="50"/>
+      <c r="M68" s="26"/>
+      <c r="N68" s="48"/>
+    </row>
+    <row r="69" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="B69" s="37">
         <v>45</v>
       </c>
-      <c r="C71" s="29"/>
-      <c r="D71" s="31"/>
-      <c r="E71" s="31"/>
-      <c r="F71" s="31"/>
-      <c r="G71" s="31"/>
-      <c r="H71" s="53"/>
-      <c r="I71" s="54"/>
-      <c r="J71" s="53"/>
-      <c r="K71" s="54"/>
-      <c r="L71" s="53"/>
-      <c r="M71" s="30"/>
-      <c r="N71" s="52"/>
-    </row>
-    <row r="72" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="41"/>
-      <c r="C72" s="42"/>
-      <c r="D72" s="43"/>
-      <c r="E72" s="43"/>
-      <c r="F72" s="44"/>
-      <c r="G72" s="43"/>
-      <c r="H72" s="45"/>
-      <c r="I72" s="46"/>
-      <c r="J72" s="46"/>
-      <c r="K72" s="46"/>
-      <c r="L72" s="46"/>
-      <c r="M72" s="47"/>
-      <c r="N72" s="50"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B73" s="4"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
-      <c r="H73" s="6"/>
-      <c r="I73" s="6"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="6"/>
-      <c r="L73" s="6"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="27"/>
+      <c r="E69" s="27"/>
+      <c r="F69" s="27"/>
+      <c r="G69" s="27"/>
+      <c r="H69" s="49"/>
+      <c r="I69" s="50"/>
+      <c r="J69" s="49"/>
+      <c r="K69" s="50"/>
+      <c r="L69" s="49"/>
+      <c r="M69" s="26"/>
+      <c r="N69" s="48"/>
+    </row>
+    <row r="70" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B70" s="37"/>
+      <c r="C70" s="38"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="40"/>
+      <c r="G70" s="39"/>
+      <c r="H70" s="41"/>
+      <c r="I70" s="42"/>
+      <c r="J70" s="42"/>
+      <c r="K70" s="42"/>
+      <c r="L70" s="42"/>
+      <c r="M70" s="43"/>
+      <c r="N70" s="46"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B71" s="4"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="6"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="H23:L23"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="C16:G17"/>
+    <mergeCell ref="C18:G19"/>
+    <mergeCell ref="C14:G15"/>
+    <mergeCell ref="D6:I6"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:I4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D5:I5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:I8"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="H25:L25"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="J19:L19"/>
-    <mergeCell ref="C18:G19"/>
-    <mergeCell ref="C20:G21"/>
-    <mergeCell ref="C16:G17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3937,37 +3930,37 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AD103B3-4618-405C-A46A-99E8E6568320}">
-  <dimension ref="B2:U69"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:U67"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.5703125" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="27.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="29.85546875" style="16" customWidth="1"/>
+    <col min="1" max="1" width="1.54296875" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="18.453125" customWidth="1"/>
+    <col min="4" max="4" width="27.1796875" customWidth="1"/>
+    <col min="5" max="5" width="23.453125" customWidth="1"/>
+    <col min="6" max="6" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.453125" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.453125" customWidth="1"/>
+    <col min="13" max="13" width="13.453125" customWidth="1"/>
+    <col min="14" max="14" width="29.81640625" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B2" s="125"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
+    <row r="2" spans="2:21" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
     </row>
-    <row r="3" spans="2:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -3979,17 +3972,17 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="126" t="s">
+    <row r="4" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="100" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="127"/>
-      <c r="D4" s="128"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="129"/>
-      <c r="I4" s="130"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="141"/>
+      <c r="F4" s="141"/>
+      <c r="G4" s="141"/>
+      <c r="H4" s="141"/>
+      <c r="I4" s="142"/>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="S4" s="2"/>
@@ -4000,19 +3993,19 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="131" t="s">
+    <row r="5" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="105" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="132"/>
-      <c r="D5" s="133" t="s">
+      <c r="C5" s="106"/>
+      <c r="D5" s="137" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="135"/>
+      <c r="E5" s="138"/>
+      <c r="F5" s="138"/>
+      <c r="G5" s="138"/>
+      <c r="H5" s="138"/>
+      <c r="I5" s="139"/>
       <c r="J5" s="15"/>
       <c r="K5" s="15"/>
       <c r="S5" s="2"/>
@@ -4021,19 +4014,19 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="103" t="s">
+    <row r="6" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="107" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="104"/>
-      <c r="D6" s="105" t="s">
+      <c r="C6" s="108"/>
+      <c r="D6" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="106"/>
-      <c r="F6" s="106"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="106"/>
-      <c r="I6" s="107"/>
+      <c r="E6" s="141"/>
+      <c r="F6" s="141"/>
+      <c r="G6" s="141"/>
+      <c r="H6" s="141"/>
+      <c r="I6" s="142"/>
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
       <c r="S6" s="2"/>
@@ -4042,867 +4035,838 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="17"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="107"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2" t="s">
+    <row r="8" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+      <c r="B8" s="36" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B8" s="18"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="108"/>
-      <c r="E8" s="109"/>
-      <c r="F8" s="109"/>
-      <c r="G8" s="109"/>
-      <c r="H8" s="109"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-    </row>
-    <row r="10" spans="2:21" ht="21" x14ac:dyDescent="0.25">
-      <c r="B10" s="40" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="2:21" s="21" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B9" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-    </row>
-    <row r="11" spans="2:21" s="25" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="22" t="s">
+      <c r="C9" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="D9" s="109" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="111" t="s">
+      <c r="E9" s="109"/>
+      <c r="F9" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="111"/>
-      <c r="F11" s="22" t="s">
+      <c r="G9" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="N9" s="47"/>
+    </row>
+    <row r="10" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="95">
+        <v>1</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="110"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="33"/>
+    </row>
+    <row r="11" spans="2:21" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+    </row>
+    <row r="12" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+      <c r="B12" s="72" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+    </row>
+    <row r="13" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+      <c r="B13" s="73" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="74" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+    </row>
+    <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="91"/>
+      <c r="C14" s="149"/>
+      <c r="D14" s="143"/>
+      <c r="E14" s="144"/>
+      <c r="F14" s="144"/>
+      <c r="G14" s="148"/>
+      <c r="H14" s="36"/>
+    </row>
+    <row r="15" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="91"/>
+      <c r="C15" s="149"/>
+      <c r="D15" s="143"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="148"/>
+      <c r="H15" s="36"/>
+    </row>
+    <row r="16" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="91"/>
+      <c r="C16" s="149"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="144"/>
+      <c r="F16" s="144"/>
+      <c r="G16" s="148"/>
+      <c r="H16" s="36"/>
+    </row>
+    <row r="17" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="91"/>
+      <c r="C17" s="149"/>
+      <c r="D17" s="143"/>
+      <c r="E17" s="144"/>
+      <c r="F17" s="144"/>
+      <c r="G17" s="148"/>
+      <c r="H17" s="36"/>
+    </row>
+    <row r="18" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="91"/>
+      <c r="C18" s="149"/>
+      <c r="D18" s="145"/>
+      <c r="E18" s="146"/>
+      <c r="F18" s="146"/>
+      <c r="G18" s="147"/>
+      <c r="H18" s="36"/>
+    </row>
+    <row r="19" spans="2:8" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="75"/>
+      <c r="C19" s="84"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+    </row>
+    <row r="20" spans="2:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="B20" s="72" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="85"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+    </row>
+    <row r="21" spans="2:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="B21" s="76" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="77" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="85"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+    </row>
+    <row r="22" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="90"/>
+      <c r="C22" s="143"/>
+      <c r="D22" s="144"/>
+      <c r="E22" s="144"/>
+      <c r="F22" s="144"/>
+      <c r="G22" s="148"/>
+      <c r="H22" s="36"/>
+    </row>
+    <row r="23" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="90"/>
+      <c r="C23" s="143"/>
+      <c r="D23" s="144"/>
+      <c r="E23" s="144"/>
+      <c r="F23" s="144"/>
+      <c r="G23" s="148"/>
+      <c r="H23" s="36"/>
+    </row>
+    <row r="24" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="90"/>
+      <c r="C24" s="145"/>
+      <c r="D24" s="146"/>
+      <c r="E24" s="146"/>
+      <c r="F24" s="146"/>
+      <c r="G24" s="147"/>
+      <c r="H24" s="36"/>
+    </row>
+    <row r="25" spans="2:8" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="75"/>
+      <c r="C25" s="84"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="85"/>
+      <c r="F25" s="85"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+    </row>
+    <row r="26" spans="2:8" ht="21" x14ac:dyDescent="0.35">
+      <c r="B26" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="N11" s="51"/>
-    </row>
-    <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="100">
+    </row>
+    <row r="27" spans="2:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B27" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B28" s="92" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="123"/>
+      <c r="D28" s="124"/>
+      <c r="E28" s="124"/>
+      <c r="F28" s="124"/>
+      <c r="G28" s="125"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B29" s="92"/>
+      <c r="C29" s="126"/>
+      <c r="D29" s="127"/>
+      <c r="E29" s="127"/>
+      <c r="F29" s="127"/>
+      <c r="G29" s="128"/>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B30" s="92" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="123"/>
+      <c r="D30" s="124"/>
+      <c r="E30" s="124"/>
+      <c r="F30" s="124"/>
+      <c r="G30" s="125"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B31" s="93"/>
+      <c r="C31" s="126"/>
+      <c r="D31" s="127"/>
+      <c r="E31" s="127"/>
+      <c r="F31" s="127"/>
+      <c r="G31" s="128"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B32" s="92" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="123"/>
+      <c r="D32" s="124"/>
+      <c r="E32" s="124"/>
+      <c r="F32" s="124"/>
+      <c r="G32" s="125"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33" s="94"/>
+      <c r="C33" s="126"/>
+      <c r="D33" s="127"/>
+      <c r="E33" s="127"/>
+      <c r="F33" s="127"/>
+      <c r="G33" s="128"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+    </row>
+    <row r="35" spans="2:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+    </row>
+    <row r="36" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B36" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="12"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="11"/>
+    </row>
+    <row r="37" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B37" s="1"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="111" t="s">
+        <v>53</v>
+      </c>
+      <c r="I37" s="112"/>
+      <c r="J37" s="112"/>
+      <c r="K37" s="112"/>
+      <c r="L37" s="113"/>
+    </row>
+    <row r="38" spans="2:15" s="44" customFormat="1" ht="31" x14ac:dyDescent="0.35">
+      <c r="B38" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" s="64" t="s">
+        <v>56</v>
+      </c>
+      <c r="E38" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="F38" s="64" t="s">
+        <v>58</v>
+      </c>
+      <c r="G38" s="64" t="s">
+        <v>59</v>
+      </c>
+      <c r="H38" s="61" t="s">
+        <v>60</v>
+      </c>
+      <c r="I38" s="62" t="s">
+        <v>61</v>
+      </c>
+      <c r="J38" s="62" t="s">
+        <v>62</v>
+      </c>
+      <c r="K38" s="62" t="s">
+        <v>63</v>
+      </c>
+      <c r="L38" s="63" t="s">
+        <v>64</v>
+      </c>
+      <c r="M38" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="N38" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="O38" s="20"/>
+    </row>
+    <row r="39" spans="2:15" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+      <c r="B39" s="37">
         <v>1</v>
       </c>
-      <c r="C12" s="38"/>
-      <c r="D12" s="112"/>
-      <c r="E12" s="112"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="37"/>
-    </row>
-    <row r="13" spans="2:21" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-    </row>
-    <row r="14" spans="2:21" ht="21" x14ac:dyDescent="0.25">
-      <c r="B14" s="76" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-    </row>
-    <row r="15" spans="2:21" ht="21" x14ac:dyDescent="0.25">
-      <c r="B15" s="77" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="78" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="78" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-    </row>
-    <row r="16" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="96"/>
-      <c r="C16" s="85"/>
-      <c r="D16" s="142"/>
-      <c r="E16" s="142"/>
-      <c r="F16" s="142"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-    </row>
-    <row r="17" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="96"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="142"/>
-      <c r="E17" s="142"/>
-      <c r="F17" s="142"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="40"/>
-    </row>
-    <row r="18" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="96"/>
-      <c r="C18" s="85"/>
-      <c r="D18" s="142"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="142"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
-    </row>
-    <row r="19" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="96"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="142"/>
-      <c r="E19" s="142"/>
-      <c r="F19" s="142"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="40"/>
-    </row>
-    <row r="20" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="96"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="142"/>
-      <c r="E20" s="142"/>
-      <c r="F20" s="142"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-    </row>
-    <row r="21" spans="2:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="79"/>
-      <c r="C21" s="89"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="90"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="40"/>
-    </row>
-    <row r="22" spans="2:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B22" s="76" t="s">
-        <v>49</v>
-      </c>
-      <c r="F22" s="90"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-    </row>
-    <row r="23" spans="2:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B23" s="80" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="81" t="s">
-        <v>71</v>
-      </c>
-      <c r="F23" s="90"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
-    </row>
-    <row r="24" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="95"/>
-      <c r="C24" s="142"/>
-      <c r="D24" s="142"/>
-      <c r="E24" s="142"/>
-      <c r="F24" s="90"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-    </row>
-    <row r="25" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="95"/>
-      <c r="C25" s="142"/>
-      <c r="D25" s="142"/>
-      <c r="E25" s="142"/>
-      <c r="F25" s="90"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="40"/>
-    </row>
-    <row r="26" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="95"/>
-      <c r="C26" s="142"/>
-      <c r="D26" s="142"/>
-      <c r="E26" s="142"/>
-      <c r="F26" s="90"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="40"/>
-    </row>
-    <row r="27" spans="2:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="79"/>
-      <c r="C27" s="89"/>
-      <c r="D27" s="90"/>
-      <c r="E27" s="90"/>
-      <c r="F27" s="90"/>
-      <c r="G27" s="40"/>
-      <c r="H27" s="40"/>
-    </row>
-    <row r="28" spans="2:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B28" s="40" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="97" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" s="136"/>
-      <c r="D30" s="137"/>
-      <c r="E30" s="137"/>
-      <c r="F30" s="137"/>
-      <c r="G30" s="138"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="97"/>
-      <c r="C31" s="139"/>
-      <c r="D31" s="140"/>
-      <c r="E31" s="140"/>
-      <c r="F31" s="140"/>
-      <c r="G31" s="141"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="97" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" s="136"/>
-      <c r="D32" s="137"/>
-      <c r="E32" s="137"/>
-      <c r="F32" s="137"/>
-      <c r="G32" s="138"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B33" s="98"/>
-      <c r="C33" s="139"/>
-      <c r="D33" s="140"/>
-      <c r="E33" s="140"/>
-      <c r="F33" s="140"/>
-      <c r="G33" s="141"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B34" s="97" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" s="136"/>
-      <c r="D34" s="137"/>
-      <c r="E34" s="137"/>
-      <c r="F34" s="137"/>
-      <c r="G34" s="138"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B35" s="99"/>
-      <c r="C35" s="139"/>
-      <c r="D35" s="140"/>
-      <c r="E35" s="140"/>
-      <c r="F35" s="140"/>
-      <c r="G35" s="141"/>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-    </row>
-    <row r="37" spans="2:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-    </row>
-    <row r="38" spans="2:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B38" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="12"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-    </row>
-    <row r="39" spans="2:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B39" s="1"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="113" t="s">
-        <v>54</v>
-      </c>
-      <c r="I39" s="114"/>
-      <c r="J39" s="114"/>
-      <c r="K39" s="114"/>
-      <c r="L39" s="115"/>
-    </row>
-    <row r="40" spans="2:15" s="48" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B40" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="C40" s="68" t="s">
-        <v>56</v>
-      </c>
-      <c r="D40" s="68" t="s">
-        <v>57</v>
-      </c>
-      <c r="E40" s="68" t="s">
-        <v>58</v>
-      </c>
-      <c r="F40" s="68" t="s">
-        <v>59</v>
-      </c>
-      <c r="G40" s="68" t="s">
-        <v>60</v>
-      </c>
-      <c r="H40" s="65" t="s">
-        <v>61</v>
-      </c>
-      <c r="I40" s="66" t="s">
-        <v>62</v>
-      </c>
-      <c r="J40" s="66" t="s">
-        <v>63</v>
-      </c>
-      <c r="K40" s="66" t="s">
-        <v>64</v>
-      </c>
-      <c r="L40" s="67" t="s">
-        <v>65</v>
-      </c>
-      <c r="M40" s="23" t="s">
+      <c r="C39" s="25"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="86" t="s">
+        <v>73</v>
+      </c>
+      <c r="I39" s="87" t="s">
+        <v>74</v>
+      </c>
+      <c r="J39" s="86" t="s">
+        <v>73</v>
+      </c>
+      <c r="K39" s="86" t="s">
+        <v>73</v>
+      </c>
+      <c r="L39" s="86" t="s">
+        <v>73</v>
+      </c>
+      <c r="M39" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="N40" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="O40" s="24"/>
-    </row>
-    <row r="41" spans="2:15" s="3" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B41" s="41">
-        <v>1</v>
-      </c>
-      <c r="C41" s="29"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="91" t="s">
-        <v>74</v>
-      </c>
-      <c r="I41" s="92" t="s">
+      <c r="N39" s="48"/>
+    </row>
+    <row r="40" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="37">
+        <v>2</v>
+      </c>
+      <c r="C40" s="25"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="27"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="26"/>
+      <c r="N40" s="48"/>
+    </row>
+    <row r="41" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="37">
+        <v>3</v>
+      </c>
+      <c r="C41" s="25"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="28"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="30"/>
+      <c r="L41" s="30"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="48"/>
+    </row>
+    <row r="42" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="37">
+        <v>4</v>
+      </c>
+      <c r="C42" s="25"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="30"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="48"/>
+    </row>
+    <row r="43" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="37">
+        <v>5</v>
+      </c>
+      <c r="C43" s="25"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="48"/>
+    </row>
+    <row r="44" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="37">
+        <v>6</v>
+      </c>
+      <c r="C44" s="25"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="28"/>
+      <c r="J44" s="29"/>
+      <c r="K44" s="30"/>
+      <c r="L44" s="30"/>
+      <c r="M44" s="26"/>
+      <c r="N44" s="48"/>
+    </row>
+    <row r="45" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="37">
+        <v>7</v>
+      </c>
+      <c r="C45" s="25"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="28"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="30"/>
+      <c r="M45" s="26"/>
+      <c r="N45" s="48"/>
+    </row>
+    <row r="46" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B46" s="37">
+        <v>8</v>
+      </c>
+      <c r="C46" s="25"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="27"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="48"/>
+    </row>
+    <row r="47" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B47" s="37">
+        <v>9</v>
+      </c>
+      <c r="C47" s="25"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="30"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="26"/>
+      <c r="N47" s="48"/>
+    </row>
+    <row r="48" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="37">
+        <v>10</v>
+      </c>
+      <c r="C48" s="25"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="27"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="30"/>
+      <c r="L48" s="30"/>
+      <c r="M48" s="26"/>
+      <c r="N48" s="48"/>
+    </row>
+    <row r="49" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="37">
+        <v>11</v>
+      </c>
+      <c r="C49" s="25"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="27"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="26"/>
+      <c r="N49" s="48"/>
+    </row>
+    <row r="50" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="37">
+        <v>12</v>
+      </c>
+      <c r="C50" s="25"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="31"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="28"/>
+      <c r="J50" s="29"/>
+      <c r="K50" s="30"/>
+      <c r="L50" s="30"/>
+      <c r="M50" s="26"/>
+      <c r="N50" s="48"/>
+    </row>
+    <row r="51" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="37">
+        <v>13</v>
+      </c>
+      <c r="C51" s="25"/>
+      <c r="D51" s="27"/>
+      <c r="E51" s="27"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="27"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="30"/>
+      <c r="L51" s="30"/>
+      <c r="M51" s="26"/>
+      <c r="N51" s="48"/>
+    </row>
+    <row r="52" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="37">
+        <v>14</v>
+      </c>
+      <c r="C52" s="25"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="26"/>
+      <c r="N52" s="48"/>
+    </row>
+    <row r="53" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="37">
+        <v>15</v>
+      </c>
+      <c r="C53" s="25"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="28"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="30"/>
+      <c r="M53" s="26"/>
+      <c r="N53" s="48"/>
+    </row>
+    <row r="54" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="37">
+        <v>16</v>
+      </c>
+      <c r="C54" s="25"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="31"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="28"/>
+      <c r="J54" s="29"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="30"/>
+      <c r="M54" s="26"/>
+      <c r="N54" s="48"/>
+    </row>
+    <row r="55" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="37">
+        <v>17</v>
+      </c>
+      <c r="C55" s="25"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="27"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="28"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="26"/>
+      <c r="N55" s="48"/>
+    </row>
+    <row r="56" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B56" s="37">
+        <v>18</v>
+      </c>
+      <c r="C56" s="25"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="31"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="28"/>
+      <c r="J56" s="29"/>
+      <c r="K56" s="30"/>
+      <c r="L56" s="30"/>
+      <c r="M56" s="26"/>
+      <c r="N56" s="48"/>
+    </row>
+    <row r="57" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B57" s="37">
+        <v>19</v>
+      </c>
+      <c r="C57" s="25"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="31"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="29"/>
+      <c r="K57" s="30"/>
+      <c r="L57" s="30"/>
+      <c r="M57" s="26"/>
+      <c r="N57" s="48"/>
+    </row>
+    <row r="58" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B58" s="37">
+        <v>20</v>
+      </c>
+      <c r="C58" s="25"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="29"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="26"/>
+      <c r="N58" s="48"/>
+    </row>
+    <row r="59" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B59" s="37">
+        <v>21</v>
+      </c>
+      <c r="C59" s="25"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="31"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="28"/>
+      <c r="J59" s="29"/>
+      <c r="K59" s="30"/>
+      <c r="L59" s="30"/>
+      <c r="M59" s="26"/>
+      <c r="N59" s="48"/>
+    </row>
+    <row r="60" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B60" s="37">
+        <v>22</v>
+      </c>
+      <c r="C60" s="25"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="31"/>
+      <c r="G60" s="27"/>
+      <c r="H60" s="32"/>
+      <c r="I60" s="28"/>
+      <c r="J60" s="29"/>
+      <c r="K60" s="30"/>
+      <c r="L60" s="30"/>
+      <c r="M60" s="26"/>
+      <c r="N60" s="48"/>
+    </row>
+    <row r="61" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B61" s="37">
+        <v>23</v>
+      </c>
+      <c r="C61" s="25"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="28"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="48"/>
+    </row>
+    <row r="62" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B62" s="37">
+        <v>24</v>
+      </c>
+      <c r="C62" s="25"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="31"/>
+      <c r="G62" s="27"/>
+      <c r="H62" s="32"/>
+      <c r="I62" s="28"/>
+      <c r="J62" s="29"/>
+      <c r="K62" s="30"/>
+      <c r="L62" s="30"/>
+      <c r="M62" s="26"/>
+      <c r="N62" s="48"/>
+    </row>
+    <row r="63" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B63" s="37">
+        <v>25</v>
+      </c>
+      <c r="C63" s="25"/>
+      <c r="D63" s="27"/>
+      <c r="E63" s="27"/>
+      <c r="F63" s="31"/>
+      <c r="G63" s="27"/>
+      <c r="H63" s="32"/>
+      <c r="I63" s="28"/>
+      <c r="J63" s="29"/>
+      <c r="K63" s="30"/>
+      <c r="L63" s="30"/>
+      <c r="M63" s="26"/>
+      <c r="N63" s="48"/>
+    </row>
+    <row r="64" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B64" s="37"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="39"/>
+      <c r="E64" s="39"/>
+      <c r="F64" s="40"/>
+      <c r="G64" s="39"/>
+      <c r="H64" s="41"/>
+      <c r="I64" s="42"/>
+      <c r="J64" s="42"/>
+      <c r="K64" s="42"/>
+      <c r="L64" s="42"/>
+      <c r="M64" s="43"/>
+      <c r="N64" s="46"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B65" s="4"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="C67" s="89" t="s">
         <v>75</v>
       </c>
-      <c r="J41" s="91" t="s">
-        <v>74</v>
-      </c>
-      <c r="K41" s="91" t="s">
-        <v>74</v>
-      </c>
-      <c r="L41" s="91" t="s">
-        <v>74</v>
-      </c>
-      <c r="M41" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="N41" s="52"/>
-    </row>
-    <row r="42" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="41">
-        <v>2</v>
-      </c>
-      <c r="C42" s="29"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="32"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="34"/>
-      <c r="M42" s="30"/>
-      <c r="N42" s="52"/>
-    </row>
-    <row r="43" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="41">
-        <v>3</v>
-      </c>
-      <c r="C43" s="29"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="36"/>
-      <c r="I43" s="32"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="34"/>
-      <c r="L43" s="34"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="52"/>
-    </row>
-    <row r="44" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="41">
-        <v>4</v>
-      </c>
-      <c r="C44" s="29"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="36"/>
-      <c r="I44" s="32"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="34"/>
-      <c r="L44" s="34"/>
-      <c r="M44" s="30"/>
-      <c r="N44" s="52"/>
-    </row>
-    <row r="45" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="41">
-        <v>5</v>
-      </c>
-      <c r="C45" s="29"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="35"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="36"/>
-      <c r="I45" s="32"/>
-      <c r="J45" s="33"/>
-      <c r="K45" s="34"/>
-      <c r="L45" s="34"/>
-      <c r="M45" s="30"/>
-      <c r="N45" s="52"/>
-    </row>
-    <row r="46" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="41">
-        <v>6</v>
-      </c>
-      <c r="C46" s="29"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="32"/>
-      <c r="J46" s="33"/>
-      <c r="K46" s="34"/>
-      <c r="L46" s="34"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="52"/>
-    </row>
-    <row r="47" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="41">
-        <v>7</v>
-      </c>
-      <c r="C47" s="29"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="35"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="36"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="33"/>
-      <c r="K47" s="34"/>
-      <c r="L47" s="34"/>
-      <c r="M47" s="30"/>
-      <c r="N47" s="52"/>
-    </row>
-    <row r="48" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="41">
-        <v>8</v>
-      </c>
-      <c r="C48" s="29"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="35"/>
-      <c r="G48" s="31"/>
-      <c r="H48" s="36"/>
-      <c r="I48" s="32"/>
-      <c r="J48" s="33"/>
-      <c r="K48" s="34"/>
-      <c r="L48" s="34"/>
-      <c r="M48" s="30"/>
-      <c r="N48" s="52"/>
-    </row>
-    <row r="49" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="41">
-        <v>9</v>
-      </c>
-      <c r="C49" s="29"/>
-      <c r="D49" s="31"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="35"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="36"/>
-      <c r="I49" s="32"/>
-      <c r="J49" s="33"/>
-      <c r="K49" s="34"/>
-      <c r="L49" s="34"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="52"/>
-    </row>
-    <row r="50" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="41">
-        <v>10</v>
-      </c>
-      <c r="C50" s="29"/>
-      <c r="D50" s="31"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="35"/>
-      <c r="G50" s="31"/>
-      <c r="H50" s="36"/>
-      <c r="I50" s="32"/>
-      <c r="J50" s="33"/>
-      <c r="K50" s="34"/>
-      <c r="L50" s="34"/>
-      <c r="M50" s="30"/>
-      <c r="N50" s="52"/>
-    </row>
-    <row r="51" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="41">
-        <v>11</v>
-      </c>
-      <c r="C51" s="29"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="35"/>
-      <c r="G51" s="31"/>
-      <c r="H51" s="36"/>
-      <c r="I51" s="32"/>
-      <c r="J51" s="33"/>
-      <c r="K51" s="34"/>
-      <c r="L51" s="34"/>
-      <c r="M51" s="30"/>
-      <c r="N51" s="52"/>
-    </row>
-    <row r="52" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="41">
-        <v>12</v>
-      </c>
-      <c r="C52" s="29"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="35"/>
-      <c r="G52" s="31"/>
-      <c r="H52" s="36"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="33"/>
-      <c r="K52" s="34"/>
-      <c r="L52" s="34"/>
-      <c r="M52" s="30"/>
-      <c r="N52" s="52"/>
-    </row>
-    <row r="53" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="41">
-        <v>13</v>
-      </c>
-      <c r="C53" s="29"/>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="35"/>
-      <c r="G53" s="31"/>
-      <c r="H53" s="36"/>
-      <c r="I53" s="32"/>
-      <c r="J53" s="33"/>
-      <c r="K53" s="34"/>
-      <c r="L53" s="34"/>
-      <c r="M53" s="30"/>
-      <c r="N53" s="52"/>
-    </row>
-    <row r="54" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="41">
-        <v>14</v>
-      </c>
-      <c r="C54" s="29"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31"/>
-      <c r="F54" s="35"/>
-      <c r="G54" s="31"/>
-      <c r="H54" s="36"/>
-      <c r="I54" s="32"/>
-      <c r="J54" s="33"/>
-      <c r="K54" s="34"/>
-      <c r="L54" s="34"/>
-      <c r="M54" s="30"/>
-      <c r="N54" s="52"/>
-    </row>
-    <row r="55" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="41">
-        <v>15</v>
-      </c>
-      <c r="C55" s="29"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="31"/>
-      <c r="H55" s="36"/>
-      <c r="I55" s="32"/>
-      <c r="J55" s="33"/>
-      <c r="K55" s="34"/>
-      <c r="L55" s="34"/>
-      <c r="M55" s="30"/>
-      <c r="N55" s="52"/>
-    </row>
-    <row r="56" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="41">
-        <v>16</v>
-      </c>
-      <c r="C56" s="29"/>
-      <c r="D56" s="31"/>
-      <c r="E56" s="31"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="31"/>
-      <c r="H56" s="36"/>
-      <c r="I56" s="32"/>
-      <c r="J56" s="33"/>
-      <c r="K56" s="34"/>
-      <c r="L56" s="34"/>
-      <c r="M56" s="30"/>
-      <c r="N56" s="52"/>
-    </row>
-    <row r="57" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="41">
-        <v>17</v>
-      </c>
-      <c r="C57" s="29"/>
-      <c r="D57" s="31"/>
-      <c r="E57" s="31"/>
-      <c r="F57" s="35"/>
-      <c r="G57" s="31"/>
-      <c r="H57" s="36"/>
-      <c r="I57" s="32"/>
-      <c r="J57" s="33"/>
-      <c r="K57" s="34"/>
-      <c r="L57" s="34"/>
-      <c r="M57" s="30"/>
-      <c r="N57" s="52"/>
-    </row>
-    <row r="58" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="41">
-        <v>18</v>
-      </c>
-      <c r="C58" s="29"/>
-      <c r="D58" s="31"/>
-      <c r="E58" s="31"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="31"/>
-      <c r="H58" s="36"/>
-      <c r="I58" s="32"/>
-      <c r="J58" s="33"/>
-      <c r="K58" s="34"/>
-      <c r="L58" s="34"/>
-      <c r="M58" s="30"/>
-      <c r="N58" s="52"/>
-    </row>
-    <row r="59" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="41">
-        <v>19</v>
-      </c>
-      <c r="C59" s="29"/>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31"/>
-      <c r="F59" s="35"/>
-      <c r="G59" s="31"/>
-      <c r="H59" s="36"/>
-      <c r="I59" s="32"/>
-      <c r="J59" s="33"/>
-      <c r="K59" s="34"/>
-      <c r="L59" s="34"/>
-      <c r="M59" s="30"/>
-      <c r="N59" s="52"/>
-    </row>
-    <row r="60" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="41">
-        <v>20</v>
-      </c>
-      <c r="C60" s="29"/>
-      <c r="D60" s="31"/>
-      <c r="E60" s="31"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="31"/>
-      <c r="H60" s="36"/>
-      <c r="I60" s="32"/>
-      <c r="J60" s="33"/>
-      <c r="K60" s="34"/>
-      <c r="L60" s="34"/>
-      <c r="M60" s="30"/>
-      <c r="N60" s="52"/>
-    </row>
-    <row r="61" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="41">
-        <v>21</v>
-      </c>
-      <c r="C61" s="29"/>
-      <c r="D61" s="31"/>
-      <c r="E61" s="31"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="31"/>
-      <c r="H61" s="36"/>
-      <c r="I61" s="32"/>
-      <c r="J61" s="33"/>
-      <c r="K61" s="34"/>
-      <c r="L61" s="34"/>
-      <c r="M61" s="30"/>
-      <c r="N61" s="52"/>
-    </row>
-    <row r="62" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="41">
-        <v>22</v>
-      </c>
-      <c r="C62" s="29"/>
-      <c r="D62" s="31"/>
-      <c r="E62" s="31"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="31"/>
-      <c r="H62" s="36"/>
-      <c r="I62" s="32"/>
-      <c r="J62" s="33"/>
-      <c r="K62" s="34"/>
-      <c r="L62" s="34"/>
-      <c r="M62" s="30"/>
-      <c r="N62" s="52"/>
-    </row>
-    <row r="63" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="41">
-        <v>23</v>
-      </c>
-      <c r="C63" s="29"/>
-      <c r="D63" s="31"/>
-      <c r="E63" s="31"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="31"/>
-      <c r="H63" s="36"/>
-      <c r="I63" s="32"/>
-      <c r="J63" s="33"/>
-      <c r="K63" s="34"/>
-      <c r="L63" s="34"/>
-      <c r="M63" s="30"/>
-      <c r="N63" s="52"/>
-    </row>
-    <row r="64" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="41">
-        <v>24</v>
-      </c>
-      <c r="C64" s="29"/>
-      <c r="D64" s="31"/>
-      <c r="E64" s="31"/>
-      <c r="F64" s="35"/>
-      <c r="G64" s="31"/>
-      <c r="H64" s="36"/>
-      <c r="I64" s="32"/>
-      <c r="J64" s="33"/>
-      <c r="K64" s="34"/>
-      <c r="L64" s="34"/>
-      <c r="M64" s="30"/>
-      <c r="N64" s="52"/>
-    </row>
-    <row r="65" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="41">
-        <v>25</v>
-      </c>
-      <c r="C65" s="29"/>
-      <c r="D65" s="31"/>
-      <c r="E65" s="31"/>
-      <c r="F65" s="35"/>
-      <c r="G65" s="31"/>
-      <c r="H65" s="36"/>
-      <c r="I65" s="32"/>
-      <c r="J65" s="33"/>
-      <c r="K65" s="34"/>
-      <c r="L65" s="34"/>
-      <c r="M65" s="30"/>
-      <c r="N65" s="52"/>
-    </row>
-    <row r="66" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="41"/>
-      <c r="C66" s="42"/>
-      <c r="D66" s="43"/>
-      <c r="E66" s="43"/>
-      <c r="F66" s="44"/>
-      <c r="G66" s="43"/>
-      <c r="H66" s="45"/>
-      <c r="I66" s="46"/>
-      <c r="J66" s="46"/>
-      <c r="K66" s="46"/>
-      <c r="L66" s="46"/>
-      <c r="M66" s="47"/>
-      <c r="N66" s="50"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B67" s="4"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="6"/>
-      <c r="L67" s="6"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C69" s="94" t="s">
-        <v>76</v>
-      </c>
-      <c r="D69" t="str">
-        <f>IF(COUNTIF(M41:M65,"Yes")=0,
+      <c r="D67" t="str">
+        <f>IF(COUNTIF(M39:M63,"Yes")=0,
   "No exceptions noted.",
-  COUNTIF(M41:M65,"Yes")&amp;" exception(s) noted."
+  COUNTIF(M39:M63,"Yes")&amp;" exception(s) noted."
 )</f>
         <v>1 exception(s) noted.</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="C34:G35"/>
-    <mergeCell ref="H39:L39"/>
-    <mergeCell ref="C32:G33"/>
-    <mergeCell ref="C30:G31"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C24:G24"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:I8"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="D4:I4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D5:I5"/>
+    <mergeCell ref="D6:I6"/>
+    <mergeCell ref="C32:G33"/>
+    <mergeCell ref="H37:L37"/>
+    <mergeCell ref="C30:G31"/>
+    <mergeCell ref="C28:G29"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M41:M65" xr:uid="{7EA76EF9-12A3-48C6-BC4E-AF4D09AB486E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M39:M63" xr:uid="{7EA76EF9-12A3-48C6-BC4E-AF4D09AB486E}">
       <formula1>"Yes, No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4914,41 +4878,41 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27C2776A-E04F-41FD-B3D7-35684437E078}">
   <dimension ref="B1:U31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.5703125" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
-    <col min="4" max="4" width="27.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="17.5703125" customWidth="1"/>
+    <col min="1" max="1" width="1.54296875" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" customWidth="1"/>
+    <col min="3" max="3" width="23.81640625" customWidth="1"/>
+    <col min="4" max="4" width="27.1796875" customWidth="1"/>
+    <col min="5" max="5" width="23.453125" customWidth="1"/>
+    <col min="6" max="6" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.453125" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.453125" customWidth="1"/>
+    <col min="13" max="13" width="13.453125" customWidth="1"/>
+    <col min="14" max="14" width="17.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B1" s="9"/>
       <c r="N1" s="16"/>
     </row>
-    <row r="2" spans="2:21" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B2" s="125"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
+    <row r="2" spans="2:21" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
       <c r="N2" s="16"/>
     </row>
-    <row r="3" spans="2:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -4961,19 +4925,19 @@
       <c r="K3" s="1"/>
       <c r="N3" s="16"/>
     </row>
-    <row r="4" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="146" t="s">
+    <row r="4" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="132" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="133"/>
+      <c r="D4" s="134" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="147"/>
-      <c r="D4" s="148" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="149"/>
-      <c r="F4" s="149"/>
-      <c r="G4" s="149"/>
-      <c r="H4" s="149"/>
-      <c r="I4" s="150"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="136"/>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="N4" s="16"/>
@@ -4985,13 +4949,13 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B5" s="9"/>
       <c r="N5" s="16"/>
     </row>
-    <row r="6" spans="2:21" ht="21" x14ac:dyDescent="0.25">
-      <c r="B6" s="76" t="s">
-        <v>42</v>
+    <row r="6" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+      <c r="B6" s="72" t="s">
+        <v>41</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -5000,199 +4964,199 @@
       <c r="G6" s="7"/>
       <c r="N6" s="16"/>
     </row>
-    <row r="7" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="22" t="s">
+    <row r="7" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B7" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="D7" s="109" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="111" t="s">
+      <c r="E7" s="109"/>
+      <c r="F7" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="111"/>
-      <c r="F7" s="22" t="s">
+      <c r="G7" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="G7" s="22" t="s">
-        <v>47</v>
-      </c>
       <c r="N7" s="16"/>
     </row>
-    <row r="8" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="69">
+    <row r="8" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="95">
         <v>1</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="37"/>
+      <c r="C8" s="153"/>
+      <c r="D8" s="151"/>
+      <c r="E8" s="152"/>
+      <c r="F8" s="154"/>
+      <c r="G8" s="155"/>
       <c r="N8" s="16"/>
     </row>
-    <row r="9" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="69"/>
-      <c r="C9" s="86"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="87"/>
-      <c r="G9" s="88"/>
+    <row r="9" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B9" s="65"/>
+      <c r="C9" s="81"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="82"/>
+      <c r="G9" s="83"/>
       <c r="N9" s="16"/>
     </row>
-    <row r="10" spans="2:21" ht="21" x14ac:dyDescent="0.25">
-      <c r="B10" s="76" t="s">
-        <v>54</v>
+    <row r="10" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+      <c r="B10" s="72" t="s">
+        <v>53</v>
       </c>
       <c r="N10" s="16"/>
     </row>
-    <row r="11" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="77" t="s">
+    <row r="11" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B11" s="73" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="74" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="78" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" s="78" t="s">
-        <v>44</v>
-      </c>
       <c r="N11" s="16"/>
     </row>
-    <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="79"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="151"/>
-      <c r="E12" s="151"/>
-      <c r="F12" s="151"/>
+    <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="156"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="145"/>
+      <c r="E12" s="146"/>
+      <c r="F12" s="147"/>
       <c r="N12" s="16"/>
     </row>
-    <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="79"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="151"/>
-      <c r="E13" s="151"/>
-      <c r="F13" s="151"/>
+    <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="156"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="145"/>
+      <c r="E13" s="146"/>
+      <c r="F13" s="147"/>
       <c r="N13" s="16"/>
     </row>
-    <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="79"/>
-      <c r="C14" s="85"/>
-      <c r="D14" s="151"/>
-      <c r="E14" s="151"/>
-      <c r="F14" s="151"/>
+    <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="156"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="145"/>
+      <c r="E14" s="146"/>
+      <c r="F14" s="147"/>
       <c r="N14" s="16"/>
     </row>
-    <row r="15" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="79"/>
-      <c r="C15" s="85"/>
-      <c r="D15" s="151"/>
-      <c r="E15" s="151"/>
-      <c r="F15" s="151"/>
+    <row r="15" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="156"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="145"/>
+      <c r="E15" s="146"/>
+      <c r="F15" s="147"/>
       <c r="N15" s="16"/>
     </row>
-    <row r="16" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="79"/>
-      <c r="C16" s="85"/>
-      <c r="D16" s="151"/>
-      <c r="E16" s="151"/>
-      <c r="F16" s="151"/>
+    <row r="16" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="156"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="145"/>
+      <c r="E16" s="146"/>
+      <c r="F16" s="147"/>
       <c r="N16" s="16"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B17" s="9"/>
       <c r="N17" s="16"/>
     </row>
-    <row r="18" spans="2:14" ht="21" x14ac:dyDescent="0.25">
-      <c r="B18" s="76" t="s">
-        <v>49</v>
+    <row r="18" spans="2:14" ht="21" x14ac:dyDescent="0.35">
+      <c r="B18" s="72" t="s">
+        <v>48</v>
       </c>
       <c r="N18" s="16"/>
     </row>
-    <row r="19" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="80" t="s">
+    <row r="19" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B19" s="76" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="77" t="s">
+        <v>70</v>
+      </c>
+      <c r="N19" s="16"/>
+    </row>
+    <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="157"/>
+      <c r="C20" s="145"/>
+      <c r="D20" s="146"/>
+      <c r="E20" s="147"/>
+      <c r="N20" s="16"/>
+    </row>
+    <row r="21" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="157"/>
+      <c r="C21" s="145"/>
+      <c r="D21" s="146"/>
+      <c r="E21" s="147"/>
+      <c r="N21" s="16"/>
+    </row>
+    <row r="22" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="157"/>
+      <c r="C22" s="145"/>
+      <c r="D22" s="146"/>
+      <c r="E22" s="147"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="N22" s="16"/>
+    </row>
+    <row r="23" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="78"/>
+      <c r="C23" s="79"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="79"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="N23" s="16"/>
+    </row>
+    <row r="24" spans="2:14" ht="21" x14ac:dyDescent="0.35">
+      <c r="B24" s="72" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="72"/>
+      <c r="N24" s="16"/>
+    </row>
+    <row r="25" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B25" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="81" t="s">
+      <c r="N25" s="16"/>
+    </row>
+    <row r="26" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="92"/>
+      <c r="C26" s="151"/>
+      <c r="D26" s="150"/>
+      <c r="E26" s="150"/>
+      <c r="F26" s="150"/>
+      <c r="G26" s="152"/>
+      <c r="N26" s="16"/>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B27" s="22"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
+      <c r="N27" s="16"/>
+    </row>
+    <row r="28" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B28" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="N19" s="16"/>
-    </row>
-    <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="82"/>
-      <c r="C20" s="142"/>
-      <c r="D20" s="142"/>
-      <c r="E20" s="142"/>
-      <c r="N20" s="16"/>
-    </row>
-    <row r="21" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="82"/>
-      <c r="C21" s="142"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="142"/>
-      <c r="N21" s="16"/>
-    </row>
-    <row r="22" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="82"/>
-      <c r="C22" s="142"/>
-      <c r="D22" s="142"/>
-      <c r="E22" s="142"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="N22" s="16"/>
-    </row>
-    <row r="23" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="82"/>
-      <c r="C23" s="83"/>
-      <c r="D23" s="83"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
-      <c r="N23" s="16"/>
-    </row>
-    <row r="24" spans="2:14" ht="21" x14ac:dyDescent="0.25">
-      <c r="B24" s="76" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="76"/>
-      <c r="N24" s="16"/>
-    </row>
-    <row r="25" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="N25" s="16"/>
-    </row>
-    <row r="26" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="26"/>
-      <c r="C26" s="143"/>
-      <c r="D26" s="144"/>
-      <c r="E26" s="144"/>
-      <c r="F26" s="144"/>
-      <c r="G26" s="145"/>
-      <c r="N26" s="16"/>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B27" s="26"/>
-      <c r="C27" s="93"/>
-      <c r="D27" s="93"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="93"/>
-      <c r="N27" s="16"/>
-    </row>
-    <row r="28" spans="2:14" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B28" s="21" t="s">
-        <v>72</v>
-      </c>
       <c r="C28" s="12"/>
-      <c r="D28" s="28"/>
+      <c r="D28" s="24"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-      <c r="G28" s="57"/>
+      <c r="G28" s="53"/>
       <c r="H28" s="1"/>
       <c r="I28" s="11"/>
       <c r="J28" s="11"/>
@@ -5200,8 +5164,8 @@
       <c r="L28" s="11"/>
       <c r="N28" s="16"/>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C31" s="84"/>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="C31" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -5228,41 +5192,41 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D90A4130-68CA-4E30-9267-87839E021ADD}">
   <dimension ref="B1:U85"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.5703125" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" customWidth="1"/>
-    <col min="4" max="4" width="27.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="1.54296875" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" customWidth="1"/>
+    <col min="3" max="3" width="24.1796875" customWidth="1"/>
+    <col min="4" max="4" width="27.1796875" customWidth="1"/>
+    <col min="5" max="5" width="23.453125" customWidth="1"/>
+    <col min="6" max="6" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.453125" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.453125" customWidth="1"/>
+    <col min="13" max="13" width="13.453125" customWidth="1"/>
+    <col min="14" max="14" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B1" s="9"/>
       <c r="N1" s="16"/>
     </row>
-    <row r="2" spans="2:21" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B2" s="125"/>
-      <c r="C2" s="125"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
+    <row r="2" spans="2:21" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
       <c r="N2" s="16"/>
     </row>
-    <row r="3" spans="2:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -5275,19 +5239,19 @@
       <c r="K3" s="1"/>
       <c r="N3" s="16"/>
     </row>
-    <row r="4" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="146" t="s">
+    <row r="4" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="132" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="158"/>
+      <c r="D4" s="134" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="147"/>
-      <c r="D4" s="148" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="149"/>
-      <c r="F4" s="149"/>
-      <c r="G4" s="149"/>
-      <c r="H4" s="149"/>
-      <c r="I4" s="150"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="135"/>
+      <c r="I4" s="136"/>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="N4" s="16"/>
@@ -5299,13 +5263,13 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B5" s="9"/>
       <c r="N5" s="16"/>
     </row>
-    <row r="6" spans="2:21" ht="21" x14ac:dyDescent="0.25">
-      <c r="B6" s="76" t="s">
-        <v>42</v>
+    <row r="6" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+      <c r="B6" s="72" t="s">
+        <v>41</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -5314,400 +5278,400 @@
       <c r="G6" s="7"/>
       <c r="N6" s="16"/>
     </row>
-    <row r="7" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="22" t="s">
+    <row r="7" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B7" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="D7" s="109" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="111" t="s">
+      <c r="E7" s="109"/>
+      <c r="F7" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="111"/>
-      <c r="F7" s="22" t="s">
+      <c r="G7" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="G7" s="22" t="s">
-        <v>47</v>
-      </c>
       <c r="N7" s="16"/>
     </row>
-    <row r="8" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="69">
+    <row r="8" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="95">
         <v>1</v>
       </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="37"/>
+      <c r="C8" s="153"/>
+      <c r="D8" s="151"/>
+      <c r="E8" s="152"/>
+      <c r="F8" s="154"/>
+      <c r="G8" s="155"/>
       <c r="N8" s="16"/>
     </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.35">
       <c r="B9" s="9"/>
       <c r="N9" s="16"/>
     </row>
-    <row r="10" spans="2:21" ht="21" x14ac:dyDescent="0.25">
-      <c r="B10" s="76" t="s">
-        <v>54</v>
+    <row r="10" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+      <c r="B10" s="72" t="s">
+        <v>53</v>
       </c>
       <c r="N10" s="16"/>
     </row>
-    <row r="11" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="77" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="78" t="s">
+    <row r="11" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B11" s="73" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="78" t="s">
-        <v>71</v>
-      </c>
       <c r="N11" s="16"/>
     </row>
-    <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="79"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="151"/>
-      <c r="E12" s="151"/>
-      <c r="F12" s="151"/>
+    <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="156"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="145"/>
+      <c r="E12" s="146"/>
+      <c r="F12" s="147"/>
       <c r="N12" s="16"/>
     </row>
-    <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="79"/>
-      <c r="C13" s="85"/>
-      <c r="D13" s="151"/>
-      <c r="E13" s="151"/>
-      <c r="F13" s="151"/>
+    <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="156"/>
+      <c r="C13" s="96"/>
+      <c r="D13" s="145"/>
+      <c r="E13" s="146"/>
+      <c r="F13" s="147"/>
       <c r="N13" s="16"/>
     </row>
-    <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="79"/>
-      <c r="C14" s="85"/>
-      <c r="D14" s="151"/>
-      <c r="E14" s="151"/>
-      <c r="F14" s="151"/>
+    <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="156"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="145"/>
+      <c r="E14" s="146"/>
+      <c r="F14" s="147"/>
       <c r="N14" s="16"/>
     </row>
-    <row r="15" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="79"/>
-      <c r="C15" s="85"/>
-      <c r="D15" s="151"/>
-      <c r="E15" s="151"/>
-      <c r="F15" s="151"/>
+    <row r="15" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="156"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="145"/>
+      <c r="E15" s="146"/>
+      <c r="F15" s="147"/>
       <c r="N15" s="16"/>
     </row>
-    <row r="16" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="79"/>
-      <c r="C16" s="85"/>
-      <c r="D16" s="151"/>
-      <c r="E16" s="151"/>
-      <c r="F16" s="151"/>
+    <row r="16" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="156"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="145"/>
+      <c r="E16" s="146"/>
+      <c r="F16" s="147"/>
       <c r="N16" s="16"/>
     </row>
-    <row r="17" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="79"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
+    <row r="17" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B17" s="75"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="79"/>
       <c r="N17" s="16"/>
     </row>
-    <row r="18" spans="2:14" ht="21" x14ac:dyDescent="0.25">
-      <c r="B18" s="76" t="s">
-        <v>49</v>
+    <row r="18" spans="2:14" ht="21" x14ac:dyDescent="0.35">
+      <c r="B18" s="72" t="s">
+        <v>48</v>
       </c>
       <c r="N18" s="16"/>
     </row>
-    <row r="19" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="80" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="81" t="s">
-        <v>71</v>
+    <row r="19" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B19" s="76" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="77" t="s">
+        <v>70</v>
       </c>
       <c r="N19" s="16"/>
     </row>
-    <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="82"/>
-      <c r="C20" s="142"/>
-      <c r="D20" s="142"/>
-      <c r="E20" s="142"/>
+    <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="157"/>
+      <c r="C20" s="145"/>
+      <c r="D20" s="146"/>
+      <c r="E20" s="147"/>
       <c r="N20" s="16"/>
     </row>
-    <row r="21" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="82"/>
-      <c r="C21" s="142"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="142"/>
+    <row r="21" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="157"/>
+      <c r="C21" s="145"/>
+      <c r="D21" s="146"/>
+      <c r="E21" s="147"/>
       <c r="N21" s="16"/>
     </row>
-    <row r="22" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="82"/>
-      <c r="C22" s="142"/>
-      <c r="D22" s="142"/>
-      <c r="E22" s="142"/>
+    <row r="22" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="157"/>
+      <c r="C22" s="145"/>
+      <c r="D22" s="146"/>
+      <c r="E22" s="147"/>
       <c r="N22" s="16"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B23" s="9"/>
       <c r="N23" s="16"/>
     </row>
-    <row r="24" spans="2:14" ht="21" x14ac:dyDescent="0.25">
-      <c r="B24" s="76" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="76"/>
+    <row r="24" spans="2:14" ht="21" x14ac:dyDescent="0.35">
+      <c r="B24" s="72" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="72"/>
       <c r="N24" s="16"/>
     </row>
-    <row r="25" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="22" t="s">
+    <row r="25" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B25" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="39" t="s">
-        <v>44</v>
-      </c>
       <c r="N25" s="16"/>
     </row>
-    <row r="26" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="26"/>
-      <c r="C26" s="143"/>
-      <c r="D26" s="144"/>
-      <c r="E26" s="144"/>
-      <c r="F26" s="144"/>
-      <c r="G26" s="145"/>
+    <row r="26" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="92"/>
+      <c r="C26" s="129"/>
+      <c r="D26" s="130"/>
+      <c r="E26" s="130"/>
+      <c r="F26" s="130"/>
+      <c r="G26" s="131"/>
       <c r="N26" s="16"/>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B27" s="26"/>
-      <c r="C27" s="93"/>
-      <c r="D27" s="93"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="93"/>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B27" s="22"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
       <c r="N27" s="16"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B28" s="9"/>
       <c r="N28" s="16"/>
     </row>
-    <row r="29" spans="2:14" ht="21" x14ac:dyDescent="0.25">
-      <c r="B29" s="21" t="s">
-        <v>73</v>
+    <row r="29" spans="2:14" ht="21" x14ac:dyDescent="0.35">
+      <c r="B29" s="17" t="s">
+        <v>72</v>
       </c>
       <c r="N29" s="16"/>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B30" s="9"/>
       <c r="N30" s="16"/>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B31" s="9"/>
       <c r="N31" s="16"/>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B32" s="9"/>
       <c r="N32" s="16"/>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B33" s="9"/>
       <c r="N33" s="16"/>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B34" s="9"/>
       <c r="N34" s="16"/>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B35" s="9"/>
       <c r="N35" s="16"/>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B36" s="9"/>
       <c r="N36" s="16"/>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B37" s="9"/>
       <c r="N37" s="16"/>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B38" s="9"/>
       <c r="N38" s="16"/>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B39" s="9"/>
       <c r="N39" s="16"/>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B40" s="9"/>
       <c r="N40" s="16"/>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B41" s="9"/>
       <c r="N41" s="16"/>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B42" s="9"/>
       <c r="N42" s="16"/>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B43" s="9"/>
       <c r="N43" s="16"/>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B44" s="9"/>
       <c r="N44" s="16"/>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B45" s="9"/>
       <c r="N45" s="16"/>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B46" s="9"/>
       <c r="N46" s="16"/>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B47" s="9"/>
       <c r="N47" s="16"/>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B48" s="9"/>
       <c r="N48" s="16"/>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B49" s="9"/>
       <c r="N49" s="16"/>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B50" s="9"/>
       <c r="N50" s="16"/>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B51" s="9"/>
       <c r="N51" s="16"/>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B52" s="9"/>
       <c r="N52" s="16"/>
     </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B53" s="9"/>
       <c r="N53" s="16"/>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B54" s="9"/>
       <c r="N54" s="16"/>
     </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B55" s="9"/>
       <c r="N55" s="16"/>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B56" s="9"/>
       <c r="N56" s="16"/>
     </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B57" s="9"/>
       <c r="N57" s="16"/>
     </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B58" s="9"/>
       <c r="N58" s="16"/>
     </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B59" s="9"/>
       <c r="N59" s="16"/>
     </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B60" s="9"/>
       <c r="N60" s="16"/>
     </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B61" s="9"/>
       <c r="N61" s="16"/>
     </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B62" s="9"/>
       <c r="N62" s="16"/>
     </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B63" s="9"/>
       <c r="N63" s="16"/>
     </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B64" s="9"/>
       <c r="N64" s="16"/>
     </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B65" s="9"/>
       <c r="N65" s="16"/>
     </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B66" s="9"/>
       <c r="N66" s="16"/>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B67" s="9"/>
       <c r="N67" s="16"/>
     </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B68" s="9"/>
       <c r="N68" s="16"/>
     </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B69" s="9"/>
       <c r="N69" s="16"/>
     </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B70" s="9"/>
       <c r="N70" s="16"/>
     </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B71" s="9"/>
       <c r="N71" s="16"/>
     </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B72" s="9"/>
       <c r="N72" s="16"/>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N73" s="16"/>
     </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N74" s="16"/>
     </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N75" s="16"/>
     </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:14" x14ac:dyDescent="0.35">
       <c r="N76" s="16"/>
     </row>
-    <row r="77" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F77" s="40"/>
-      <c r="G77" s="40"/>
-      <c r="H77" s="40"/>
+    <row r="77" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F77" s="36"/>
+      <c r="G77" s="36"/>
+      <c r="H77" s="36"/>
       <c r="N77" s="16"/>
     </row>
-    <row r="78" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="82"/>
-      <c r="C78" s="83"/>
-      <c r="D78" s="83"/>
-      <c r="E78" s="83"/>
-      <c r="F78" s="40"/>
-      <c r="G78" s="40"/>
-      <c r="H78" s="40"/>
+    <row r="78" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B78" s="78"/>
+      <c r="C78" s="79"/>
+      <c r="D78" s="79"/>
+      <c r="E78" s="79"/>
+      <c r="F78" s="36"/>
+      <c r="G78" s="36"/>
+      <c r="H78" s="36"/>
       <c r="N78" s="16"/>
     </row>
-    <row r="79" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="82"/>
-      <c r="C79" s="83"/>
-      <c r="D79" s="83"/>
-      <c r="E79" s="83"/>
-      <c r="F79" s="40"/>
-      <c r="G79" s="40"/>
-      <c r="H79" s="40"/>
+    <row r="79" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B79" s="78"/>
+      <c r="C79" s="79"/>
+      <c r="D79" s="79"/>
+      <c r="E79" s="79"/>
+      <c r="F79" s="36"/>
+      <c r="G79" s="36"/>
+      <c r="H79" s="36"/>
       <c r="N79" s="16"/>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B80" s="9"/>
       <c r="C80" s="16"/>
       <c r="D80" s="16"/>
@@ -5716,7 +5680,7 @@
       <c r="G80" s="16"/>
       <c r="N80" s="16"/>
     </row>
-    <row r="81" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B81" s="9"/>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
@@ -5725,12 +5689,12 @@
       <c r="G81" s="10"/>
       <c r="N81" s="16"/>
     </row>
-    <row r="82" spans="2:14" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
       <c r="C82" s="12"/>
-      <c r="D82" s="28"/>
+      <c r="D82" s="24"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="57"/>
+      <c r="G82" s="53"/>
       <c r="H82" s="1"/>
       <c r="I82" s="11"/>
       <c r="J82" s="11"/>
@@ -5738,8 +5702,8 @@
       <c r="L82" s="11"/>
       <c r="N82" s="16"/>
     </row>
-    <row r="85" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C85" s="84"/>
+    <row r="85" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="C85" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -5792,15 +5756,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F6BF0C1AE5C4B149A9D2AD89D2837366" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="40601f7a5fe36372b416c6ecff72cd3c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="c596204b-3c01-4828-83dd-c39c80911371" xmlns:ns3="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="db0ed1a0b0b2b772abce234683c82171" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6072,6 +6027,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
   <ds:schemaRefs>
@@ -6091,14 +6055,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3224E9B-0553-45B7-85AA-2692D0C61765}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6116,4 +6072,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/_templates/DEFAULT WP.xlsx
+++ b/_templates/DEFAULT WP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Colby.Kellersberger\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFEA60D-698E-4B49-8CE9-2561CB68CC57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A812A74E-DEDC-458F-84B2-1F673786082F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4900" yWindow="4900" windowWidth="28800" windowHeight="15360" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26445" yWindow="1080" windowWidth="24465" windowHeight="19665" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions _ Common Tickmarks" sheetId="2" r:id="rId1"/>
@@ -18,10 +18,11 @@
     <sheet name="Detailed Results (2)" sheetId="5" r:id="rId3"/>
     <sheet name="Document Testing WP" sheetId="3" r:id="rId4"/>
     <sheet name="Schedule Testing WP" sheetId="4" r:id="rId5"/>
+    <sheet name="Analytical Procedures WP" sheetId="6" r:id="rId6"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="NoYes">'[1]Drop down'!$Q$6:$Q$7</definedName>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="83">
   <si>
     <t>Tickmark</t>
   </si>
@@ -277,6 +278,27 @@
   </si>
   <si>
     <t>Results:</t>
+  </si>
+  <si>
+    <t>Internal Audit Analytic Procedures - Fuel Contracts Remediation</t>
+  </si>
+  <si>
+    <t>Purpose of Analysis</t>
+  </si>
+  <si>
+    <t>Data Sources</t>
+  </si>
+  <si>
+    <t>Analytical Procedures Performed</t>
+  </si>
+  <si>
+    <t>Evaluation Criteria</t>
+  </si>
+  <si>
+    <t>Results and Audit Interpretation</t>
+  </si>
+  <si>
+    <t>&lt;Title of Data Source tested&gt;</t>
   </si>
 </sst>
 </file>
@@ -286,7 +308,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\-yy;@"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="61" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -720,6 +742,22 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFF68925"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="14"/>
+      <color rgb="FFF68925"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1428,7 +1466,7 @@
     <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1745,11 +1783,90 @@
     <xf numFmtId="0" fontId="50" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="48" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="34" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="34" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="34" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -1777,57 +1894,32 @@
     <xf numFmtId="0" fontId="2" fillId="34" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="34" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="34" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="34" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1847,6 +1939,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1856,86 +1972,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -2063,6 +2114,72 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>203411</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>106743</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{827D63DE-711E-409D-9F68-C858F8CB8BF2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="66675" y="0"/>
+          <a:ext cx="1670261" cy="678243"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2578,15 +2695,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83B0AAC3-C8F9-463F-BDFF-E021531C1393}">
   <dimension ref="B2:H16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.54296875" customWidth="1"/>
-    <col min="6" max="8" width="26.453125" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="6" max="8" width="26.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" ht="23.25" x14ac:dyDescent="0.25">
       <c r="B2" s="59" t="s">
         <v>0</v>
       </c>
@@ -2598,146 +2715,151 @@
       </c>
       <c r="H2" s="16"/>
     </row>
-    <row r="3" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="98" t="s">
+      <c r="C3" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="98"/>
-      <c r="F3" s="97" t="s">
+      <c r="D3" s="103"/>
+      <c r="F3" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="97"/>
-      <c r="H3" s="97"/>
-    </row>
-    <row r="4" spans="2:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G3" s="104"/>
+      <c r="H3" s="104"/>
+    </row>
+    <row r="4" spans="2:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="98" t="s">
+      <c r="C4" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="98"/>
+      <c r="D4" s="103"/>
       <c r="F4" s="55" t="s">
         <v>8</v>
       </c>
       <c r="H4" s="16"/>
     </row>
-    <row r="5" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="98" t="s">
+      <c r="C5" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="98"/>
+      <c r="D5" s="103"/>
       <c r="F5" s="55" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="98" t="s">
+      <c r="C6" s="103" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="98"/>
+      <c r="D6" s="103"/>
       <c r="F6" s="58" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="98" t="s">
+      <c r="C7" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="98"/>
+      <c r="D7" s="103"/>
       <c r="F7" s="54" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="98" t="s">
+      <c r="C8" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="98"/>
-    </row>
-    <row r="9" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D8" s="103"/>
+    </row>
+    <row r="9" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="98" t="s">
+      <c r="C9" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="98"/>
-    </row>
-    <row r="10" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D9" s="103"/>
+    </row>
+    <row r="10" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="98" t="s">
+      <c r="C10" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="98"/>
-    </row>
-    <row r="11" spans="2:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D10" s="103"/>
+    </row>
+    <row r="11" spans="2:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="98" t="s">
+      <c r="C11" s="103" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="98"/>
-    </row>
-    <row r="12" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D11" s="103"/>
+    </row>
+    <row r="12" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="98" t="s">
+      <c r="C12" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="98"/>
-    </row>
-    <row r="13" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D12" s="103"/>
+    </row>
+    <row r="13" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="69"/>
       <c r="C13" s="66"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="98" t="s">
+      <c r="C14" s="103" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="98"/>
-    </row>
-    <row r="15" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D14" s="103"/>
+    </row>
+    <row r="15" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="68"/>
-      <c r="C15" s="98"/>
-      <c r="D15" s="98"/>
-    </row>
-    <row r="16" spans="2:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
+    </row>
+    <row r="16" spans="2:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="98" t="s">
+      <c r="C16" s="103" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="98"/>
+      <c r="D16" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C15:D15"/>
@@ -2747,11 +2869,6 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2761,36 +2878,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:U71"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.54296875" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="18.453125" customWidth="1"/>
-    <col min="4" max="4" width="27.1796875" customWidth="1"/>
-    <col min="5" max="5" width="23.453125" customWidth="1"/>
-    <col min="6" max="6" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.453125" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.453125" customWidth="1"/>
-    <col min="13" max="13" width="13.453125" customWidth="1"/>
-    <col min="14" max="14" width="29.81640625" style="16" customWidth="1"/>
+    <col min="1" max="1" width="1.5703125" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="29.85546875" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
+    <row r="2" spans="2:21" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
     </row>
-    <row r="3" spans="2:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -2802,17 +2919,17 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="100" t="s">
+    <row r="4" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="125" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="101"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="103"/>
-      <c r="I4" s="104"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="128"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="128"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="129"/>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="S4" s="2"/>
@@ -2823,19 +2940,19 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="105" t="s">
+    <row r="5" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="130" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="102" t="s">
+      <c r="C5" s="131"/>
+      <c r="D5" s="127" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="104"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="129"/>
       <c r="J5" s="15"/>
       <c r="K5" s="15"/>
       <c r="S5" s="2"/>
@@ -2844,19 +2961,19 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="107" t="s">
+    <row r="6" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="108"/>
-      <c r="D6" s="140" t="s">
+      <c r="C6" s="106"/>
+      <c r="D6" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="141"/>
-      <c r="F6" s="141"/>
-      <c r="G6" s="141"/>
-      <c r="H6" s="141"/>
-      <c r="I6" s="142"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="123"/>
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
       <c r="S6" s="2"/>
@@ -2865,7 +2982,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="B8" s="36" t="s">
         <v>41</v>
       </c>
@@ -2875,17 +2992,17 @@
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="2:21" s="21" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:21" s="21" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="18" t="s">
         <v>42</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="109" t="s">
+      <c r="D9" s="107" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="109"/>
+      <c r="E9" s="107"/>
       <c r="F9" s="18" t="s">
         <v>45</v>
       </c>
@@ -2894,17 +3011,17 @@
       </c>
       <c r="N9" s="47"/>
     </row>
-    <row r="10" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="65">
         <v>1</v>
       </c>
       <c r="C10" s="34"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
+      <c r="D10" s="108"/>
+      <c r="E10" s="108"/>
       <c r="F10" s="52"/>
       <c r="G10" s="33"/>
     </row>
-    <row r="11" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
@@ -2912,7 +3029,7 @@
       <c r="G11" s="36"/>
       <c r="H11" s="36"/>
     </row>
-    <row r="12" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="B12" s="36" t="s">
         <v>47</v>
       </c>
@@ -2923,7 +3040,7 @@
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
     </row>
-    <row r="13" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B13" s="18" t="s">
         <v>42</v>
       </c>
@@ -2934,96 +3051,96 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B14" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="117"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="118"/>
-      <c r="G14" s="119"/>
+      <c r="C14" s="115"/>
+      <c r="D14" s="116"/>
+      <c r="E14" s="116"/>
+      <c r="F14" s="116"/>
+      <c r="G14" s="117"/>
       <c r="I14" s="22">
         <v>1</v>
       </c>
-      <c r="J14" s="114"/>
-      <c r="K14" s="115"/>
-      <c r="L14" s="116"/>
-    </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="J14" s="112"/>
+      <c r="K14" s="113"/>
+      <c r="L14" s="114"/>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B15" s="22"/>
-      <c r="C15" s="120"/>
-      <c r="D15" s="121"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="121"/>
-      <c r="G15" s="122"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="119"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="120"/>
       <c r="I15" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="J15" s="114"/>
-      <c r="K15" s="115"/>
-      <c r="L15" s="116"/>
-    </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="J15" s="112"/>
+      <c r="K15" s="113"/>
+      <c r="L15" s="114"/>
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B16" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="117"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="118"/>
-      <c r="G16" s="119"/>
+      <c r="C16" s="115"/>
+      <c r="D16" s="116"/>
+      <c r="E16" s="116"/>
+      <c r="F16" s="116"/>
+      <c r="G16" s="117"/>
       <c r="I16" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="J16" s="114"/>
-      <c r="K16" s="115"/>
-      <c r="L16" s="116"/>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="J16" s="112"/>
+      <c r="K16" s="113"/>
+      <c r="L16" s="114"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="23"/>
-      <c r="C17" s="120"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
-      <c r="G17" s="122"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="119"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="120"/>
       <c r="I17" s="22"/>
-      <c r="J17" s="114"/>
-      <c r="K17" s="115"/>
-      <c r="L17" s="116"/>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="J17" s="112"/>
+      <c r="K17" s="113"/>
+      <c r="L17" s="114"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="117"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="118"/>
-      <c r="G18" s="119"/>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="C19" s="120"/>
-      <c r="D19" s="121"/>
-      <c r="E19" s="121"/>
-      <c r="F19" s="121"/>
-      <c r="G19" s="122"/>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C18" s="115"/>
+      <c r="D18" s="116"/>
+      <c r="E18" s="116"/>
+      <c r="F18" s="116"/>
+      <c r="G18" s="117"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C19" s="118"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="120"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C20" s="16"/>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16"/>
     </row>
-    <row r="21" spans="2:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
     </row>
-    <row r="22" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:15" ht="23.25" x14ac:dyDescent="0.25">
       <c r="B22" s="17" t="s">
         <v>52</v>
       </c>
@@ -3040,22 +3157,22 @@
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
     </row>
-    <row r="23" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:15" ht="23.25" x14ac:dyDescent="0.25">
       <c r="B23" s="1"/>
       <c r="C23" s="12"/>
       <c r="D23" s="24"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="53"/>
-      <c r="H23" s="111" t="s">
+      <c r="H23" s="109" t="s">
         <v>53</v>
       </c>
-      <c r="I23" s="112"/>
-      <c r="J23" s="112"/>
-      <c r="K23" s="112"/>
-      <c r="L23" s="113"/>
-    </row>
-    <row r="24" spans="2:15" s="44" customFormat="1" ht="31" x14ac:dyDescent="0.35">
+      <c r="I23" s="110"/>
+      <c r="J23" s="110"/>
+      <c r="K23" s="110"/>
+      <c r="L23" s="111"/>
+    </row>
+    <row r="24" spans="2:15" s="44" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B24" s="18" t="s">
         <v>54</v>
       </c>
@@ -3097,7 +3214,7 @@
       </c>
       <c r="O24" s="20"/>
     </row>
-    <row r="25" spans="2:15" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:15" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B25" s="37">
         <v>1</v>
       </c>
@@ -3126,7 +3243,7 @@
       </c>
       <c r="N25" s="48"/>
     </row>
-    <row r="26" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="37">
         <v>2</v>
       </c>
@@ -3143,7 +3260,7 @@
       <c r="M26" s="26"/>
       <c r="N26" s="48"/>
     </row>
-    <row r="27" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="37">
         <v>3</v>
       </c>
@@ -3160,7 +3277,7 @@
       <c r="M27" s="26"/>
       <c r="N27" s="48"/>
     </row>
-    <row r="28" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="37">
         <v>4</v>
       </c>
@@ -3177,7 +3294,7 @@
       <c r="M28" s="26"/>
       <c r="N28" s="48"/>
     </row>
-    <row r="29" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="37">
         <v>5</v>
       </c>
@@ -3194,7 +3311,7 @@
       <c r="M29" s="26"/>
       <c r="N29" s="48"/>
     </row>
-    <row r="30" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="37">
         <v>6</v>
       </c>
@@ -3211,7 +3328,7 @@
       <c r="M30" s="26"/>
       <c r="N30" s="48"/>
     </row>
-    <row r="31" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="37">
         <v>7</v>
       </c>
@@ -3228,7 +3345,7 @@
       <c r="M31" s="26"/>
       <c r="N31" s="48"/>
     </row>
-    <row r="32" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="37">
         <v>8</v>
       </c>
@@ -3245,7 +3362,7 @@
       <c r="M32" s="26"/>
       <c r="N32" s="48"/>
     </row>
-    <row r="33" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="37">
         <v>9</v>
       </c>
@@ -3262,7 +3379,7 @@
       <c r="M33" s="26"/>
       <c r="N33" s="48"/>
     </row>
-    <row r="34" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="37">
         <v>10</v>
       </c>
@@ -3279,7 +3396,7 @@
       <c r="M34" s="26"/>
       <c r="N34" s="48"/>
     </row>
-    <row r="35" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="37">
         <v>11</v>
       </c>
@@ -3296,7 +3413,7 @@
       <c r="M35" s="26"/>
       <c r="N35" s="48"/>
     </row>
-    <row r="36" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="37">
         <v>12</v>
       </c>
@@ -3313,7 +3430,7 @@
       <c r="M36" s="26"/>
       <c r="N36" s="48"/>
     </row>
-    <row r="37" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="37">
         <v>13</v>
       </c>
@@ -3330,7 +3447,7 @@
       <c r="M37" s="26"/>
       <c r="N37" s="48"/>
     </row>
-    <row r="38" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="37">
         <v>14</v>
       </c>
@@ -3347,7 +3464,7 @@
       <c r="M38" s="26"/>
       <c r="N38" s="48"/>
     </row>
-    <row r="39" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="37">
         <v>15</v>
       </c>
@@ -3364,7 +3481,7 @@
       <c r="M39" s="26"/>
       <c r="N39" s="48"/>
     </row>
-    <row r="40" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="37">
         <v>16</v>
       </c>
@@ -3381,7 +3498,7 @@
       <c r="M40" s="26"/>
       <c r="N40" s="48"/>
     </row>
-    <row r="41" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="37">
         <v>17</v>
       </c>
@@ -3398,7 +3515,7 @@
       <c r="M41" s="26"/>
       <c r="N41" s="48"/>
     </row>
-    <row r="42" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="37">
         <v>18</v>
       </c>
@@ -3415,7 +3532,7 @@
       <c r="M42" s="26"/>
       <c r="N42" s="48"/>
     </row>
-    <row r="43" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B43" s="37">
         <v>19</v>
       </c>
@@ -3432,7 +3549,7 @@
       <c r="M43" s="26"/>
       <c r="N43" s="48"/>
     </row>
-    <row r="44" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="37">
         <v>20</v>
       </c>
@@ -3449,7 +3566,7 @@
       <c r="M44" s="26"/>
       <c r="N44" s="48"/>
     </row>
-    <row r="45" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="37">
         <v>21</v>
       </c>
@@ -3466,7 +3583,7 @@
       <c r="M45" s="26"/>
       <c r="N45" s="48"/>
     </row>
-    <row r="46" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B46" s="37">
         <v>22</v>
       </c>
@@ -3483,7 +3600,7 @@
       <c r="M46" s="26"/>
       <c r="N46" s="48"/>
     </row>
-    <row r="47" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="37">
         <v>23</v>
       </c>
@@ -3500,7 +3617,7 @@
       <c r="M47" s="26"/>
       <c r="N47" s="48"/>
     </row>
-    <row r="48" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="37">
         <v>24</v>
       </c>
@@ -3517,7 +3634,7 @@
       <c r="M48" s="26"/>
       <c r="N48" s="48"/>
     </row>
-    <row r="49" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B49" s="37">
         <v>25</v>
       </c>
@@ -3534,7 +3651,7 @@
       <c r="M49" s="26"/>
       <c r="N49" s="48"/>
     </row>
-    <row r="50" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="37">
         <v>26</v>
       </c>
@@ -3551,7 +3668,7 @@
       <c r="M50" s="26"/>
       <c r="N50" s="48"/>
     </row>
-    <row r="51" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="37">
         <v>27</v>
       </c>
@@ -3568,7 +3685,7 @@
       <c r="M51" s="26"/>
       <c r="N51" s="48"/>
     </row>
-    <row r="52" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="37">
         <v>28</v>
       </c>
@@ -3585,7 +3702,7 @@
       <c r="M52" s="26"/>
       <c r="N52" s="48"/>
     </row>
-    <row r="53" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="37">
         <v>29</v>
       </c>
@@ -3602,7 +3719,7 @@
       <c r="M53" s="26"/>
       <c r="N53" s="48"/>
     </row>
-    <row r="54" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B54" s="37">
         <v>30</v>
       </c>
@@ -3619,7 +3736,7 @@
       <c r="M54" s="26"/>
       <c r="N54" s="48"/>
     </row>
-    <row r="55" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B55" s="37">
         <v>31</v>
       </c>
@@ -3636,7 +3753,7 @@
       <c r="M55" s="26"/>
       <c r="N55" s="48"/>
     </row>
-    <row r="56" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B56" s="37">
         <v>32</v>
       </c>
@@ -3653,7 +3770,7 @@
       <c r="M56" s="26"/>
       <c r="N56" s="48"/>
     </row>
-    <row r="57" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B57" s="37">
         <v>33</v>
       </c>
@@ -3670,7 +3787,7 @@
       <c r="M57" s="26"/>
       <c r="N57" s="48"/>
     </row>
-    <row r="58" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B58" s="37">
         <v>34</v>
       </c>
@@ -3687,7 +3804,7 @@
       <c r="M58" s="26"/>
       <c r="N58" s="48"/>
     </row>
-    <row r="59" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B59" s="37">
         <v>35</v>
       </c>
@@ -3704,7 +3821,7 @@
       <c r="M59" s="26"/>
       <c r="N59" s="48"/>
     </row>
-    <row r="60" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B60" s="37">
         <v>36</v>
       </c>
@@ -3721,7 +3838,7 @@
       <c r="M60" s="26"/>
       <c r="N60" s="48"/>
     </row>
-    <row r="61" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B61" s="37">
         <v>37</v>
       </c>
@@ -3738,7 +3855,7 @@
       <c r="M61" s="26"/>
       <c r="N61" s="45"/>
     </row>
-    <row r="62" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B62" s="37">
         <v>38</v>
       </c>
@@ -3755,7 +3872,7 @@
       <c r="M62" s="26"/>
       <c r="N62" s="48"/>
     </row>
-    <row r="63" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B63" s="37">
         <v>39</v>
       </c>
@@ -3772,7 +3889,7 @@
       <c r="M63" s="26"/>
       <c r="N63" s="48"/>
     </row>
-    <row r="64" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B64" s="37">
         <v>40</v>
       </c>
@@ -3789,7 +3906,7 @@
       <c r="M64" s="26"/>
       <c r="N64" s="48"/>
     </row>
-    <row r="65" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B65" s="37">
         <v>41</v>
       </c>
@@ -3806,7 +3923,7 @@
       <c r="M65" s="26"/>
       <c r="N65" s="48"/>
     </row>
-    <row r="66" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B66" s="37">
         <v>42</v>
       </c>
@@ -3823,7 +3940,7 @@
       <c r="M66" s="26"/>
       <c r="N66" s="48"/>
     </row>
-    <row r="67" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B67" s="37">
         <v>43</v>
       </c>
@@ -3840,7 +3957,7 @@
       <c r="M67" s="26"/>
       <c r="N67" s="48"/>
     </row>
-    <row r="68" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B68" s="37">
         <v>44</v>
       </c>
@@ -3857,7 +3974,7 @@
       <c r="M68" s="26"/>
       <c r="N68" s="48"/>
     </row>
-    <row r="69" spans="2:14" s="3" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:14" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B69" s="37">
         <v>45</v>
       </c>
@@ -3874,7 +3991,7 @@
       <c r="M69" s="26"/>
       <c r="N69" s="48"/>
     </row>
-    <row r="70" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="37"/>
       <c r="C70" s="38"/>
       <c r="D70" s="39"/>
@@ -3889,7 +4006,7 @@
       <c r="M70" s="43"/>
       <c r="N70" s="46"/>
     </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B71" s="4"/>
       <c r="C71" s="5"/>
       <c r="D71" s="5"/>
@@ -3904,6 +4021,11 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:I5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="D10:E10"/>
@@ -3916,11 +4038,6 @@
     <mergeCell ref="C18:G19"/>
     <mergeCell ref="C14:G15"/>
     <mergeCell ref="D6:I6"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:I5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3931,36 +4048,36 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AD103B3-4618-405C-A46A-99E8E6568320}">
   <dimension ref="B2:U67"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.54296875" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="18.453125" customWidth="1"/>
-    <col min="4" max="4" width="27.1796875" customWidth="1"/>
-    <col min="5" max="5" width="23.453125" customWidth="1"/>
-    <col min="6" max="6" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.453125" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.453125" customWidth="1"/>
-    <col min="13" max="13" width="13.453125" customWidth="1"/>
-    <col min="14" max="14" width="29.81640625" style="16" customWidth="1"/>
+    <col min="1" max="1" width="1.5703125" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" style="9" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="29.85546875" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
+    <row r="2" spans="2:21" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
     </row>
-    <row r="3" spans="2:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -3972,17 +4089,17 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="100" t="s">
+    <row r="4" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="125" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="101"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="141"/>
-      <c r="F4" s="141"/>
-      <c r="G4" s="141"/>
-      <c r="H4" s="141"/>
-      <c r="I4" s="142"/>
+      <c r="C4" s="126"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="123"/>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="S4" s="2"/>
@@ -3993,19 +4110,19 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="105" t="s">
+    <row r="5" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="130" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="137" t="s">
+      <c r="C5" s="131"/>
+      <c r="D5" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="138"/>
-      <c r="F5" s="138"/>
-      <c r="G5" s="138"/>
-      <c r="H5" s="138"/>
-      <c r="I5" s="139"/>
+      <c r="E5" s="139"/>
+      <c r="F5" s="139"/>
+      <c r="G5" s="139"/>
+      <c r="H5" s="139"/>
+      <c r="I5" s="140"/>
       <c r="J5" s="15"/>
       <c r="K5" s="15"/>
       <c r="S5" s="2"/>
@@ -4014,19 +4131,19 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="107" t="s">
+    <row r="6" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="108"/>
-      <c r="D6" s="140" t="s">
+      <c r="C6" s="106"/>
+      <c r="D6" s="121" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="141"/>
-      <c r="F6" s="141"/>
-      <c r="G6" s="141"/>
-      <c r="H6" s="141"/>
-      <c r="I6" s="142"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="122"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="123"/>
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
       <c r="S6" s="2"/>
@@ -4035,7 +4152,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="B8" s="36" t="s">
         <v>41</v>
       </c>
@@ -4045,17 +4162,17 @@
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="2:21" s="21" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:21" s="21" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="18" t="s">
         <v>42</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="109" t="s">
+      <c r="D9" s="107" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="109"/>
+      <c r="E9" s="107"/>
       <c r="F9" s="18" t="s">
         <v>45</v>
       </c>
@@ -4064,17 +4181,17 @@
       </c>
       <c r="N9" s="47"/>
     </row>
-    <row r="10" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="95">
         <v>1</v>
       </c>
       <c r="C10" s="34"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
+      <c r="D10" s="108"/>
+      <c r="E10" s="108"/>
       <c r="F10" s="52"/>
       <c r="G10" s="33"/>
     </row>
-    <row r="11" spans="2:21" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:21" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
@@ -4082,14 +4199,14 @@
       <c r="G11" s="36"/>
       <c r="H11" s="36"/>
     </row>
-    <row r="12" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="B12" s="72" t="s">
         <v>53</v>
       </c>
       <c r="G12" s="36"/>
       <c r="H12" s="36"/>
     </row>
-    <row r="13" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="B13" s="73" t="s">
         <v>42</v>
       </c>
@@ -4102,52 +4219,52 @@
       <c r="G13" s="36"/>
       <c r="H13" s="36"/>
     </row>
-    <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="91"/>
-      <c r="C14" s="149"/>
-      <c r="D14" s="143"/>
-      <c r="E14" s="144"/>
-      <c r="F14" s="144"/>
-      <c r="G14" s="148"/>
+      <c r="C14" s="97"/>
+      <c r="D14" s="132"/>
+      <c r="E14" s="133"/>
+      <c r="F14" s="133"/>
+      <c r="G14" s="134"/>
       <c r="H14" s="36"/>
     </row>
-    <row r="15" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="91"/>
-      <c r="C15" s="149"/>
-      <c r="D15" s="143"/>
-      <c r="E15" s="144"/>
-      <c r="F15" s="144"/>
-      <c r="G15" s="148"/>
+      <c r="C15" s="97"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="133"/>
+      <c r="F15" s="133"/>
+      <c r="G15" s="134"/>
       <c r="H15" s="36"/>
     </row>
-    <row r="16" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="91"/>
-      <c r="C16" s="149"/>
-      <c r="D16" s="143"/>
-      <c r="E16" s="144"/>
-      <c r="F16" s="144"/>
-      <c r="G16" s="148"/>
+      <c r="C16" s="97"/>
+      <c r="D16" s="132"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="133"/>
+      <c r="G16" s="134"/>
       <c r="H16" s="36"/>
     </row>
-    <row r="17" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="91"/>
-      <c r="C17" s="149"/>
-      <c r="D17" s="143"/>
-      <c r="E17" s="144"/>
-      <c r="F17" s="144"/>
-      <c r="G17" s="148"/>
+      <c r="C17" s="97"/>
+      <c r="D17" s="132"/>
+      <c r="E17" s="133"/>
+      <c r="F17" s="133"/>
+      <c r="G17" s="134"/>
       <c r="H17" s="36"/>
     </row>
-    <row r="18" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="91"/>
-      <c r="C18" s="149"/>
-      <c r="D18" s="145"/>
-      <c r="E18" s="146"/>
-      <c r="F18" s="146"/>
-      <c r="G18" s="147"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="135"/>
+      <c r="E18" s="136"/>
+      <c r="F18" s="136"/>
+      <c r="G18" s="137"/>
       <c r="H18" s="36"/>
     </row>
-    <row r="19" spans="2:8" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="75"/>
       <c r="C19" s="84"/>
       <c r="D19" s="85"/>
@@ -4156,7 +4273,7 @@
       <c r="G19" s="36"/>
       <c r="H19" s="36"/>
     </row>
-    <row r="20" spans="2:8" ht="21" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:8" ht="21" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
         <v>48</v>
       </c>
@@ -4164,7 +4281,7 @@
       <c r="G20" s="36"/>
       <c r="H20" s="36"/>
     </row>
-    <row r="21" spans="2:8" ht="21" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:8" ht="21" x14ac:dyDescent="0.25">
       <c r="B21" s="76" t="s">
         <v>42</v>
       </c>
@@ -4175,34 +4292,31 @@
       <c r="G21" s="36"/>
       <c r="H21" s="36"/>
     </row>
-    <row r="22" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="90"/>
-      <c r="C22" s="143"/>
-      <c r="D22" s="144"/>
-      <c r="E22" s="144"/>
-      <c r="F22" s="144"/>
-      <c r="G22" s="148"/>
+      <c r="C22" s="132"/>
+      <c r="D22" s="133"/>
+      <c r="E22" s="133"/>
+      <c r="F22" s="134"/>
       <c r="H22" s="36"/>
     </row>
-    <row r="23" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="90"/>
-      <c r="C23" s="143"/>
-      <c r="D23" s="144"/>
-      <c r="E23" s="144"/>
-      <c r="F23" s="144"/>
-      <c r="G23" s="148"/>
+      <c r="C23" s="132"/>
+      <c r="D23" s="133"/>
+      <c r="E23" s="133"/>
+      <c r="F23" s="134"/>
       <c r="H23" s="36"/>
     </row>
-    <row r="24" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="90"/>
-      <c r="C24" s="145"/>
-      <c r="D24" s="146"/>
-      <c r="E24" s="146"/>
-      <c r="F24" s="146"/>
-      <c r="G24" s="147"/>
+      <c r="C24" s="135"/>
+      <c r="D24" s="136"/>
+      <c r="E24" s="136"/>
+      <c r="F24" s="137"/>
       <c r="H24" s="36"/>
     </row>
-    <row r="25" spans="2:8" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="75"/>
       <c r="C25" s="84"/>
       <c r="D25" s="85"/>
@@ -4211,12 +4325,12 @@
       <c r="G25" s="36"/>
       <c r="H25" s="36"/>
     </row>
-    <row r="26" spans="2:8" ht="21" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:8" ht="21" x14ac:dyDescent="0.25">
       <c r="B26" s="36" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B27" s="18" t="s">
         <v>42</v>
       </c>
@@ -4224,75 +4338,75 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="92" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="123"/>
-      <c r="D28" s="124"/>
-      <c r="E28" s="124"/>
-      <c r="F28" s="124"/>
-      <c r="G28" s="125"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C28" s="141"/>
+      <c r="D28" s="142"/>
+      <c r="E28" s="142"/>
+      <c r="F28" s="142"/>
+      <c r="G28" s="143"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="92"/>
-      <c r="C29" s="126"/>
-      <c r="D29" s="127"/>
-      <c r="E29" s="127"/>
-      <c r="F29" s="127"/>
-      <c r="G29" s="128"/>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C29" s="144"/>
+      <c r="D29" s="145"/>
+      <c r="E29" s="145"/>
+      <c r="F29" s="145"/>
+      <c r="G29" s="146"/>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="92" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="123"/>
-      <c r="D30" s="124"/>
-      <c r="E30" s="124"/>
-      <c r="F30" s="124"/>
-      <c r="G30" s="125"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C30" s="141"/>
+      <c r="D30" s="142"/>
+      <c r="E30" s="142"/>
+      <c r="F30" s="142"/>
+      <c r="G30" s="143"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="93"/>
-      <c r="C31" s="126"/>
-      <c r="D31" s="127"/>
-      <c r="E31" s="127"/>
-      <c r="F31" s="127"/>
-      <c r="G31" s="128"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C31" s="144"/>
+      <c r="D31" s="145"/>
+      <c r="E31" s="145"/>
+      <c r="F31" s="145"/>
+      <c r="G31" s="146"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="92" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="123"/>
-      <c r="D32" s="124"/>
-      <c r="E32" s="124"/>
-      <c r="F32" s="124"/>
-      <c r="G32" s="125"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C32" s="141"/>
+      <c r="D32" s="142"/>
+      <c r="E32" s="142"/>
+      <c r="F32" s="142"/>
+      <c r="G32" s="143"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B33" s="94"/>
-      <c r="C33" s="126"/>
-      <c r="D33" s="127"/>
-      <c r="E33" s="127"/>
-      <c r="F33" s="127"/>
-      <c r="G33" s="128"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="C33" s="144"/>
+      <c r="D33" s="145"/>
+      <c r="E33" s="145"/>
+      <c r="F33" s="145"/>
+      <c r="G33" s="146"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C34" s="16"/>
       <c r="D34" s="16"/>
       <c r="E34" s="16"/>
       <c r="F34" s="16"/>
       <c r="G34" s="16"/>
     </row>
-    <row r="35" spans="2:15" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
       <c r="G35" s="10"/>
     </row>
-    <row r="36" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:15" ht="23.25" x14ac:dyDescent="0.25">
       <c r="B36" s="17" t="s">
         <v>52</v>
       </c>
@@ -4307,22 +4421,22 @@
       <c r="K36" s="11"/>
       <c r="L36" s="11"/>
     </row>
-    <row r="37" spans="2:15" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:15" ht="23.25" x14ac:dyDescent="0.25">
       <c r="B37" s="1"/>
       <c r="C37" s="12"/>
       <c r="D37" s="24"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="53"/>
-      <c r="H37" s="111" t="s">
+      <c r="H37" s="109" t="s">
         <v>53</v>
       </c>
-      <c r="I37" s="112"/>
-      <c r="J37" s="112"/>
-      <c r="K37" s="112"/>
-      <c r="L37" s="113"/>
-    </row>
-    <row r="38" spans="2:15" s="44" customFormat="1" ht="31" x14ac:dyDescent="0.35">
+      <c r="I37" s="110"/>
+      <c r="J37" s="110"/>
+      <c r="K37" s="110"/>
+      <c r="L37" s="111"/>
+    </row>
+    <row r="38" spans="2:15" s="44" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B38" s="18" t="s">
         <v>54</v>
       </c>
@@ -4364,7 +4478,7 @@
       </c>
       <c r="O38" s="20"/>
     </row>
-    <row r="39" spans="2:15" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:15" s="3" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B39" s="37">
         <v>1</v>
       </c>
@@ -4393,7 +4507,7 @@
       </c>
       <c r="N39" s="48"/>
     </row>
-    <row r="40" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="37">
         <v>2</v>
       </c>
@@ -4410,7 +4524,7 @@
       <c r="M40" s="26"/>
       <c r="N40" s="48"/>
     </row>
-    <row r="41" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="37">
         <v>3</v>
       </c>
@@ -4427,7 +4541,7 @@
       <c r="M41" s="26"/>
       <c r="N41" s="48"/>
     </row>
-    <row r="42" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="37">
         <v>4</v>
       </c>
@@ -4444,7 +4558,7 @@
       <c r="M42" s="26"/>
       <c r="N42" s="48"/>
     </row>
-    <row r="43" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="37">
         <v>5</v>
       </c>
@@ -4461,7 +4575,7 @@
       <c r="M43" s="26"/>
       <c r="N43" s="48"/>
     </row>
-    <row r="44" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="37">
         <v>6</v>
       </c>
@@ -4478,7 +4592,7 @@
       <c r="M44" s="26"/>
       <c r="N44" s="48"/>
     </row>
-    <row r="45" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="37">
         <v>7</v>
       </c>
@@ -4495,7 +4609,7 @@
       <c r="M45" s="26"/>
       <c r="N45" s="48"/>
     </row>
-    <row r="46" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="37">
         <v>8</v>
       </c>
@@ -4512,7 +4626,7 @@
       <c r="M46" s="26"/>
       <c r="N46" s="48"/>
     </row>
-    <row r="47" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="37">
         <v>9</v>
       </c>
@@ -4529,7 +4643,7 @@
       <c r="M47" s="26"/>
       <c r="N47" s="48"/>
     </row>
-    <row r="48" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="37">
         <v>10</v>
       </c>
@@ -4546,7 +4660,7 @@
       <c r="M48" s="26"/>
       <c r="N48" s="48"/>
     </row>
-    <row r="49" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="37">
         <v>11</v>
       </c>
@@ -4563,7 +4677,7 @@
       <c r="M49" s="26"/>
       <c r="N49" s="48"/>
     </row>
-    <row r="50" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="37">
         <v>12</v>
       </c>
@@ -4580,7 +4694,7 @@
       <c r="M50" s="26"/>
       <c r="N50" s="48"/>
     </row>
-    <row r="51" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="37">
         <v>13</v>
       </c>
@@ -4597,7 +4711,7 @@
       <c r="M51" s="26"/>
       <c r="N51" s="48"/>
     </row>
-    <row r="52" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="37">
         <v>14</v>
       </c>
@@ -4614,7 +4728,7 @@
       <c r="M52" s="26"/>
       <c r="N52" s="48"/>
     </row>
-    <row r="53" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="37">
         <v>15</v>
       </c>
@@ -4631,7 +4745,7 @@
       <c r="M53" s="26"/>
       <c r="N53" s="48"/>
     </row>
-    <row r="54" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="37">
         <v>16</v>
       </c>
@@ -4648,7 +4762,7 @@
       <c r="M54" s="26"/>
       <c r="N54" s="48"/>
     </row>
-    <row r="55" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="37">
         <v>17</v>
       </c>
@@ -4665,7 +4779,7 @@
       <c r="M55" s="26"/>
       <c r="N55" s="48"/>
     </row>
-    <row r="56" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="37">
         <v>18</v>
       </c>
@@ -4682,7 +4796,7 @@
       <c r="M56" s="26"/>
       <c r="N56" s="48"/>
     </row>
-    <row r="57" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="37">
         <v>19</v>
       </c>
@@ -4699,7 +4813,7 @@
       <c r="M57" s="26"/>
       <c r="N57" s="48"/>
     </row>
-    <row r="58" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="37">
         <v>20</v>
       </c>
@@ -4716,7 +4830,7 @@
       <c r="M58" s="26"/>
       <c r="N58" s="48"/>
     </row>
-    <row r="59" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="37">
         <v>21</v>
       </c>
@@ -4733,7 +4847,7 @@
       <c r="M59" s="26"/>
       <c r="N59" s="48"/>
     </row>
-    <row r="60" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="37">
         <v>22</v>
       </c>
@@ -4750,7 +4864,7 @@
       <c r="M60" s="26"/>
       <c r="N60" s="48"/>
     </row>
-    <row r="61" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="37">
         <v>23</v>
       </c>
@@ -4767,7 +4881,7 @@
       <c r="M61" s="26"/>
       <c r="N61" s="48"/>
     </row>
-    <row r="62" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="37">
         <v>24</v>
       </c>
@@ -4784,7 +4898,7 @@
       <c r="M62" s="26"/>
       <c r="N62" s="48"/>
     </row>
-    <row r="63" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="37">
         <v>25</v>
       </c>
@@ -4801,7 +4915,7 @@
       <c r="M63" s="26"/>
       <c r="N63" s="48"/>
     </row>
-    <row r="64" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B64" s="37"/>
       <c r="C64" s="38"/>
       <c r="D64" s="39"/>
@@ -4816,7 +4930,7 @@
       <c r="M64" s="43"/>
       <c r="N64" s="46"/>
     </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B65" s="4"/>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -4829,7 +4943,7 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
       <c r="C67" s="89" t="s">
         <v>75</v>
       </c>
@@ -4843,14 +4957,15 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C32:G33"/>
+    <mergeCell ref="H37:L37"/>
+    <mergeCell ref="C30:G31"/>
+    <mergeCell ref="C28:G29"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:C4"/>
@@ -4858,12 +4973,11 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D5:I5"/>
     <mergeCell ref="D6:I6"/>
-    <mergeCell ref="C32:G33"/>
-    <mergeCell ref="H37:L37"/>
-    <mergeCell ref="C30:G31"/>
-    <mergeCell ref="C28:G29"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D18:G18"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M39:M63" xr:uid="{7EA76EF9-12A3-48C6-BC4E-AF4D09AB486E}">
@@ -4878,41 +4992,41 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27C2776A-E04F-41FD-B3D7-35684437E078}">
   <dimension ref="B1:U31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.54296875" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" customWidth="1"/>
-    <col min="3" max="3" width="23.81640625" customWidth="1"/>
-    <col min="4" max="4" width="27.1796875" customWidth="1"/>
-    <col min="5" max="5" width="23.453125" customWidth="1"/>
-    <col min="6" max="6" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.453125" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.453125" customWidth="1"/>
-    <col min="13" max="13" width="13.453125" customWidth="1"/>
-    <col min="14" max="14" width="17.54296875" customWidth="1"/>
+    <col min="1" max="1" width="1.5703125" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B1" s="9"/>
       <c r="N1" s="16"/>
     </row>
-    <row r="2" spans="2:21" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
+    <row r="2" spans="2:21" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
       <c r="N2" s="16"/>
     </row>
-    <row r="3" spans="2:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -4925,19 +5039,16 @@
       <c r="K3" s="1"/>
       <c r="N3" s="16"/>
     </row>
-    <row r="4" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="132" t="s">
+    <row r="4" spans="2:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="150" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="133"/>
-      <c r="D4" s="134" t="s">
+      <c r="C4" s="151"/>
+      <c r="D4" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="136"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="123"/>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="N4" s="16"/>
@@ -4949,11 +5060,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B5" s="9"/>
       <c r="N5" s="16"/>
     </row>
-    <row r="6" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="B6" s="72" t="s">
         <v>41</v>
       </c>
@@ -4964,17 +5075,17 @@
       <c r="G6" s="7"/>
       <c r="N6" s="16"/>
     </row>
-    <row r="7" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="18" t="s">
         <v>42</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="109" t="s">
+      <c r="D7" s="107" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="109"/>
+      <c r="E7" s="107"/>
       <c r="F7" s="18" t="s">
         <v>45</v>
       </c>
@@ -4983,18 +5094,18 @@
       </c>
       <c r="N7" s="16"/>
     </row>
-    <row r="8" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="95">
         <v>1</v>
       </c>
-      <c r="C8" s="153"/>
-      <c r="D8" s="151"/>
-      <c r="E8" s="152"/>
-      <c r="F8" s="154"/>
-      <c r="G8" s="155"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="147"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="100"/>
       <c r="N8" s="16"/>
     </row>
-    <row r="9" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="65"/>
       <c r="C9" s="81"/>
       <c r="D9" s="43"/>
@@ -5003,13 +5114,13 @@
       <c r="G9" s="83"/>
       <c r="N9" s="16"/>
     </row>
-    <row r="10" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="B10" s="72" t="s">
         <v>53</v>
       </c>
       <c r="N10" s="16"/>
     </row>
-    <row r="11" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="73" t="s">
         <v>42</v>
       </c>
@@ -5021,57 +5132,57 @@
       </c>
       <c r="N11" s="16"/>
     </row>
-    <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="156"/>
+    <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="101"/>
       <c r="C12" s="96"/>
-      <c r="D12" s="145"/>
-      <c r="E12" s="146"/>
-      <c r="F12" s="147"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="137"/>
       <c r="N12" s="16"/>
     </row>
-    <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="156"/>
+    <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="101"/>
       <c r="C13" s="96"/>
-      <c r="D13" s="145"/>
-      <c r="E13" s="146"/>
-      <c r="F13" s="147"/>
+      <c r="D13" s="135"/>
+      <c r="E13" s="136"/>
+      <c r="F13" s="137"/>
       <c r="N13" s="16"/>
     </row>
-    <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="156"/>
+    <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="101"/>
       <c r="C14" s="96"/>
-      <c r="D14" s="145"/>
-      <c r="E14" s="146"/>
-      <c r="F14" s="147"/>
+      <c r="D14" s="135"/>
+      <c r="E14" s="136"/>
+      <c r="F14" s="137"/>
       <c r="N14" s="16"/>
     </row>
-    <row r="15" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="156"/>
+    <row r="15" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="101"/>
       <c r="C15" s="96"/>
-      <c r="D15" s="145"/>
-      <c r="E15" s="146"/>
-      <c r="F15" s="147"/>
+      <c r="D15" s="135"/>
+      <c r="E15" s="136"/>
+      <c r="F15" s="137"/>
       <c r="N15" s="16"/>
     </row>
-    <row r="16" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="156"/>
+    <row r="16" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="101"/>
       <c r="C16" s="96"/>
-      <c r="D16" s="145"/>
-      <c r="E16" s="146"/>
-      <c r="F16" s="147"/>
+      <c r="D16" s="135"/>
+      <c r="E16" s="136"/>
+      <c r="F16" s="137"/>
       <c r="N16" s="16"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="9"/>
       <c r="N17" s="16"/>
     </row>
-    <row r="18" spans="2:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:14" ht="21" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
         <v>48</v>
       </c>
       <c r="N18" s="16"/>
     </row>
-    <row r="19" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B19" s="76" t="s">
         <v>42</v>
       </c>
@@ -5080,31 +5191,31 @@
       </c>
       <c r="N19" s="16"/>
     </row>
-    <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="157"/>
-      <c r="C20" s="145"/>
-      <c r="D20" s="146"/>
-      <c r="E20" s="147"/>
+    <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="102"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="136"/>
+      <c r="E20" s="137"/>
       <c r="N20" s="16"/>
     </row>
-    <row r="21" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="157"/>
-      <c r="C21" s="145"/>
-      <c r="D21" s="146"/>
-      <c r="E21" s="147"/>
+    <row r="21" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="102"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="136"/>
+      <c r="E21" s="137"/>
       <c r="N21" s="16"/>
     </row>
-    <row r="22" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="157"/>
-      <c r="C22" s="145"/>
-      <c r="D22" s="146"/>
-      <c r="E22" s="147"/>
+    <row r="22" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="102"/>
+      <c r="C22" s="135"/>
+      <c r="D22" s="136"/>
+      <c r="E22" s="137"/>
       <c r="F22" s="36"/>
       <c r="G22" s="36"/>
       <c r="H22" s="36"/>
       <c r="N22" s="16"/>
     </row>
-    <row r="23" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="78"/>
       <c r="C23" s="79"/>
       <c r="D23" s="79"/>
@@ -5114,14 +5225,14 @@
       <c r="H23" s="36"/>
       <c r="N23" s="16"/>
     </row>
-    <row r="24" spans="2:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:14" ht="21" x14ac:dyDescent="0.25">
       <c r="B24" s="72" t="s">
         <v>47</v>
       </c>
       <c r="C24" s="72"/>
       <c r="N24" s="16"/>
     </row>
-    <row r="25" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="s">
         <v>42</v>
       </c>
@@ -5130,16 +5241,16 @@
       </c>
       <c r="N25" s="16"/>
     </row>
-    <row r="26" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="92"/>
-      <c r="C26" s="151"/>
-      <c r="D26" s="150"/>
-      <c r="E26" s="150"/>
-      <c r="F26" s="150"/>
-      <c r="G26" s="152"/>
+      <c r="C26" s="147"/>
+      <c r="D26" s="149"/>
+      <c r="E26" s="149"/>
+      <c r="F26" s="149"/>
+      <c r="G26" s="148"/>
       <c r="N26" s="16"/>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="22"/>
       <c r="C27" s="88"/>
       <c r="D27" s="88"/>
@@ -5148,7 +5259,7 @@
       <c r="G27" s="88"/>
       <c r="N27" s="16"/>
     </row>
-    <row r="28" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:14" ht="23.25" x14ac:dyDescent="0.25">
       <c r="B28" s="17" t="s">
         <v>71</v>
       </c>
@@ -5164,7 +5275,7 @@
       <c r="L28" s="11"/>
       <c r="N28" s="16"/>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C31" s="80"/>
     </row>
   </sheetData>
@@ -5174,7 +5285,6 @@
     <mergeCell ref="C26:G26"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:I4"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D14:F14"/>
@@ -5183,6 +5293,7 @@
     <mergeCell ref="C22:E22"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D4:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5192,41 +5303,41 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D90A4130-68CA-4E30-9267-87839E021ADD}">
   <dimension ref="B1:U85"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.54296875" customWidth="1"/>
-    <col min="2" max="2" width="6.453125" customWidth="1"/>
-    <col min="3" max="3" width="24.1796875" customWidth="1"/>
-    <col min="4" max="4" width="27.1796875" customWidth="1"/>
-    <col min="5" max="5" width="23.453125" customWidth="1"/>
-    <col min="6" max="6" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.453125" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.453125" customWidth="1"/>
-    <col min="13" max="13" width="13.453125" customWidth="1"/>
-    <col min="14" max="14" width="14.453125" customWidth="1"/>
+    <col min="1" max="1" width="1.5703125" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" customWidth="1"/>
+    <col min="4" max="4" width="27.140625" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B1" s="9"/>
       <c r="N1" s="16"/>
     </row>
-    <row r="2" spans="2:21" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
+    <row r="2" spans="2:21" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
       <c r="N2" s="16"/>
     </row>
-    <row r="3" spans="2:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:21" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -5239,19 +5350,19 @@
       <c r="K3" s="1"/>
       <c r="N3" s="16"/>
     </row>
-    <row r="4" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="132" t="s">
+    <row r="4" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="150" t="s">
         <v>67</v>
       </c>
       <c r="C4" s="158"/>
-      <c r="D4" s="134" t="s">
+      <c r="D4" s="152" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="135"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="135"/>
-      <c r="H4" s="135"/>
-      <c r="I4" s="136"/>
+      <c r="E4" s="153"/>
+      <c r="F4" s="153"/>
+      <c r="G4" s="153"/>
+      <c r="H4" s="153"/>
+      <c r="I4" s="154"/>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="N4" s="16"/>
@@ -5263,11 +5374,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B5" s="9"/>
       <c r="N5" s="16"/>
     </row>
-    <row r="6" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="B6" s="72" t="s">
         <v>41</v>
       </c>
@@ -5278,17 +5389,17 @@
       <c r="G6" s="7"/>
       <c r="N6" s="16"/>
     </row>
-    <row r="7" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="18" t="s">
         <v>42</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="109" t="s">
+      <c r="D7" s="107" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="109"/>
+      <c r="E7" s="107"/>
       <c r="F7" s="18" t="s">
         <v>45</v>
       </c>
@@ -5297,28 +5408,28 @@
       </c>
       <c r="N7" s="16"/>
     </row>
-    <row r="8" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="95">
         <v>1</v>
       </c>
-      <c r="C8" s="153"/>
-      <c r="D8" s="151"/>
-      <c r="E8" s="152"/>
-      <c r="F8" s="154"/>
-      <c r="G8" s="155"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="147"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="100"/>
       <c r="N8" s="16"/>
     </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B9" s="9"/>
       <c r="N9" s="16"/>
     </row>
-    <row r="10" spans="2:21" ht="21" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="B10" s="72" t="s">
         <v>53</v>
       </c>
       <c r="N10" s="16"/>
     </row>
-    <row r="11" spans="2:21" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="73" t="s">
         <v>42</v>
       </c>
@@ -5330,60 +5441,60 @@
       </c>
       <c r="N11" s="16"/>
     </row>
-    <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="156"/>
+    <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="101"/>
       <c r="C12" s="96"/>
-      <c r="D12" s="145"/>
-      <c r="E12" s="146"/>
-      <c r="F12" s="147"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="137"/>
       <c r="N12" s="16"/>
     </row>
-    <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="156"/>
+    <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="101"/>
       <c r="C13" s="96"/>
-      <c r="D13" s="145"/>
-      <c r="E13" s="146"/>
-      <c r="F13" s="147"/>
+      <c r="D13" s="135"/>
+      <c r="E13" s="136"/>
+      <c r="F13" s="137"/>
       <c r="N13" s="16"/>
     </row>
-    <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="156"/>
+    <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="101"/>
       <c r="C14" s="96"/>
-      <c r="D14" s="145"/>
-      <c r="E14" s="146"/>
-      <c r="F14" s="147"/>
+      <c r="D14" s="135"/>
+      <c r="E14" s="136"/>
+      <c r="F14" s="137"/>
       <c r="N14" s="16"/>
     </row>
-    <row r="15" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="156"/>
+    <row r="15" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="101"/>
       <c r="C15" s="96"/>
-      <c r="D15" s="145"/>
-      <c r="E15" s="146"/>
-      <c r="F15" s="147"/>
+      <c r="D15" s="135"/>
+      <c r="E15" s="136"/>
+      <c r="F15" s="137"/>
       <c r="N15" s="16"/>
     </row>
-    <row r="16" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="156"/>
+    <row r="16" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="101"/>
       <c r="C16" s="96"/>
-      <c r="D16" s="145"/>
-      <c r="E16" s="146"/>
-      <c r="F16" s="147"/>
+      <c r="D16" s="135"/>
+      <c r="E16" s="136"/>
+      <c r="F16" s="137"/>
       <c r="N16" s="16"/>
     </row>
-    <row r="17" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B17" s="75"/>
       <c r="C17" s="79"/>
       <c r="D17" s="79"/>
       <c r="E17" s="79"/>
       <c r="N17" s="16"/>
     </row>
-    <row r="18" spans="2:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:14" ht="21" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
         <v>48</v>
       </c>
       <c r="N18" s="16"/>
     </row>
-    <row r="19" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B19" s="76" t="s">
         <v>42</v>
       </c>
@@ -5392,39 +5503,39 @@
       </c>
       <c r="N19" s="16"/>
     </row>
-    <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="157"/>
-      <c r="C20" s="145"/>
-      <c r="D20" s="146"/>
-      <c r="E20" s="147"/>
+    <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="102"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="136"/>
+      <c r="E20" s="137"/>
       <c r="N20" s="16"/>
     </row>
-    <row r="21" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="157"/>
-      <c r="C21" s="145"/>
-      <c r="D21" s="146"/>
-      <c r="E21" s="147"/>
+    <row r="21" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="102"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="136"/>
+      <c r="E21" s="137"/>
       <c r="N21" s="16"/>
     </row>
-    <row r="22" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="157"/>
-      <c r="C22" s="145"/>
-      <c r="D22" s="146"/>
-      <c r="E22" s="147"/>
+    <row r="22" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="102"/>
+      <c r="C22" s="135"/>
+      <c r="D22" s="136"/>
+      <c r="E22" s="137"/>
       <c r="N22" s="16"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="9"/>
       <c r="N23" s="16"/>
     </row>
-    <row r="24" spans="2:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:14" ht="21" x14ac:dyDescent="0.25">
       <c r="B24" s="72" t="s">
         <v>47</v>
       </c>
       <c r="C24" s="72"/>
       <c r="N24" s="16"/>
     </row>
-    <row r="25" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B25" s="18" t="s">
         <v>42</v>
       </c>
@@ -5433,16 +5544,16 @@
       </c>
       <c r="N25" s="16"/>
     </row>
-    <row r="26" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="92"/>
-      <c r="C26" s="129"/>
-      <c r="D26" s="130"/>
-      <c r="E26" s="130"/>
-      <c r="F26" s="130"/>
-      <c r="G26" s="131"/>
+      <c r="C26" s="155"/>
+      <c r="D26" s="156"/>
+      <c r="E26" s="156"/>
+      <c r="F26" s="156"/>
+      <c r="G26" s="157"/>
       <c r="N26" s="16"/>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="22"/>
       <c r="C27" s="88"/>
       <c r="D27" s="88"/>
@@ -5451,207 +5562,207 @@
       <c r="G27" s="88"/>
       <c r="N27" s="16"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="9"/>
       <c r="N28" s="16"/>
     </row>
-    <row r="29" spans="2:14" ht="21" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:14" ht="21" x14ac:dyDescent="0.25">
       <c r="B29" s="17" t="s">
         <v>72</v>
       </c>
       <c r="N29" s="16"/>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="9"/>
       <c r="N30" s="16"/>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="9"/>
       <c r="N31" s="16"/>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B32" s="9"/>
       <c r="N32" s="16"/>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" s="9"/>
       <c r="N33" s="16"/>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B34" s="9"/>
       <c r="N34" s="16"/>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B35" s="9"/>
       <c r="N35" s="16"/>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B36" s="9"/>
       <c r="N36" s="16"/>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B37" s="9"/>
       <c r="N37" s="16"/>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B38" s="9"/>
       <c r="N38" s="16"/>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B39" s="9"/>
       <c r="N39" s="16"/>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B40" s="9"/>
       <c r="N40" s="16"/>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B41" s="9"/>
       <c r="N41" s="16"/>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B42" s="9"/>
       <c r="N42" s="16"/>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B43" s="9"/>
       <c r="N43" s="16"/>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B44" s="9"/>
       <c r="N44" s="16"/>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B45" s="9"/>
       <c r="N45" s="16"/>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B46" s="9"/>
       <c r="N46" s="16"/>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B47" s="9"/>
       <c r="N47" s="16"/>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B48" s="9"/>
       <c r="N48" s="16"/>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B49" s="9"/>
       <c r="N49" s="16"/>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B50" s="9"/>
       <c r="N50" s="16"/>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B51" s="9"/>
       <c r="N51" s="16"/>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B52" s="9"/>
       <c r="N52" s="16"/>
     </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B53" s="9"/>
       <c r="N53" s="16"/>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B54" s="9"/>
       <c r="N54" s="16"/>
     </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B55" s="9"/>
       <c r="N55" s="16"/>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B56" s="9"/>
       <c r="N56" s="16"/>
     </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B57" s="9"/>
       <c r="N57" s="16"/>
     </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B58" s="9"/>
       <c r="N58" s="16"/>
     </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B59" s="9"/>
       <c r="N59" s="16"/>
     </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B60" s="9"/>
       <c r="N60" s="16"/>
     </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B61" s="9"/>
       <c r="N61" s="16"/>
     </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B62" s="9"/>
       <c r="N62" s="16"/>
     </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B63" s="9"/>
       <c r="N63" s="16"/>
     </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B64" s="9"/>
       <c r="N64" s="16"/>
     </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B65" s="9"/>
       <c r="N65" s="16"/>
     </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B66" s="9"/>
       <c r="N66" s="16"/>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B67" s="9"/>
       <c r="N67" s="16"/>
     </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B68" s="9"/>
       <c r="N68" s="16"/>
     </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B69" s="9"/>
       <c r="N69" s="16"/>
     </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B70" s="9"/>
       <c r="N70" s="16"/>
     </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B71" s="9"/>
       <c r="N71" s="16"/>
     </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B72" s="9"/>
       <c r="N72" s="16"/>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N73" s="16"/>
     </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N74" s="16"/>
     </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N75" s="16"/>
     </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:14" x14ac:dyDescent="0.25">
       <c r="N76" s="16"/>
     </row>
-    <row r="77" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F77" s="36"/>
       <c r="G77" s="36"/>
       <c r="H77" s="36"/>
       <c r="N77" s="16"/>
     </row>
-    <row r="78" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="78"/>
       <c r="C78" s="79"/>
       <c r="D78" s="79"/>
@@ -5661,7 +5772,7 @@
       <c r="H78" s="36"/>
       <c r="N78" s="16"/>
     </row>
-    <row r="79" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="78"/>
       <c r="C79" s="79"/>
       <c r="D79" s="79"/>
@@ -5671,7 +5782,7 @@
       <c r="H79" s="36"/>
       <c r="N79" s="16"/>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B80" s="9"/>
       <c r="C80" s="16"/>
       <c r="D80" s="16"/>
@@ -5680,7 +5791,7 @@
       <c r="G80" s="16"/>
       <c r="N80" s="16"/>
     </row>
-    <row r="81" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="9"/>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
@@ -5689,7 +5800,7 @@
       <c r="G81" s="10"/>
       <c r="N81" s="16"/>
     </row>
-    <row r="82" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:14" ht="23.25" x14ac:dyDescent="0.25">
       <c r="C82" s="12"/>
       <c r="D82" s="24"/>
       <c r="E82" s="1"/>
@@ -5702,7 +5813,7 @@
       <c r="L82" s="11"/>
       <c r="N82" s="16"/>
     </row>
-    <row r="85" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C85" s="80"/>
     </row>
   </sheetData>
@@ -5727,32 +5838,214 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEACF759-6B24-41AC-859A-CF8770670DE1}">
+  <dimension ref="B5:K29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="150" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="151"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="122"/>
+      <c r="I5" s="122"/>
+      <c r="J5" s="123"/>
+    </row>
+    <row r="7" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+      <c r="B7" s="159" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B8" s="160" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="147"/>
+      <c r="C9" s="149"/>
+      <c r="D9" s="149"/>
+      <c r="E9" s="149"/>
+      <c r="F9" s="149"/>
+      <c r="G9" s="149"/>
+      <c r="H9" s="149"/>
+      <c r="I9" s="149"/>
+      <c r="J9" s="149"/>
+      <c r="K9" s="148"/>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+    </row>
+    <row r="11" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B11" s="160" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="147"/>
+      <c r="C12" s="149"/>
+      <c r="D12" s="149"/>
+      <c r="E12" s="149"/>
+      <c r="F12" s="149"/>
+      <c r="G12" s="149"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="149"/>
+      <c r="J12" s="149"/>
+      <c r="K12" s="148"/>
+    </row>
+    <row r="14" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B14" s="160" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="147"/>
+      <c r="C15" s="149"/>
+      <c r="D15" s="149"/>
+      <c r="E15" s="149"/>
+      <c r="F15" s="149"/>
+      <c r="G15" s="149"/>
+      <c r="H15" s="149"/>
+      <c r="I15" s="149"/>
+      <c r="J15" s="149"/>
+      <c r="K15" s="148"/>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B16" s="88"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="88"/>
+    </row>
+    <row r="17" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="161" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="88"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88"/>
+    </row>
+    <row r="18" spans="2:11" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="147"/>
+      <c r="C18" s="149"/>
+      <c r="D18" s="149"/>
+      <c r="E18" s="149"/>
+      <c r="F18" s="149"/>
+      <c r="G18" s="149"/>
+      <c r="H18" s="149"/>
+      <c r="I18" s="149"/>
+      <c r="J18" s="149"/>
+      <c r="K18" s="148"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+    </row>
+    <row r="20" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="162" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+    </row>
+    <row r="21" spans="2:11" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="147"/>
+      <c r="C21" s="149"/>
+      <c r="D21" s="149"/>
+      <c r="E21" s="149"/>
+      <c r="F21" s="149"/>
+      <c r="G21" s="149"/>
+      <c r="H21" s="149"/>
+      <c r="I21" s="149"/>
+      <c r="J21" s="149"/>
+      <c r="K21" s="148"/>
+    </row>
+    <row r="23" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+      <c r="B23" s="72" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="76" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="77" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B25" s="163"/>
+      <c r="C25" s="132"/>
+      <c r="D25" s="133"/>
+      <c r="E25" s="133"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="133"/>
+      <c r="H25" s="134"/>
+    </row>
+    <row r="26" spans="2:11" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B26" s="163"/>
+      <c r="C26" s="132"/>
+      <c r="D26" s="133"/>
+      <c r="E26" s="133"/>
+      <c r="F26" s="133"/>
+      <c r="G26" s="133"/>
+      <c r="H26" s="134"/>
+    </row>
+    <row r="27" spans="2:11" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B27" s="163"/>
+      <c r="C27" s="135"/>
+      <c r="D27" s="136"/>
+      <c r="E27" s="136"/>
+      <c r="F27" s="136"/>
+      <c r="G27" s="136"/>
+      <c r="H27" s="137"/>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B28" s="9"/>
+    </row>
+    <row r="29" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+      <c r="B29" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="B9:K9"/>
+    <mergeCell ref="B12:K12"/>
+    <mergeCell ref="B15:K15"/>
+    <mergeCell ref="B18:K18"/>
+    <mergeCell ref="B21:K21"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:J5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c596204b-3c01-4828-83dd-c39c80911371" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Owner xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <MediaLengthInSeconds xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" xsi:nil="true"/>
-    <SharedWithUsers xmlns="c596204b-3c01-4828-83dd-c39c80911371">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6028,28 +6321,37 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c596204b-3c01-4828-83dd-c39c80911371" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Owner xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <MediaLengthInSeconds xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" xsi:nil="true"/>
+    <SharedWithUsers xmlns="c596204b-3c01-4828-83dd-c39c80911371">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="c596204b-3c01-4828-83dd-c39c80911371"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6075,9 +6377,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="c596204b-3c01-4828-83dd-c39c80911371"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/_templates/DEFAULT WP.xlsx
+++ b/_templates/DEFAULT WP.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Colby.Kellersberger\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A812A74E-DEDC-458F-84B2-1F673786082F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01168CA5-0627-4E18-A088-DEA7ECB0E2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26445" yWindow="1080" windowWidth="24465" windowHeight="19665" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24690" yWindow="2820" windowWidth="24165" windowHeight="16260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions _ Common Tickmarks" sheetId="2" r:id="rId1"/>
     <sheet name="Detailed Results" sheetId="1" r:id="rId2"/>
-    <sheet name="Detailed Results (2)" sheetId="5" r:id="rId3"/>
-    <sheet name="Document Testing WP" sheetId="3" r:id="rId4"/>
-    <sheet name="Schedule Testing WP" sheetId="4" r:id="rId5"/>
-    <sheet name="Analytical Procedures WP" sheetId="6" r:id="rId6"/>
+    <sheet name="Detailed Results 2" sheetId="7" r:id="rId3"/>
+    <sheet name="Document Testing WP" sheetId="8" r:id="rId4"/>
+    <sheet name="Schedule Testing WP" sheetId="9" r:id="rId5"/>
+    <sheet name="Analytical Procedures WP" sheetId="10" r:id="rId6"/>
+    <sheet name="Planning Document" sheetId="11" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <definedNames>
     <definedName name="NoYes">'[1]Drop down'!$Q$6:$Q$7</definedName>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="93">
   <si>
     <t>Tickmark</t>
   </si>
@@ -271,18 +272,9 @@
     <t>Schedule Testing</t>
   </si>
   <si>
-    <t>✔</t>
-  </si>
-  <si>
     <t>✘</t>
   </si>
   <si>
-    <t>Results:</t>
-  </si>
-  <si>
-    <t>Internal Audit Analytic Procedures - Fuel Contracts Remediation</t>
-  </si>
-  <si>
     <t>Purpose of Analysis</t>
   </si>
   <si>
@@ -299,6 +291,45 @@
   </si>
   <si>
     <t>&lt;Title of Data Source tested&gt;</t>
+  </si>
+  <si>
+    <t>Sample Size</t>
+  </si>
+  <si>
+    <t></t>
+  </si>
+  <si>
+    <t>Count of Tick Marks</t>
+  </si>
+  <si>
+    <t>T/M Ref</t>
+  </si>
+  <si>
+    <t>Internal Audit Analytic Procedures — &lt;Testing Name&gt;</t>
+  </si>
+  <si>
+    <t>Audit Name</t>
+  </si>
+  <si>
+    <t>&lt;Name of Audit&gt;</t>
+  </si>
+  <si>
+    <t>Background</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Initial Risk Assessment</t>
+  </si>
+  <si>
+    <t>Risk ID</t>
+  </si>
+  <si>
+    <t>Risk Theme</t>
+  </si>
+  <si>
+    <t>Risk Statement</t>
   </si>
 </sst>
 </file>
@@ -308,7 +339,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\-yy;@"/>
   </numFmts>
-  <fonts count="61" x14ac:knownFonts="1">
+  <fonts count="62" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -762,6 +793,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="37">
     <fill>
@@ -968,7 +1006,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -1358,19 +1396,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF15488B"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF0080C0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF0080C0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -1395,28 +1420,211 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF0080C0"/>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
       </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF0080BF"/>
+      </left>
+      <right/>
       <top style="thin">
-        <color rgb="FF0080C0"/>
+        <color rgb="FF0080BF"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF0080C0"/>
+        <color rgb="FF0080BF"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color rgb="FF15488B"/>
+        <color rgb="FF0080BF"/>
       </right>
       <top style="thin">
-        <color rgb="FF0080C0"/>
+        <color rgb="FF0080BF"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF0080C0"/>
+        <color rgb="FF0080BF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF0080BF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF0080BF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="hair">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="hair">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="hair">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1466,7 +1674,7 @@
     <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="181">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1761,9 +1969,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1780,34 +1985,63 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -1869,30 +2103,23 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1921,24 +2148,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1948,45 +2157,94 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="34" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="34" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -2114,72 +2372,6 @@
         </a:fontRef>
       </xdr:style>
     </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>203411</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>106743</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{827D63DE-711E-409D-9F68-C858F8CB8BF2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="66675" y="0"/>
-          <a:ext cx="1670261" cy="678243"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2719,10 +2911,10 @@
       <c r="B3" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="103" t="s">
+      <c r="C3" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="103"/>
+      <c r="D3" s="105"/>
       <c r="F3" s="104" t="s">
         <v>5</v>
       </c>
@@ -2733,10 +2925,10 @@
       <c r="B4" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="103" t="s">
+      <c r="C4" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="103"/>
+      <c r="D4" s="105"/>
       <c r="F4" s="55" t="s">
         <v>8</v>
       </c>
@@ -2746,10 +2938,10 @@
       <c r="B5" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="103" t="s">
+      <c r="C5" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="103"/>
+      <c r="D5" s="105"/>
       <c r="F5" s="55" t="s">
         <v>11</v>
       </c>
@@ -2759,10 +2951,10 @@
       <c r="B6" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="103" t="s">
+      <c r="C6" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="103"/>
+      <c r="D6" s="105"/>
       <c r="F6" s="58" t="s">
         <v>14</v>
       </c>
@@ -2772,10 +2964,10 @@
       <c r="B7" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="103" t="s">
+      <c r="C7" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="103"/>
+      <c r="D7" s="105"/>
       <c r="F7" s="54" t="s">
         <v>17</v>
       </c>
@@ -2785,46 +2977,46 @@
       <c r="B8" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="103" t="s">
+      <c r="C8" s="105" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="103"/>
+      <c r="D8" s="105"/>
     </row>
     <row r="9" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="103" t="s">
+      <c r="C9" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="103"/>
+      <c r="D9" s="105"/>
     </row>
     <row r="10" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="103" t="s">
+      <c r="C10" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="103"/>
+      <c r="D10" s="105"/>
     </row>
     <row r="11" spans="2:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="103" t="s">
+      <c r="C11" s="105" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="103"/>
+      <c r="D11" s="105"/>
     </row>
     <row r="12" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="103" t="s">
+      <c r="C12" s="105" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="103"/>
+      <c r="D12" s="105"/>
     </row>
     <row r="13" spans="2:8" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="69"/>
@@ -2834,32 +3026,27 @@
       <c r="B14" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="103" t="s">
+      <c r="C14" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="103"/>
+      <c r="D14" s="105"/>
     </row>
     <row r="15" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="68"/>
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="105"/>
     </row>
     <row r="16" spans="2:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="103" t="s">
+      <c r="C16" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="103"/>
+      <c r="D16" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C15:D15"/>
@@ -2869,6 +3056,11 @@
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C6:D6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2895,14 +3087,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:21" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
@@ -2920,16 +3112,16 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="125" t="s">
+      <c r="B4" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="126"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="128"/>
-      <c r="F4" s="128"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="128"/>
-      <c r="I4" s="129"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="111"/>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="S4" s="2"/>
@@ -2941,18 +3133,18 @@
       </c>
     </row>
     <row r="5" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="130" t="s">
+      <c r="B5" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="131"/>
-      <c r="D5" s="127" t="s">
+      <c r="C5" s="113"/>
+      <c r="D5" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="128"/>
-      <c r="F5" s="128"/>
-      <c r="G5" s="128"/>
-      <c r="H5" s="128"/>
-      <c r="I5" s="129"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="111"/>
       <c r="J5" s="15"/>
       <c r="K5" s="15"/>
       <c r="S5" s="2"/>
@@ -2962,18 +3154,18 @@
       </c>
     </row>
     <row r="6" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="105" t="s">
+      <c r="B6" s="114" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="106"/>
-      <c r="D6" s="121" t="s">
+      <c r="C6" s="115"/>
+      <c r="D6" s="130" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="123"/>
+      <c r="E6" s="131"/>
+      <c r="F6" s="131"/>
+      <c r="G6" s="131"/>
+      <c r="H6" s="131"/>
+      <c r="I6" s="132"/>
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
       <c r="S6" s="2"/>
@@ -2999,10 +3191,10 @@
       <c r="C9" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="107" t="s">
+      <c r="D9" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="107"/>
+      <c r="E9" s="116"/>
       <c r="F9" s="18" t="s">
         <v>45</v>
       </c>
@@ -3016,8 +3208,8 @@
         <v>1</v>
       </c>
       <c r="C10" s="34"/>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108"/>
+      <c r="D10" s="117"/>
+      <c r="E10" s="117"/>
       <c r="F10" s="52"/>
       <c r="G10" s="33"/>
     </row>
@@ -3055,76 +3247,76 @@
       <c r="B14" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="115"/>
-      <c r="D14" s="116"/>
-      <c r="E14" s="116"/>
-      <c r="F14" s="116"/>
-      <c r="G14" s="117"/>
+      <c r="C14" s="124"/>
+      <c r="D14" s="125"/>
+      <c r="E14" s="125"/>
+      <c r="F14" s="125"/>
+      <c r="G14" s="126"/>
       <c r="I14" s="22">
         <v>1</v>
       </c>
-      <c r="J14" s="112"/>
-      <c r="K14" s="113"/>
-      <c r="L14" s="114"/>
+      <c r="J14" s="121"/>
+      <c r="K14" s="122"/>
+      <c r="L14" s="123"/>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B15" s="22"/>
-      <c r="C15" s="118"/>
-      <c r="D15" s="119"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="120"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="128"/>
+      <c r="E15" s="128"/>
+      <c r="F15" s="128"/>
+      <c r="G15" s="129"/>
       <c r="I15" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="J15" s="112"/>
-      <c r="K15" s="113"/>
-      <c r="L15" s="114"/>
+      <c r="J15" s="121"/>
+      <c r="K15" s="122"/>
+      <c r="L15" s="123"/>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B16" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="115"/>
-      <c r="D16" s="116"/>
-      <c r="E16" s="116"/>
-      <c r="F16" s="116"/>
-      <c r="G16" s="117"/>
+      <c r="C16" s="124"/>
+      <c r="D16" s="125"/>
+      <c r="E16" s="125"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="126"/>
       <c r="I16" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="J16" s="112"/>
-      <c r="K16" s="113"/>
-      <c r="L16" s="114"/>
+      <c r="J16" s="121"/>
+      <c r="K16" s="122"/>
+      <c r="L16" s="123"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B17" s="23"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="119"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="120"/>
+      <c r="C17" s="127"/>
+      <c r="D17" s="128"/>
+      <c r="E17" s="128"/>
+      <c r="F17" s="128"/>
+      <c r="G17" s="129"/>
       <c r="I17" s="22"/>
-      <c r="J17" s="112"/>
-      <c r="K17" s="113"/>
-      <c r="L17" s="114"/>
+      <c r="J17" s="121"/>
+      <c r="K17" s="122"/>
+      <c r="L17" s="123"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B18" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="115"/>
-      <c r="D18" s="116"/>
-      <c r="E18" s="116"/>
-      <c r="F18" s="116"/>
-      <c r="G18" s="117"/>
+      <c r="C18" s="124"/>
+      <c r="D18" s="125"/>
+      <c r="E18" s="125"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="126"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C19" s="118"/>
-      <c r="D19" s="119"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="119"/>
-      <c r="G19" s="120"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="128"/>
+      <c r="E19" s="128"/>
+      <c r="F19" s="128"/>
+      <c r="G19" s="129"/>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C20" s="16"/>
@@ -3164,13 +3356,13 @@
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="53"/>
-      <c r="H23" s="109" t="s">
+      <c r="H23" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="I23" s="110"/>
-      <c r="J23" s="110"/>
-      <c r="K23" s="110"/>
-      <c r="L23" s="111"/>
+      <c r="I23" s="119"/>
+      <c r="J23" s="119"/>
+      <c r="K23" s="119"/>
+      <c r="L23" s="120"/>
     </row>
     <row r="24" spans="2:15" s="44" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="B24" s="18" t="s">
@@ -4021,11 +4213,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:I5"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="D10:E10"/>
@@ -4038,6 +4225,11 @@
     <mergeCell ref="C18:G19"/>
     <mergeCell ref="C14:G15"/>
     <mergeCell ref="D6:I6"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:I5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4046,8 +4238,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AD103B3-4618-405C-A46A-99E8E6568320}">
-  <dimension ref="B2:U67"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16EDE142-CD7E-4860-A576-592D7843E36C}">
+  <dimension ref="B2:U77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.5703125" customWidth="1"/>
@@ -4065,14 +4257,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:21" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
@@ -4090,16 +4282,16 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="125" t="s">
+      <c r="B4" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="126"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="122"/>
-      <c r="F4" s="122"/>
-      <c r="G4" s="122"/>
-      <c r="H4" s="122"/>
-      <c r="I4" s="123"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="145"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="147"/>
+      <c r="H4" s="153"/>
+      <c r="I4" s="153"/>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="S4" s="2"/>
@@ -4111,18 +4303,18 @@
       </c>
     </row>
     <row r="5" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="130" t="s">
+      <c r="B5" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="131"/>
-      <c r="D5" s="138" t="s">
+      <c r="C5" s="113"/>
+      <c r="D5" s="145" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="139"/>
-      <c r="F5" s="139"/>
-      <c r="G5" s="139"/>
-      <c r="H5" s="139"/>
-      <c r="I5" s="140"/>
+      <c r="E5" s="146"/>
+      <c r="F5" s="146"/>
+      <c r="G5" s="147"/>
+      <c r="H5" s="153"/>
+      <c r="I5" s="153"/>
       <c r="J5" s="15"/>
       <c r="K5" s="15"/>
       <c r="S5" s="2"/>
@@ -4132,18 +4324,18 @@
       </c>
     </row>
     <row r="6" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="105" t="s">
+      <c r="B6" s="114" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="106"/>
-      <c r="D6" s="121" t="s">
+      <c r="C6" s="115"/>
+      <c r="D6" s="130" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="122"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="122"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="123"/>
+      <c r="E6" s="131"/>
+      <c r="F6" s="131"/>
+      <c r="G6" s="132"/>
+      <c r="H6" s="153"/>
+      <c r="I6" s="153"/>
       <c r="J6" s="14"/>
       <c r="K6" s="14"/>
       <c r="S6" s="2"/>
@@ -4152,381 +4344,384 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="2:21" ht="21" x14ac:dyDescent="0.25">
-      <c r="B8" s="36" t="s">
+    <row r="7" spans="2:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="97"/>
+      <c r="C7" s="97" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="130"/>
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="132"/>
+      <c r="H7" s="153"/>
+      <c r="I7" s="153"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+    </row>
+    <row r="9" spans="2:21" ht="21" x14ac:dyDescent="0.25">
+      <c r="B9" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-    </row>
-    <row r="9" spans="2:21" s="21" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="18" t="s">
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" spans="2:21" s="21" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C10" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="107" t="s">
+      <c r="D10" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="107"/>
-      <c r="F9" s="18" t="s">
+      <c r="E10" s="116"/>
+      <c r="F10" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G10" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="N9" s="47"/>
-    </row>
-    <row r="10" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="95">
+      <c r="N10" s="47"/>
+    </row>
+    <row r="11" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="94">
         <v>1</v>
       </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="108"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="33"/>
-    </row>
-    <row r="11" spans="2:21" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-    </row>
-    <row r="12" spans="2:21" ht="21" x14ac:dyDescent="0.25">
-      <c r="B12" s="72" t="s">
-        <v>53</v>
-      </c>
+      <c r="C11" s="95"/>
+      <c r="D11" s="148"/>
+      <c r="E11" s="149"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="33"/>
+    </row>
+    <row r="12" spans="2:21" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
       <c r="G12" s="36"/>
       <c r="H12" s="36"/>
     </row>
     <row r="13" spans="2:21" ht="21" x14ac:dyDescent="0.25">
-      <c r="B13" s="73" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="74" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" s="74" t="s">
-        <v>43</v>
+      <c r="B13" s="72" t="s">
+        <v>53</v>
       </c>
       <c r="G13" s="36"/>
       <c r="H13" s="36"/>
     </row>
-    <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="91"/>
-      <c r="C14" s="97"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="133"/>
-      <c r="F14" s="133"/>
-      <c r="G14" s="134"/>
+    <row r="14" spans="2:21" ht="21" x14ac:dyDescent="0.25">
+      <c r="B14" s="73" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="74" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="36"/>
       <c r="H14" s="36"/>
     </row>
     <row r="15" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="91"/>
-      <c r="C15" s="97"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="133"/>
-      <c r="F15" s="133"/>
-      <c r="G15" s="134"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="140"/>
+      <c r="G15" s="141"/>
       <c r="H15" s="36"/>
     </row>
     <row r="16" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="91"/>
-      <c r="C16" s="97"/>
-      <c r="D16" s="132"/>
-      <c r="E16" s="133"/>
-      <c r="F16" s="133"/>
-      <c r="G16" s="134"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="98"/>
+      <c r="D16" s="139"/>
+      <c r="E16" s="140"/>
+      <c r="F16" s="140"/>
+      <c r="G16" s="141"/>
       <c r="H16" s="36"/>
     </row>
     <row r="17" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="91"/>
-      <c r="C17" s="97"/>
-      <c r="D17" s="132"/>
-      <c r="E17" s="133"/>
-      <c r="F17" s="133"/>
-      <c r="G17" s="134"/>
+      <c r="B17" s="90"/>
+      <c r="C17" s="98"/>
+      <c r="D17" s="139"/>
+      <c r="E17" s="140"/>
+      <c r="F17" s="140"/>
+      <c r="G17" s="141"/>
       <c r="H17" s="36"/>
     </row>
     <row r="18" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="91"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="135"/>
-      <c r="E18" s="136"/>
-      <c r="F18" s="136"/>
-      <c r="G18" s="137"/>
+      <c r="B18" s="90"/>
+      <c r="C18" s="98"/>
+      <c r="D18" s="139"/>
+      <c r="E18" s="140"/>
+      <c r="F18" s="140"/>
+      <c r="G18" s="141"/>
       <c r="H18" s="36"/>
     </row>
-    <row r="19" spans="2:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="75"/>
-      <c r="C19" s="84"/>
-      <c r="D19" s="85"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="85"/>
-      <c r="G19" s="36"/>
+    <row r="19" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="90"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="142"/>
+      <c r="E19" s="143"/>
+      <c r="F19" s="143"/>
+      <c r="G19" s="144"/>
       <c r="H19" s="36"/>
     </row>
-    <row r="20" spans="2:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B20" s="72" t="s">
-        <v>48</v>
-      </c>
+    <row r="20" spans="2:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="75"/>
+      <c r="C20" s="84"/>
+      <c r="D20" s="85"/>
+      <c r="E20" s="85"/>
       <c r="F20" s="85"/>
       <c r="G20" s="36"/>
       <c r="H20" s="36"/>
     </row>
     <row r="21" spans="2:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B21" s="76" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="77" t="s">
-        <v>70</v>
+      <c r="B21" s="72" t="s">
+        <v>48</v>
       </c>
       <c r="F21" s="85"/>
       <c r="G21" s="36"/>
       <c r="H21" s="36"/>
     </row>
-    <row r="22" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="90"/>
-      <c r="C22" s="132"/>
-      <c r="D22" s="133"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="134"/>
+    <row r="22" spans="2:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="B22" s="76" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="77" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" s="85"/>
+      <c r="G22" s="36"/>
       <c r="H22" s="36"/>
     </row>
     <row r="23" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="90"/>
-      <c r="C23" s="132"/>
-      <c r="D23" s="133"/>
-      <c r="E23" s="133"/>
-      <c r="F23" s="134"/>
+      <c r="B23" s="154"/>
+      <c r="C23" s="139"/>
+      <c r="D23" s="140"/>
+      <c r="E23" s="140"/>
+      <c r="F23" s="140"/>
+      <c r="G23" s="141"/>
       <c r="H23" s="36"/>
     </row>
     <row r="24" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="90"/>
-      <c r="C24" s="135"/>
-      <c r="D24" s="136"/>
-      <c r="E24" s="136"/>
-      <c r="F24" s="137"/>
+      <c r="B24" s="154"/>
+      <c r="C24" s="139"/>
+      <c r="D24" s="140"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="140"/>
+      <c r="G24" s="141"/>
       <c r="H24" s="36"/>
     </row>
-    <row r="25" spans="2:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="75"/>
-      <c r="C25" s="84"/>
-      <c r="D25" s="85"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="85"/>
-      <c r="G25" s="36"/>
+    <row r="25" spans="2:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="154"/>
+      <c r="C25" s="142"/>
+      <c r="D25" s="143"/>
+      <c r="E25" s="143"/>
+      <c r="F25" s="143"/>
+      <c r="G25" s="144"/>
       <c r="H25" s="36"/>
     </row>
-    <row r="26" spans="2:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="B26" s="36" t="s">
+    <row r="26" spans="2:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="75"/>
+      <c r="C26" s="84"/>
+      <c r="D26" s="85"/>
+      <c r="E26" s="85"/>
+      <c r="F26" s="85"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="36"/>
+    </row>
+    <row r="27" spans="2:8" ht="21" x14ac:dyDescent="0.25">
+      <c r="B27" s="36" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="18" t="s">
+    <row r="28" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="35" t="s">
+      <c r="C28" s="35" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="92" t="s">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="91" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="141"/>
-      <c r="D28" s="142"/>
-      <c r="E28" s="142"/>
-      <c r="F28" s="142"/>
-      <c r="G28" s="143"/>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="92"/>
-      <c r="C29" s="144"/>
-      <c r="D29" s="145"/>
-      <c r="E29" s="145"/>
-      <c r="F29" s="145"/>
-      <c r="G29" s="146"/>
+      <c r="C29" s="133"/>
+      <c r="D29" s="134"/>
+      <c r="E29" s="134"/>
+      <c r="F29" s="134"/>
+      <c r="G29" s="135"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="92" t="s">
+      <c r="B30" s="91"/>
+      <c r="C30" s="136"/>
+      <c r="D30" s="137"/>
+      <c r="E30" s="137"/>
+      <c r="F30" s="137"/>
+      <c r="G30" s="138"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="91" t="s">
         <v>50</v>
       </c>
-      <c r="C30" s="141"/>
-      <c r="D30" s="142"/>
-      <c r="E30" s="142"/>
-      <c r="F30" s="142"/>
-      <c r="G30" s="143"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="93"/>
-      <c r="C31" s="144"/>
-      <c r="D31" s="145"/>
-      <c r="E31" s="145"/>
-      <c r="F31" s="145"/>
-      <c r="G31" s="146"/>
+      <c r="C31" s="133"/>
+      <c r="D31" s="134"/>
+      <c r="E31" s="134"/>
+      <c r="F31" s="134"/>
+      <c r="G31" s="135"/>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="92" t="s">
+      <c r="B32" s="92"/>
+      <c r="C32" s="136"/>
+      <c r="D32" s="137"/>
+      <c r="E32" s="137"/>
+      <c r="F32" s="137"/>
+      <c r="G32" s="138"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B33" s="91" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="141"/>
-      <c r="D32" s="142"/>
-      <c r="E32" s="142"/>
-      <c r="F32" s="142"/>
-      <c r="G32" s="143"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B33" s="94"/>
-      <c r="C33" s="144"/>
-      <c r="D33" s="145"/>
-      <c r="E33" s="145"/>
-      <c r="F33" s="145"/>
-      <c r="G33" s="146"/>
+      <c r="C33" s="133"/>
+      <c r="D33" s="134"/>
+      <c r="E33" s="134"/>
+      <c r="F33" s="134"/>
+      <c r="G33" s="135"/>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-    </row>
-    <row r="35" spans="2:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-    </row>
-    <row r="36" spans="2:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B36" s="17" t="s">
+      <c r="B34" s="93"/>
+      <c r="C34" s="136"/>
+      <c r="D34" s="137"/>
+      <c r="E34" s="137"/>
+      <c r="F34" s="137"/>
+      <c r="G34" s="138"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+    </row>
+    <row r="36" spans="2:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+    </row>
+    <row r="37" spans="2:15" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B37" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="53"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-    </row>
-    <row r="37" spans="2:15" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B37" s="1"/>
       <c r="C37" s="12"/>
       <c r="D37" s="24"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="53"/>
-      <c r="H37" s="109" t="s">
+      <c r="H37" s="1"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="11"/>
+    </row>
+    <row r="38" spans="2:15" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B38" s="1"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="118" t="s">
         <v>53</v>
       </c>
-      <c r="I37" s="110"/>
-      <c r="J37" s="110"/>
-      <c r="K37" s="110"/>
-      <c r="L37" s="111"/>
-    </row>
-    <row r="38" spans="2:15" s="44" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B38" s="18" t="s">
+      <c r="I38" s="119"/>
+      <c r="J38" s="119"/>
+      <c r="K38" s="119"/>
+      <c r="L38" s="120"/>
+    </row>
+    <row r="39" spans="2:15" s="44" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B39" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="64" t="s">
+      <c r="C39" s="64" t="s">
         <v>55</v>
       </c>
-      <c r="D38" s="64" t="s">
+      <c r="D39" s="64" t="s">
         <v>56</v>
       </c>
-      <c r="E38" s="64" t="s">
+      <c r="E39" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="F38" s="64" t="s">
+      <c r="F39" s="64" t="s">
         <v>58</v>
       </c>
-      <c r="G38" s="64" t="s">
+      <c r="G39" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="H38" s="61" t="s">
+      <c r="H39" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="I38" s="62" t="s">
+      <c r="I39" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="J38" s="62" t="s">
+      <c r="J39" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="K38" s="62" t="s">
+      <c r="K39" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="L38" s="63" t="s">
+      <c r="L39" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="M38" s="19" t="s">
+      <c r="M39" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="N38" s="19" t="s">
+      <c r="N39" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="O38" s="20"/>
-    </row>
-    <row r="39" spans="2:15" s="3" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B39" s="37">
+      <c r="O39" s="20"/>
+    </row>
+    <row r="40" spans="2:15" s="3" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B40" s="37">
         <v>1</v>
-      </c>
-      <c r="C39" s="25"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="86" t="s">
-        <v>73</v>
-      </c>
-      <c r="I39" s="87" t="s">
-        <v>74</v>
-      </c>
-      <c r="J39" s="86" t="s">
-        <v>73</v>
-      </c>
-      <c r="K39" s="86" t="s">
-        <v>73</v>
-      </c>
-      <c r="L39" s="86" t="s">
-        <v>73</v>
-      </c>
-      <c r="M39" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="N39" s="48"/>
-    </row>
-    <row r="40" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="37">
-        <v>2</v>
       </c>
       <c r="C40" s="25"/>
       <c r="D40" s="27"/>
       <c r="E40" s="27"/>
       <c r="F40" s="31"/>
       <c r="G40" s="27"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="26"/>
+      <c r="H40" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="I40" s="87" t="s">
+        <v>73</v>
+      </c>
+      <c r="J40" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="K40" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="L40" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="M40" s="155" t="s">
+        <v>66</v>
+      </c>
       <c r="N40" s="48"/>
     </row>
     <row r="41" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41" s="25"/>
       <c r="D41" s="27"/>
@@ -4538,12 +4733,12 @@
       <c r="J41" s="29"/>
       <c r="K41" s="30"/>
       <c r="L41" s="30"/>
-      <c r="M41" s="26"/>
+      <c r="M41" s="155"/>
       <c r="N41" s="48"/>
     </row>
     <row r="42" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C42" s="25"/>
       <c r="D42" s="27"/>
@@ -4555,12 +4750,12 @@
       <c r="J42" s="29"/>
       <c r="K42" s="30"/>
       <c r="L42" s="30"/>
-      <c r="M42" s="26"/>
+      <c r="M42" s="155"/>
       <c r="N42" s="48"/>
     </row>
     <row r="43" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C43" s="25"/>
       <c r="D43" s="27"/>
@@ -4572,12 +4767,12 @@
       <c r="J43" s="29"/>
       <c r="K43" s="30"/>
       <c r="L43" s="30"/>
-      <c r="M43" s="26"/>
+      <c r="M43" s="155"/>
       <c r="N43" s="48"/>
     </row>
     <row r="44" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" s="25"/>
       <c r="D44" s="27"/>
@@ -4589,12 +4784,12 @@
       <c r="J44" s="29"/>
       <c r="K44" s="30"/>
       <c r="L44" s="30"/>
-      <c r="M44" s="26"/>
+      <c r="M44" s="155"/>
       <c r="N44" s="48"/>
     </row>
     <row r="45" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C45" s="25"/>
       <c r="D45" s="27"/>
@@ -4606,12 +4801,12 @@
       <c r="J45" s="29"/>
       <c r="K45" s="30"/>
       <c r="L45" s="30"/>
-      <c r="M45" s="26"/>
+      <c r="M45" s="155"/>
       <c r="N45" s="48"/>
     </row>
     <row r="46" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C46" s="25"/>
       <c r="D46" s="27"/>
@@ -4623,12 +4818,12 @@
       <c r="J46" s="29"/>
       <c r="K46" s="30"/>
       <c r="L46" s="30"/>
-      <c r="M46" s="26"/>
+      <c r="M46" s="155"/>
       <c r="N46" s="48"/>
     </row>
     <row r="47" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C47" s="25"/>
       <c r="D47" s="27"/>
@@ -4640,12 +4835,12 @@
       <c r="J47" s="29"/>
       <c r="K47" s="30"/>
       <c r="L47" s="30"/>
-      <c r="M47" s="26"/>
+      <c r="M47" s="155"/>
       <c r="N47" s="48"/>
     </row>
     <row r="48" spans="2:15" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C48" s="25"/>
       <c r="D48" s="27"/>
@@ -4657,12 +4852,12 @@
       <c r="J48" s="29"/>
       <c r="K48" s="30"/>
       <c r="L48" s="30"/>
-      <c r="M48" s="26"/>
+      <c r="M48" s="155"/>
       <c r="N48" s="48"/>
     </row>
     <row r="49" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="37">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C49" s="25"/>
       <c r="D49" s="27"/>
@@ -4674,12 +4869,12 @@
       <c r="J49" s="29"/>
       <c r="K49" s="30"/>
       <c r="L49" s="30"/>
-      <c r="M49" s="26"/>
+      <c r="M49" s="155"/>
       <c r="N49" s="48"/>
     </row>
     <row r="50" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="37">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C50" s="25"/>
       <c r="D50" s="27"/>
@@ -4691,12 +4886,12 @@
       <c r="J50" s="29"/>
       <c r="K50" s="30"/>
       <c r="L50" s="30"/>
-      <c r="M50" s="26"/>
+      <c r="M50" s="155"/>
       <c r="N50" s="48"/>
     </row>
     <row r="51" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="37">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C51" s="25"/>
       <c r="D51" s="27"/>
@@ -4708,12 +4903,12 @@
       <c r="J51" s="29"/>
       <c r="K51" s="30"/>
       <c r="L51" s="30"/>
-      <c r="M51" s="26"/>
+      <c r="M51" s="155"/>
       <c r="N51" s="48"/>
     </row>
     <row r="52" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="37">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C52" s="25"/>
       <c r="D52" s="27"/>
@@ -4725,12 +4920,12 @@
       <c r="J52" s="29"/>
       <c r="K52" s="30"/>
       <c r="L52" s="30"/>
-      <c r="M52" s="26"/>
+      <c r="M52" s="155"/>
       <c r="N52" s="48"/>
     </row>
     <row r="53" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="37">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C53" s="25"/>
       <c r="D53" s="27"/>
@@ -4742,12 +4937,12 @@
       <c r="J53" s="29"/>
       <c r="K53" s="30"/>
       <c r="L53" s="30"/>
-      <c r="M53" s="26"/>
+      <c r="M53" s="155"/>
       <c r="N53" s="48"/>
     </row>
     <row r="54" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="37">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C54" s="25"/>
       <c r="D54" s="27"/>
@@ -4759,12 +4954,12 @@
       <c r="J54" s="29"/>
       <c r="K54" s="30"/>
       <c r="L54" s="30"/>
-      <c r="M54" s="26"/>
+      <c r="M54" s="155"/>
       <c r="N54" s="48"/>
     </row>
     <row r="55" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="37">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C55" s="25"/>
       <c r="D55" s="27"/>
@@ -4776,12 +4971,12 @@
       <c r="J55" s="29"/>
       <c r="K55" s="30"/>
       <c r="L55" s="30"/>
-      <c r="M55" s="26"/>
+      <c r="M55" s="155"/>
       <c r="N55" s="48"/>
     </row>
     <row r="56" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="37">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C56" s="25"/>
       <c r="D56" s="27"/>
@@ -4793,12 +4988,12 @@
       <c r="J56" s="29"/>
       <c r="K56" s="30"/>
       <c r="L56" s="30"/>
-      <c r="M56" s="26"/>
+      <c r="M56" s="155"/>
       <c r="N56" s="48"/>
     </row>
     <row r="57" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="37">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C57" s="25"/>
       <c r="D57" s="27"/>
@@ -4810,12 +5005,12 @@
       <c r="J57" s="29"/>
       <c r="K57" s="30"/>
       <c r="L57" s="30"/>
-      <c r="M57" s="26"/>
+      <c r="M57" s="155"/>
       <c r="N57" s="48"/>
     </row>
     <row r="58" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="37">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C58" s="25"/>
       <c r="D58" s="27"/>
@@ -4827,12 +5022,12 @@
       <c r="J58" s="29"/>
       <c r="K58" s="30"/>
       <c r="L58" s="30"/>
-      <c r="M58" s="26"/>
+      <c r="M58" s="155"/>
       <c r="N58" s="48"/>
     </row>
     <row r="59" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="37">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C59" s="25"/>
       <c r="D59" s="27"/>
@@ -4844,12 +5039,12 @@
       <c r="J59" s="29"/>
       <c r="K59" s="30"/>
       <c r="L59" s="30"/>
-      <c r="M59" s="26"/>
+      <c r="M59" s="155"/>
       <c r="N59" s="48"/>
     </row>
     <row r="60" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="37">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C60" s="25"/>
       <c r="D60" s="27"/>
@@ -4861,12 +5056,12 @@
       <c r="J60" s="29"/>
       <c r="K60" s="30"/>
       <c r="L60" s="30"/>
-      <c r="M60" s="26"/>
+      <c r="M60" s="155"/>
       <c r="N60" s="48"/>
     </row>
     <row r="61" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="37">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C61" s="25"/>
       <c r="D61" s="27"/>
@@ -4878,12 +5073,12 @@
       <c r="J61" s="29"/>
       <c r="K61" s="30"/>
       <c r="L61" s="30"/>
-      <c r="M61" s="26"/>
+      <c r="M61" s="155"/>
       <c r="N61" s="48"/>
     </row>
     <row r="62" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="37">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C62" s="25"/>
       <c r="D62" s="27"/>
@@ -4895,12 +5090,12 @@
       <c r="J62" s="29"/>
       <c r="K62" s="30"/>
       <c r="L62" s="30"/>
-      <c r="M62" s="26"/>
+      <c r="M62" s="155"/>
       <c r="N62" s="48"/>
     </row>
     <row r="63" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="37">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C63" s="25"/>
       <c r="D63" s="27"/>
@@ -4912,75 +5107,245 @@
       <c r="J63" s="29"/>
       <c r="K63" s="30"/>
       <c r="L63" s="30"/>
-      <c r="M63" s="26"/>
+      <c r="M63" s="155"/>
       <c r="N63" s="48"/>
     </row>
-    <row r="64" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="37"/>
-      <c r="C64" s="38"/>
-      <c r="D64" s="39"/>
-      <c r="E64" s="39"/>
-      <c r="F64" s="40"/>
-      <c r="G64" s="39"/>
-      <c r="H64" s="41"/>
-      <c r="I64" s="42"/>
-      <c r="J64" s="42"/>
-      <c r="K64" s="42"/>
-      <c r="L64" s="42"/>
-      <c r="M64" s="43"/>
-      <c r="N64" s="46"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B65" s="4"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="6"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="C67" s="89" t="s">
-        <v>75</v>
-      </c>
-      <c r="D67" t="str">
-        <f>IF(COUNTIF(M39:M63,"Yes")=0,
-  "No exceptions noted.",
-  COUNTIF(M39:M63,"Yes")&amp;" exception(s) noted."
-)</f>
+    <row r="64" spans="2:14" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="37">
+        <v>25</v>
+      </c>
+      <c r="C64" s="25"/>
+      <c r="D64" s="27"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="31"/>
+      <c r="G64" s="27"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="28"/>
+      <c r="J64" s="29"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="155"/>
+      <c r="N64" s="48"/>
+    </row>
+    <row r="65" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B65" s="37"/>
+      <c r="C65" s="38"/>
+      <c r="D65" s="39"/>
+      <c r="E65" s="39"/>
+      <c r="F65" s="40"/>
+      <c r="G65" s="39"/>
+      <c r="H65" s="41"/>
+      <c r="I65" s="42"/>
+      <c r="J65" s="42"/>
+      <c r="K65" s="42"/>
+      <c r="L65" s="42"/>
+      <c r="M65" s="43"/>
+      <c r="N65" s="46"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B66" s="4"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="156" t="str">
+        <f>IF(COUNTIF(M40:M64,"Yes")=0,
+"No exceptions noted.",
+COUNTIF(M40:M64,"Yes")&amp;" exception(s) noted.")</f>
         <v>1 exception(s) noted.</v>
       </c>
     </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C68" s="89"/>
+    </row>
+    <row r="69" spans="2:14" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="H69" s="157" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="G70" s="158" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="G71" s="159" t="s">
+        <v>81</v>
+      </c>
+      <c r="H71" s="160">
+        <f>_xlfn.LET(_xlpm.x, COUNTIF(H$40:H$64, $G71), IF(_xlpm.x=0, "", _xlpm.x))</f>
+        <v>1</v>
+      </c>
+      <c r="I71" s="160" t="str">
+        <f t="shared" ref="I71:L72" si="0">_xlfn.LET(_xlpm.x, COUNTIF(I$40:I$64, $G71), IF(_xlpm.x=0, "", _xlpm.x))</f>
+        <v/>
+      </c>
+      <c r="J71" s="160">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="K71" s="160">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L71" s="160">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="G72" s="161" t="s">
+        <v>73</v>
+      </c>
+      <c r="H72" s="160" t="str">
+        <f>_xlfn.LET(_xlpm.x, COUNTIF(H$40:H$64, $G72), IF(_xlpm.x=0, "", _xlpm.x))</f>
+        <v/>
+      </c>
+      <c r="I72" s="160">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="J72" s="160" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="K72" s="160" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="L72" s="160" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="2:14" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="G73" s="162"/>
+      <c r="H73" s="160" t="str">
+        <f t="shared" ref="H73:L76" si="1">_xlfn.LET(_xlpm.x, COUNTIF(H$40:H$64, $G73), IF(_xlpm.x=0, "", _xlpm.x))</f>
+        <v/>
+      </c>
+      <c r="I73" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J73" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K73" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L73" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="2:14" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="G74" s="163"/>
+      <c r="H74" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I74" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J74" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K74" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L74" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="2:14" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="G75" s="163"/>
+      <c r="H75" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I75" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J75" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K75" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L75" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="2:14" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="G76" s="163"/>
+      <c r="H76" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I76" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="J76" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K76" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L76" s="160" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="H77" s="163"/>
+    </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="C32:G33"/>
-    <mergeCell ref="H37:L37"/>
-    <mergeCell ref="C30:G31"/>
-    <mergeCell ref="C28:G29"/>
-    <mergeCell ref="D9:E9"/>
+  <mergeCells count="22">
+    <mergeCell ref="C31:G32"/>
+    <mergeCell ref="C33:G34"/>
+    <mergeCell ref="H38:L38"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="C29:G30"/>
+    <mergeCell ref="D7:G7"/>
     <mergeCell ref="D10:E10"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="D6:I6"/>
-    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D11:E11"/>
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="D16:G16"/>
     <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:G6"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M39:M63" xr:uid="{7EA76EF9-12A3-48C6-BC4E-AF4D09AB486E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M40:M64" xr:uid="{1C4E1F67-A064-4A90-9D2F-62200BEC4B05}">
       <formula1>"Yes, No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4990,7 +5355,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27C2776A-E04F-41FD-B3D7-35684437E078}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7586FEF-2C46-4329-B264-064D01E7F01D}">
   <dimension ref="B1:U31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5013,14 +5378,14 @@
       <c r="N1" s="16"/>
     </row>
     <row r="2" spans="2:21" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
@@ -5039,16 +5404,19 @@
       <c r="K3" s="1"/>
       <c r="N3" s="16"/>
     </row>
-    <row r="4" spans="2:21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="150" t="s">
+    <row r="4" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="151" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="151"/>
-      <c r="D4" s="121" t="s">
+      <c r="C4" s="152"/>
+      <c r="D4" s="130" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="122"/>
-      <c r="F4" s="123"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="131"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="153"/>
+      <c r="I4" s="153"/>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="N4" s="16"/>
@@ -5082,10 +5450,10 @@
       <c r="C7" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="107" t="s">
+      <c r="D7" s="116" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="107"/>
+      <c r="E7" s="116"/>
       <c r="F7" s="18" t="s">
         <v>45</v>
       </c>
@@ -5095,14 +5463,14 @@
       <c r="N7" s="16"/>
     </row>
     <row r="8" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="95">
+      <c r="B8" s="94">
         <v>1</v>
       </c>
-      <c r="C8" s="98"/>
-      <c r="D8" s="147"/>
-      <c r="E8" s="148"/>
-      <c r="F8" s="99"/>
-      <c r="G8" s="100"/>
+      <c r="C8" s="95"/>
+      <c r="D8" s="148"/>
+      <c r="E8" s="149"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="33"/>
       <c r="N8" s="16"/>
     </row>
     <row r="9" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
@@ -5133,43 +5501,48 @@
       <c r="N11" s="16"/>
     </row>
     <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="101"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="136"/>
-      <c r="F12" s="137"/>
+      <c r="B12" s="90"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="139"/>
+      <c r="E12" s="140"/>
+      <c r="F12" s="140"/>
+      <c r="G12" s="141"/>
       <c r="N12" s="16"/>
     </row>
     <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="101"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="135"/>
-      <c r="E13" s="136"/>
-      <c r="F13" s="137"/>
+      <c r="B13" s="90"/>
+      <c r="C13" s="98"/>
+      <c r="D13" s="139"/>
+      <c r="E13" s="140"/>
+      <c r="F13" s="140"/>
+      <c r="G13" s="141"/>
       <c r="N13" s="16"/>
     </row>
     <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="101"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="135"/>
-      <c r="E14" s="136"/>
-      <c r="F14" s="137"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="139"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="140"/>
+      <c r="G14" s="141"/>
       <c r="N14" s="16"/>
     </row>
     <row r="15" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="101"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="135"/>
-      <c r="E15" s="136"/>
-      <c r="F15" s="137"/>
+      <c r="B15" s="90"/>
+      <c r="C15" s="98"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="140"/>
+      <c r="G15" s="141"/>
       <c r="N15" s="16"/>
     </row>
     <row r="16" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="101"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="135"/>
-      <c r="E16" s="136"/>
-      <c r="F16" s="137"/>
+      <c r="B16" s="90"/>
+      <c r="C16" s="98"/>
+      <c r="D16" s="142"/>
+      <c r="E16" s="143"/>
+      <c r="F16" s="143"/>
+      <c r="G16" s="144"/>
       <c r="N16" s="16"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.25">
@@ -5192,26 +5565,30 @@
       <c r="N19" s="16"/>
     </row>
     <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="102"/>
-      <c r="C20" s="135"/>
-      <c r="D20" s="136"/>
-      <c r="E20" s="137"/>
+      <c r="B20" s="96"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
+      <c r="F20" s="140"/>
+      <c r="G20" s="141"/>
       <c r="N20" s="16"/>
     </row>
     <row r="21" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="102"/>
-      <c r="C21" s="135"/>
-      <c r="D21" s="136"/>
-      <c r="E21" s="137"/>
+      <c r="B21" s="96"/>
+      <c r="C21" s="139"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="140"/>
+      <c r="G21" s="141"/>
       <c r="N21" s="16"/>
     </row>
     <row r="22" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="102"/>
-      <c r="C22" s="135"/>
-      <c r="D22" s="136"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="142"/>
+      <c r="D22" s="143"/>
+      <c r="E22" s="143"/>
+      <c r="F22" s="143"/>
+      <c r="G22" s="144"/>
       <c r="H22" s="36"/>
       <c r="N22" s="16"/>
     </row>
@@ -5242,12 +5619,12 @@
       <c r="N25" s="16"/>
     </row>
     <row r="26" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="92"/>
-      <c r="C26" s="147"/>
-      <c r="D26" s="149"/>
-      <c r="E26" s="149"/>
-      <c r="F26" s="149"/>
-      <c r="G26" s="148"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="148"/>
+      <c r="D26" s="150"/>
+      <c r="E26" s="150"/>
+      <c r="F26" s="150"/>
+      <c r="G26" s="149"/>
       <c r="N26" s="16"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
@@ -5280,20 +5657,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:G4"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="D8:E8"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5301,22 +5678,535 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D90A4130-68CA-4E30-9267-87839E021ADD}">
-  <dimension ref="B1:U85"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED6BF3F6-6A37-40AB-99D1-445D42FFF4A0}">
+  <dimension ref="A1:T32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" customWidth="1"/>
+    <col min="3" max="3" width="27.140625" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="9"/>
+      <c r="M1" s="16"/>
+    </row>
+    <row r="2" spans="1:20" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="106"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="M2" s="16"/>
+    </row>
+    <row r="3" spans="1:20" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="M3" s="16"/>
+    </row>
+    <row r="4" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="151" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="152"/>
+      <c r="C4" s="130" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="131"/>
+      <c r="E4" s="131"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="153"/>
+      <c r="H4" s="153"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="M4" s="16"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="9"/>
+      <c r="M5" s="16"/>
+    </row>
+    <row r="6" spans="1:20" ht="21" x14ac:dyDescent="0.25">
+      <c r="A6" s="72" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="M6" s="16"/>
+    </row>
+    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="116" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="116"/>
+      <c r="E7" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="M7" s="16"/>
+    </row>
+    <row r="8" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="94">
+        <v>1</v>
+      </c>
+      <c r="B8" s="95"/>
+      <c r="C8" s="148"/>
+      <c r="D8" s="149"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="33"/>
+      <c r="M8" s="16"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="M9" s="16"/>
+    </row>
+    <row r="10" spans="1:20" ht="21" x14ac:dyDescent="0.25">
+      <c r="A10" s="72" t="s">
+        <v>53</v>
+      </c>
+      <c r="M10" s="16"/>
+    </row>
+    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="73" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="74" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="M11" s="16"/>
+    </row>
+    <row r="12" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="90"/>
+      <c r="B12" s="98"/>
+      <c r="C12" s="139"/>
+      <c r="D12" s="140"/>
+      <c r="E12" s="140"/>
+      <c r="F12" s="141"/>
+      <c r="M12" s="16"/>
+    </row>
+    <row r="13" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="90"/>
+      <c r="B13" s="98"/>
+      <c r="C13" s="139"/>
+      <c r="D13" s="140"/>
+      <c r="E13" s="140"/>
+      <c r="F13" s="141"/>
+      <c r="M13" s="16"/>
+    </row>
+    <row r="14" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="90"/>
+      <c r="B14" s="98"/>
+      <c r="C14" s="139"/>
+      <c r="D14" s="140"/>
+      <c r="E14" s="140"/>
+      <c r="F14" s="141"/>
+      <c r="M14" s="16"/>
+    </row>
+    <row r="15" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="90"/>
+      <c r="B15" s="98"/>
+      <c r="C15" s="139"/>
+      <c r="D15" s="140"/>
+      <c r="E15" s="140"/>
+      <c r="F15" s="141"/>
+      <c r="M15" s="16"/>
+    </row>
+    <row r="16" spans="1:20" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="90"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="142"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="143"/>
+      <c r="F16" s="144"/>
+      <c r="M16" s="16"/>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="75"/>
+      <c r="B17" s="79"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="79"/>
+      <c r="M17" s="16"/>
+    </row>
+    <row r="18" spans="1:13" ht="21" x14ac:dyDescent="0.25">
+      <c r="A18" s="72" t="s">
+        <v>48</v>
+      </c>
+      <c r="M18" s="16"/>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="76" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="77" t="s">
+        <v>70</v>
+      </c>
+      <c r="M19" s="16"/>
+    </row>
+    <row r="20" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="96"/>
+      <c r="B20" s="139"/>
+      <c r="C20" s="140"/>
+      <c r="D20" s="140"/>
+      <c r="E20" s="140"/>
+      <c r="F20" s="141"/>
+      <c r="M20" s="16"/>
+    </row>
+    <row r="21" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="96"/>
+      <c r="B21" s="139"/>
+      <c r="C21" s="140"/>
+      <c r="D21" s="140"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="141"/>
+      <c r="M21" s="16"/>
+    </row>
+    <row r="22" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="96"/>
+      <c r="B22" s="142"/>
+      <c r="C22" s="143"/>
+      <c r="D22" s="143"/>
+      <c r="E22" s="143"/>
+      <c r="F22" s="144"/>
+      <c r="M22" s="16"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="9"/>
+      <c r="M23" s="16"/>
+    </row>
+    <row r="24" spans="1:13" ht="21" x14ac:dyDescent="0.25">
+      <c r="A24" s="72" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="72"/>
+      <c r="M24" s="16"/>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="M25" s="16"/>
+    </row>
+    <row r="26" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="91"/>
+      <c r="B26" s="148"/>
+      <c r="C26" s="150"/>
+      <c r="D26" s="150"/>
+      <c r="E26" s="150"/>
+      <c r="F26" s="149"/>
+      <c r="M26" s="16"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="88"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="M27" s="16"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="9"/>
+      <c r="M28" s="16"/>
+    </row>
+    <row r="29" spans="1:13" ht="21" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="M29" s="16"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="9"/>
+      <c r="M30" s="16"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="9"/>
+      <c r="M31" s="16"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="9"/>
+      <c r="M32" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C15:F15"/>
+    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E5FE2DD-55C3-4556-A346-6E1197169D20}">
+  <dimension ref="B5:J29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="151" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="152"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="131"/>
+      <c r="F5" s="131"/>
+      <c r="G5" s="131"/>
+      <c r="H5" s="131"/>
+      <c r="I5" s="131"/>
+      <c r="J5" s="132"/>
+    </row>
+    <row r="7" spans="2:10" ht="21" x14ac:dyDescent="0.25">
+      <c r="B7" s="99" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B8" s="100" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="148"/>
+      <c r="C9" s="150"/>
+      <c r="D9" s="150"/>
+      <c r="E9" s="150"/>
+      <c r="F9" s="150"/>
+      <c r="G9" s="150"/>
+      <c r="H9" s="150"/>
+      <c r="I9" s="150"/>
+      <c r="J9" s="149"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+    </row>
+    <row r="11" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B11" s="100" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="148"/>
+      <c r="C12" s="150"/>
+      <c r="D12" s="150"/>
+      <c r="E12" s="150"/>
+      <c r="F12" s="150"/>
+      <c r="G12" s="150"/>
+      <c r="H12" s="150"/>
+      <c r="I12" s="150"/>
+      <c r="J12" s="149"/>
+    </row>
+    <row r="14" spans="2:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B14" s="100" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="148"/>
+      <c r="C15" s="150"/>
+      <c r="D15" s="150"/>
+      <c r="E15" s="150"/>
+      <c r="F15" s="150"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="150"/>
+      <c r="I15" s="150"/>
+      <c r="J15" s="149"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="88"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="88"/>
+    </row>
+    <row r="17" spans="2:10" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="101" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="88"/>
+      <c r="D17" s="88"/>
+      <c r="E17" s="88"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="148"/>
+      <c r="C18" s="150"/>
+      <c r="D18" s="150"/>
+      <c r="E18" s="150"/>
+      <c r="F18" s="150"/>
+      <c r="G18" s="150"/>
+      <c r="H18" s="150"/>
+      <c r="I18" s="150"/>
+      <c r="J18" s="149"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+    </row>
+    <row r="20" spans="2:10" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="102" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="148"/>
+      <c r="C21" s="150"/>
+      <c r="D21" s="150"/>
+      <c r="E21" s="150"/>
+      <c r="F21" s="150"/>
+      <c r="G21" s="150"/>
+      <c r="H21" s="150"/>
+      <c r="I21" s="150"/>
+      <c r="J21" s="149"/>
+    </row>
+    <row r="23" spans="2:10" ht="21" x14ac:dyDescent="0.25">
+      <c r="B23" s="72" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="76" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="77" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B25" s="103"/>
+      <c r="C25" s="139"/>
+      <c r="D25" s="140"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="140"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="141"/>
+    </row>
+    <row r="26" spans="2:10" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B26" s="103"/>
+      <c r="C26" s="139"/>
+      <c r="D26" s="140"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="141"/>
+    </row>
+    <row r="27" spans="2:10" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="B27" s="103"/>
+      <c r="C27" s="142"/>
+      <c r="D27" s="143"/>
+      <c r="E27" s="143"/>
+      <c r="F27" s="143"/>
+      <c r="G27" s="143"/>
+      <c r="H27" s="144"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="9"/>
+    </row>
+    <row r="29" spans="2:10" ht="21" x14ac:dyDescent="0.25">
+      <c r="B29" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B21:J21"/>
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C26:H26"/>
+    <mergeCell ref="C27:H27"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="B18:J18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{324DBACE-32A8-4E36-A226-BC2599EA3408}">
+  <dimension ref="B1:U29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="1.5703125" customWidth="1"/>
     <col min="2" max="2" width="6.42578125" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" customWidth="1"/>
-    <col min="4" max="4" width="27.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" customWidth="1"/>
+    <col min="5" max="5" width="49.140625" customWidth="1"/>
     <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" customWidth="1"/>
+    <col min="7" max="7" width="36.85546875" customWidth="1"/>
     <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.42578125" customWidth="1"/>
+    <col min="10" max="10" width="33.85546875" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" customWidth="1"/>
     <col min="13" max="13" width="13.42578125" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" customWidth="1"/>
+    <col min="14" max="14" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:21" x14ac:dyDescent="0.25">
@@ -5324,14 +6214,14 @@
       <c r="N1" s="16"/>
     </row>
     <row r="2" spans="2:21" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
       <c r="L2" s="13"/>
@@ -5350,19 +6240,18 @@
       <c r="K3" s="1"/>
       <c r="N3" s="16"/>
     </row>
-    <row r="4" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="150" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="158"/>
-      <c r="D4" s="152" t="s">
-        <v>68</v>
-      </c>
-      <c r="E4" s="153"/>
-      <c r="F4" s="153"/>
-      <c r="G4" s="153"/>
+    <row r="4" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="151" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="152"/>
+      <c r="D4" s="164" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="165"/>
+      <c r="G4" s="163"/>
       <c r="H4" s="153"/>
-      <c r="I4" s="154"/>
+      <c r="I4" s="153"/>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="N4" s="16"/>
@@ -5380,672 +6269,162 @@
     </row>
     <row r="6" spans="2:21" ht="21" x14ac:dyDescent="0.25">
       <c r="B6" s="72" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="7"/>
+        <v>43</v>
+      </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="N6" s="16"/>
     </row>
-    <row r="7" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="107" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="107"/>
-      <c r="F7" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="N7" s="16"/>
-    </row>
-    <row r="8" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="95">
-        <v>1</v>
-      </c>
-      <c r="C8" s="98"/>
-      <c r="D8" s="147"/>
-      <c r="E8" s="148"/>
-      <c r="F8" s="99"/>
-      <c r="G8" s="100"/>
-      <c r="N8" s="16"/>
-    </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B9" s="9"/>
-      <c r="N9" s="16"/>
-    </row>
-    <row r="10" spans="2:21" ht="21" x14ac:dyDescent="0.25">
-      <c r="B10" s="72" t="s">
-        <v>53</v>
-      </c>
-      <c r="N10" s="16"/>
-    </row>
-    <row r="11" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="73" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="74" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" s="74" t="s">
-        <v>70</v>
-      </c>
-      <c r="N11" s="16"/>
-    </row>
-    <row r="12" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="101"/>
-      <c r="C12" s="96"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="136"/>
-      <c r="F12" s="137"/>
-      <c r="N12" s="16"/>
-    </row>
-    <row r="13" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="101"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="135"/>
-      <c r="E13" s="136"/>
-      <c r="F13" s="137"/>
-      <c r="N13" s="16"/>
-    </row>
-    <row r="14" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="101"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="135"/>
-      <c r="E14" s="136"/>
-      <c r="F14" s="137"/>
-      <c r="N14" s="16"/>
-    </row>
-    <row r="15" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="101"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="135"/>
-      <c r="E15" s="136"/>
-      <c r="F15" s="137"/>
-      <c r="N15" s="16"/>
-    </row>
-    <row r="16" spans="2:21" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="101"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="135"/>
-      <c r="E16" s="136"/>
-      <c r="F16" s="137"/>
-      <c r="N16" s="16"/>
-    </row>
-    <row r="17" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="75"/>
-      <c r="C17" s="79"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79"/>
-      <c r="N17" s="16"/>
-    </row>
-    <row r="18" spans="2:14" ht="21" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B7" s="88"/>
+      <c r="C7" s="166"/>
+      <c r="D7" s="167"/>
+      <c r="E7" s="168"/>
+      <c r="G7" s="163"/>
+    </row>
+    <row r="9" spans="2:21" ht="21" x14ac:dyDescent="0.25">
+      <c r="B9" s="72" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="80"/>
+    </row>
+    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C10" s="166"/>
+      <c r="D10" s="167"/>
+      <c r="E10" s="168"/>
+      <c r="G10" s="163"/>
+    </row>
+    <row r="12" spans="2:21" ht="21" x14ac:dyDescent="0.25">
+      <c r="B12" s="72" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C13" s="166"/>
+      <c r="D13" s="167"/>
+      <c r="E13" s="168"/>
+      <c r="G13" s="163"/>
+    </row>
+    <row r="15" spans="2:21" ht="21" x14ac:dyDescent="0.25">
+      <c r="B15" s="72" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="C16" s="166"/>
+      <c r="D16" s="167"/>
+      <c r="E16" s="168"/>
+      <c r="G16" s="163"/>
+    </row>
+    <row r="18" spans="2:5" ht="21" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>48</v>
-      </c>
-      <c r="N18" s="16"/>
-    </row>
-    <row r="19" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="76" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="77" t="s">
-        <v>70</v>
-      </c>
-      <c r="N19" s="16"/>
-    </row>
-    <row r="20" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="102"/>
-      <c r="C20" s="135"/>
-      <c r="D20" s="136"/>
-      <c r="E20" s="137"/>
-      <c r="N20" s="16"/>
-    </row>
-    <row r="21" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="102"/>
-      <c r="C21" s="135"/>
-      <c r="D21" s="136"/>
-      <c r="E21" s="137"/>
-      <c r="N21" s="16"/>
-    </row>
-    <row r="22" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="102"/>
-      <c r="C22" s="135"/>
-      <c r="D22" s="136"/>
-      <c r="E22" s="137"/>
-      <c r="N22" s="16"/>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B23" s="9"/>
-      <c r="N23" s="16"/>
-    </row>
-    <row r="24" spans="2:14" ht="21" x14ac:dyDescent="0.25">
-      <c r="B24" s="72" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" s="72"/>
-      <c r="N24" s="16"/>
-    </row>
-    <row r="25" spans="2:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="N25" s="16"/>
-    </row>
-    <row r="26" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="92"/>
-      <c r="C26" s="155"/>
-      <c r="D26" s="156"/>
-      <c r="E26" s="156"/>
-      <c r="F26" s="156"/>
-      <c r="G26" s="157"/>
-      <c r="N26" s="16"/>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B27" s="22"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88"/>
-      <c r="N27" s="16"/>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B28" s="9"/>
-      <c r="N28" s="16"/>
-    </row>
-    <row r="29" spans="2:14" ht="21" x14ac:dyDescent="0.25">
-      <c r="B29" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="N29" s="16"/>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B30" s="9"/>
-      <c r="N30" s="16"/>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B31" s="9"/>
-      <c r="N31" s="16"/>
-    </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B32" s="9"/>
-      <c r="N32" s="16"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B33" s="9"/>
-      <c r="N33" s="16"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B34" s="9"/>
-      <c r="N34" s="16"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B35" s="9"/>
-      <c r="N35" s="16"/>
-    </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B36" s="9"/>
-      <c r="N36" s="16"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B37" s="9"/>
-      <c r="N37" s="16"/>
-    </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B38" s="9"/>
-      <c r="N38" s="16"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B39" s="9"/>
-      <c r="N39" s="16"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B40" s="9"/>
-      <c r="N40" s="16"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B41" s="9"/>
-      <c r="N41" s="16"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B42" s="9"/>
-      <c r="N42" s="16"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B43" s="9"/>
-      <c r="N43" s="16"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B44" s="9"/>
-      <c r="N44" s="16"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B45" s="9"/>
-      <c r="N45" s="16"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B46" s="9"/>
-      <c r="N46" s="16"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B47" s="9"/>
-      <c r="N47" s="16"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B48" s="9"/>
-      <c r="N48" s="16"/>
-    </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B49" s="9"/>
-      <c r="N49" s="16"/>
-    </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B50" s="9"/>
-      <c r="N50" s="16"/>
-    </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B51" s="9"/>
-      <c r="N51" s="16"/>
-    </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B52" s="9"/>
-      <c r="N52" s="16"/>
-    </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B53" s="9"/>
-      <c r="N53" s="16"/>
-    </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B54" s="9"/>
-      <c r="N54" s="16"/>
-    </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B55" s="9"/>
-      <c r="N55" s="16"/>
-    </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B56" s="9"/>
-      <c r="N56" s="16"/>
-    </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B57" s="9"/>
-      <c r="N57" s="16"/>
-    </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B58" s="9"/>
-      <c r="N58" s="16"/>
-    </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B59" s="9"/>
-      <c r="N59" s="16"/>
-    </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B60" s="9"/>
-      <c r="N60" s="16"/>
-    </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B61" s="9"/>
-      <c r="N61" s="16"/>
-    </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B62" s="9"/>
-      <c r="N62" s="16"/>
-    </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B63" s="9"/>
-      <c r="N63" s="16"/>
-    </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B64" s="9"/>
-      <c r="N64" s="16"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B65" s="9"/>
-      <c r="N65" s="16"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B66" s="9"/>
-      <c r="N66" s="16"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B67" s="9"/>
-      <c r="N67" s="16"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B68" s="9"/>
-      <c r="N68" s="16"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B69" s="9"/>
-      <c r="N69" s="16"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B70" s="9"/>
-      <c r="N70" s="16"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B71" s="9"/>
-      <c r="N71" s="16"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B72" s="9"/>
-      <c r="N72" s="16"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="N73" s="16"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="N74" s="16"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="N75" s="16"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="N76" s="16"/>
-    </row>
-    <row r="77" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F77" s="36"/>
-      <c r="G77" s="36"/>
-      <c r="H77" s="36"/>
-      <c r="N77" s="16"/>
-    </row>
-    <row r="78" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="78"/>
-      <c r="C78" s="79"/>
-      <c r="D78" s="79"/>
-      <c r="E78" s="79"/>
-      <c r="F78" s="36"/>
-      <c r="G78" s="36"/>
-      <c r="H78" s="36"/>
-      <c r="N78" s="16"/>
-    </row>
-    <row r="79" spans="2:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="78"/>
-      <c r="C79" s="79"/>
-      <c r="D79" s="79"/>
-      <c r="E79" s="79"/>
-      <c r="F79" s="36"/>
-      <c r="G79" s="36"/>
-      <c r="H79" s="36"/>
-      <c r="N79" s="16"/>
-    </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B80" s="9"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="16"/>
-      <c r="N80" s="16"/>
-    </row>
-    <row r="81" spans="2:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="9"/>
-      <c r="C81" s="10"/>
-      <c r="D81" s="10"/>
-      <c r="E81" s="10"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="10"/>
-      <c r="N81" s="16"/>
-    </row>
-    <row r="82" spans="2:14" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="C82" s="12"/>
-      <c r="D82" s="24"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="53"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="11"/>
-      <c r="J82" s="11"/>
-      <c r="K82" s="11"/>
-      <c r="L82" s="11"/>
-      <c r="N82" s="16"/>
-    </row>
-    <row r="85" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C85" s="80"/>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="169" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="170" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" s="171" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="172"/>
+      <c r="D20" s="173"/>
+      <c r="E20" s="174"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C21" s="175"/>
+      <c r="D21" s="176"/>
+      <c r="E21" s="177"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C22" s="175"/>
+      <c r="D22" s="176"/>
+      <c r="E22" s="177"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C23" s="175"/>
+      <c r="D23" s="176"/>
+      <c r="E23" s="177"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C24" s="175"/>
+      <c r="D24" s="176"/>
+      <c r="E24" s="177"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C25" s="175"/>
+      <c r="D25" s="176"/>
+      <c r="E25" s="177"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C26" s="175"/>
+      <c r="D26" s="176"/>
+      <c r="E26" s="177"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C27" s="175"/>
+      <c r="D27" s="176"/>
+      <c r="E27" s="177"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C28" s="175"/>
+      <c r="D28" s="176"/>
+      <c r="E28" s="177"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C29" s="178"/>
+      <c r="D29" s="179"/>
+      <c r="E29" s="180"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="C26:G26"/>
+  <mergeCells count="7">
+    <mergeCell ref="C16:E16"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C13:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEACF759-6B24-41AC-859A-CF8770670DE1}">
-  <dimension ref="B5:K29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="4.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="5" spans="2:11" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="150" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="151"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="122"/>
-      <c r="F5" s="122"/>
-      <c r="G5" s="122"/>
-      <c r="H5" s="122"/>
-      <c r="I5" s="122"/>
-      <c r="J5" s="123"/>
-    </row>
-    <row r="7" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B7" s="159" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B8" s="160" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="147"/>
-      <c r="C9" s="149"/>
-      <c r="D9" s="149"/>
-      <c r="E9" s="149"/>
-      <c r="F9" s="149"/>
-      <c r="G9" s="149"/>
-      <c r="H9" s="149"/>
-      <c r="I9" s="149"/>
-      <c r="J9" s="149"/>
-      <c r="K9" s="148"/>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-    </row>
-    <row r="11" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B11" s="160" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="147"/>
-      <c r="C12" s="149"/>
-      <c r="D12" s="149"/>
-      <c r="E12" s="149"/>
-      <c r="F12" s="149"/>
-      <c r="G12" s="149"/>
-      <c r="H12" s="149"/>
-      <c r="I12" s="149"/>
-      <c r="J12" s="149"/>
-      <c r="K12" s="148"/>
-    </row>
-    <row r="14" spans="2:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B14" s="160" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="147"/>
-      <c r="C15" s="149"/>
-      <c r="D15" s="149"/>
-      <c r="E15" s="149"/>
-      <c r="F15" s="149"/>
-      <c r="G15" s="149"/>
-      <c r="H15" s="149"/>
-      <c r="I15" s="149"/>
-      <c r="J15" s="149"/>
-      <c r="K15" s="148"/>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="88"/>
-      <c r="C16" s="88"/>
-      <c r="D16" s="88"/>
-      <c r="E16" s="88"/>
-    </row>
-    <row r="17" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="161" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="88"/>
-      <c r="D17" s="88"/>
-      <c r="E17" s="88"/>
-    </row>
-    <row r="18" spans="2:11" ht="78.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="147"/>
-      <c r="C18" s="149"/>
-      <c r="D18" s="149"/>
-      <c r="E18" s="149"/>
-      <c r="F18" s="149"/>
-      <c r="G18" s="149"/>
-      <c r="H18" s="149"/>
-      <c r="I18" s="149"/>
-      <c r="J18" s="149"/>
-      <c r="K18" s="148"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-    </row>
-    <row r="20" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="162" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-    </row>
-    <row r="21" spans="2:11" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="147"/>
-      <c r="C21" s="149"/>
-      <c r="D21" s="149"/>
-      <c r="E21" s="149"/>
-      <c r="F21" s="149"/>
-      <c r="G21" s="149"/>
-      <c r="H21" s="149"/>
-      <c r="I21" s="149"/>
-      <c r="J21" s="149"/>
-      <c r="K21" s="148"/>
-    </row>
-    <row r="23" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B23" s="72" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="76" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="77" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B25" s="163"/>
-      <c r="C25" s="132"/>
-      <c r="D25" s="133"/>
-      <c r="E25" s="133"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="133"/>
-      <c r="H25" s="134"/>
-    </row>
-    <row r="26" spans="2:11" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B26" s="163"/>
-      <c r="C26" s="132"/>
-      <c r="D26" s="133"/>
-      <c r="E26" s="133"/>
-      <c r="F26" s="133"/>
-      <c r="G26" s="133"/>
-      <c r="H26" s="134"/>
-    </row>
-    <row r="27" spans="2:11" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="B27" s="163"/>
-      <c r="C27" s="135"/>
-      <c r="D27" s="136"/>
-      <c r="E27" s="136"/>
-      <c r="F27" s="136"/>
-      <c r="G27" s="136"/>
-      <c r="H27" s="137"/>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="9"/>
-    </row>
-    <row r="29" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B29" s="17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="C25:H25"/>
-    <mergeCell ref="C26:H26"/>
-    <mergeCell ref="C27:H27"/>
-    <mergeCell ref="B9:K9"/>
-    <mergeCell ref="B12:K12"/>
-    <mergeCell ref="B15:K15"/>
-    <mergeCell ref="B18:K18"/>
-    <mergeCell ref="B21:K21"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:J5"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c596204b-3c01-4828-83dd-c39c80911371" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Owner xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <MediaLengthInSeconds xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" xsi:nil="true"/>
+    <SharedWithUsers xmlns="c596204b-3c01-4828-83dd-c39c80911371">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6321,37 +6700,28 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="c596204b-3c01-4828-83dd-c39c80911371" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Owner xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <MediaLengthInSeconds xmlns="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e" xsi:nil="true"/>
-    <SharedWithUsers xmlns="c596204b-3c01-4828-83dd-c39c80911371">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="c596204b-3c01-4828-83dd-c39c80911371"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6377,19 +6747,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB5231C-6BCA-4792-A2E8-F73749A126E6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{357647EC-285E-4C2F-8A05-102191C13D0D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="c596204b-3c01-4828-83dd-c39c80911371"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="01b9241b-a2d1-4ffb-ad58-1ec8bac5674e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>